--- a/data/out/mitsumori/mitsumori.xlsx
+++ b/data/out/mitsumori/mitsumori.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,33 +29,68 @@
     </font>
     <font>
       <name val="MS-Mincho"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="MS-Mincho"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="MS-Gothic"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="MS-Mincho"/>
+      <color rgb="00000000"/>
       <sz val="25"/>
     </font>
     <font>
       <name val="MS-Mincho"/>
-      <sz val="10"/>
+      <color rgb="00000000"/>
+      <sz val="12.5"/>
     </font>
     <font>
       <name val="MS-Mincho"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="MS-Mincho"/>
+      <color rgb="00000000"/>
+      <sz val="17"/>
+    </font>
+    <font>
+      <name val="MS-Gothic"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="MS-Mincho"/>
-      <sz val="17"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
     </font>
     <font>
-      <name val="MS-Mincho"/>
-      <color rgb="004F4F4F"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="MS-Mincho"/>
+      <name val="MS-Gothic"/>
       <color rgb="004F4F4F"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="MS-Mincho"/>
-      <sz val="12.5"/>
+      <name val="Helvetica"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="AAAAAA+MS-PGothic"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="AAAAAA+MS-PGothic"/>
+      <color rgb="004F4F4F"/>
+      <sz val="18"/>
     </font>
     <font>
       <b val="1"/>
@@ -93,7 +128,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -102,27 +137,57 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
+      <left/>
       <right/>
-      <top style="thin"/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
       <bottom/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin"/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
       <bottom/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
       <bottom/>
     </border>
     <border>
@@ -133,34 +198,39 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
       <top/>
       <bottom/>
     </border>
     <border>
-      <left style="thin"/>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
       <right/>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
     <border>
       <left style="thin"/>
@@ -172,54 +242,88 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -615,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="G10:DI154"/>
+  <dimension ref="F10:DI165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="0.9399999999999999" customWidth="1" min="1" max="1"/>
@@ -760,169 +864,436 @@
           <t>御見積書</t>
         </is>
       </c>
-      <c r="AZ10" s="4" t="n"/>
-      <c r="BA10" s="4" t="n"/>
-      <c r="BB10" s="4" t="n"/>
-      <c r="BC10" s="4" t="n"/>
-      <c r="BD10" s="4" t="n"/>
-      <c r="BE10" s="4" t="n"/>
-      <c r="BF10" s="4" t="n"/>
-      <c r="BG10" s="4" t="n"/>
-      <c r="BH10" s="4" t="n"/>
-      <c r="BI10" s="4" t="n"/>
-      <c r="BJ10" s="4" t="n"/>
-      <c r="BK10" s="4" t="n"/>
-      <c r="BL10" s="4" t="n"/>
-      <c r="BM10" s="4" t="n"/>
-      <c r="BN10" s="4" t="n"/>
-      <c r="BO10" s="4" t="n"/>
-      <c r="BP10" s="4" t="n"/>
-      <c r="BQ10" s="4" t="n"/>
-      <c r="BR10" s="4" t="n"/>
-      <c r="BS10" s="4" t="n"/>
-      <c r="BT10" s="4" t="n"/>
+      <c r="AZ10" s="2" t="n"/>
+      <c r="BA10" s="2" t="n"/>
+      <c r="BB10" s="2" t="n"/>
+      <c r="BC10" s="2" t="n"/>
+      <c r="BD10" s="2" t="n"/>
+      <c r="BE10" s="2" t="n"/>
+      <c r="BF10" s="2" t="n"/>
+      <c r="BG10" s="2" t="n"/>
+      <c r="BH10" s="2" t="n"/>
+      <c r="BI10" s="2" t="n"/>
+      <c r="BJ10" s="2" t="n"/>
+      <c r="BK10" s="2" t="n"/>
+      <c r="BL10" s="2" t="n"/>
+      <c r="BM10" s="2" t="n"/>
+      <c r="BN10" s="2" t="n"/>
+      <c r="BO10" s="2" t="n"/>
+      <c r="BP10" s="2" t="n"/>
+      <c r="BQ10" s="2" t="n"/>
+      <c r="BR10" s="2" t="n"/>
+      <c r="BS10" s="2" t="n"/>
+      <c r="BT10" s="2" t="n"/>
       <c r="BU10" s="2" t="n"/>
       <c r="BV10" s="2" t="n"/>
       <c r="BW10" s="2" t="n"/>
       <c r="BX10" s="2" t="n"/>
-      <c r="BY10" s="5" t="n"/>
+      <c r="BY10" s="4" t="n"/>
     </row>
     <row r="11" ht="4.96" customHeight="1">
-      <c r="AT11" s="6" t="n"/>
-      <c r="AU11" s="7" t="n"/>
-      <c r="AV11" s="7" t="n"/>
-      <c r="AW11" s="7" t="n"/>
-      <c r="AX11" s="7" t="n"/>
-      <c r="BU11" s="7" t="n"/>
-      <c r="BV11" s="7" t="n"/>
-      <c r="BW11" s="7" t="n"/>
-      <c r="BX11" s="7" t="n"/>
-      <c r="BY11" s="8" t="n"/>
+      <c r="AT11" s="5" t="n"/>
+      <c r="AU11" s="6" t="n"/>
+      <c r="AV11" s="6" t="n"/>
+      <c r="AW11" s="6" t="n"/>
+      <c r="AX11" s="6" t="n"/>
+      <c r="AY11" s="6" t="n"/>
+      <c r="AZ11" s="6" t="n"/>
+      <c r="BA11" s="6" t="n"/>
+      <c r="BB11" s="6" t="n"/>
+      <c r="BC11" s="6" t="n"/>
+      <c r="BD11" s="6" t="n"/>
+      <c r="BE11" s="6" t="n"/>
+      <c r="BF11" s="6" t="n"/>
+      <c r="BG11" s="6" t="n"/>
+      <c r="BH11" s="6" t="n"/>
+      <c r="BI11" s="6" t="n"/>
+      <c r="BJ11" s="6" t="n"/>
+      <c r="BK11" s="6" t="n"/>
+      <c r="BL11" s="6" t="n"/>
+      <c r="BM11" s="6" t="n"/>
+      <c r="BN11" s="6" t="n"/>
+      <c r="BO11" s="6" t="n"/>
+      <c r="BP11" s="6" t="n"/>
+      <c r="BQ11" s="6" t="n"/>
+      <c r="BR11" s="6" t="n"/>
+      <c r="BS11" s="6" t="n"/>
+      <c r="BT11" s="6" t="n"/>
+      <c r="BU11" s="6" t="n"/>
+      <c r="BV11" s="6" t="n"/>
+      <c r="BW11" s="6" t="n"/>
+      <c r="BX11" s="6" t="n"/>
+      <c r="BY11" s="7" t="n"/>
     </row>
     <row r="12" ht="4.96" customHeight="1">
-      <c r="AT12" s="6" t="n"/>
-      <c r="AU12" s="7" t="n"/>
-      <c r="AV12" s="7" t="n"/>
-      <c r="AW12" s="7" t="n"/>
-      <c r="AX12" s="7" t="n"/>
-      <c r="BU12" s="7" t="n"/>
-      <c r="BV12" s="7" t="n"/>
-      <c r="BW12" s="7" t="n"/>
-      <c r="BX12" s="7" t="n"/>
-      <c r="BY12" s="8" t="n"/>
+      <c r="AT12" s="5" t="n"/>
+      <c r="AU12" s="6" t="n"/>
+      <c r="AV12" s="6" t="n"/>
+      <c r="AW12" s="6" t="n"/>
+      <c r="AX12" s="6" t="n"/>
+      <c r="AY12" s="6" t="n"/>
+      <c r="AZ12" s="6" t="n"/>
+      <c r="BA12" s="6" t="n"/>
+      <c r="BB12" s="6" t="n"/>
+      <c r="BC12" s="6" t="n"/>
+      <c r="BD12" s="6" t="n"/>
+      <c r="BE12" s="6" t="n"/>
+      <c r="BF12" s="6" t="n"/>
+      <c r="BG12" s="6" t="n"/>
+      <c r="BH12" s="6" t="n"/>
+      <c r="BI12" s="6" t="n"/>
+      <c r="BJ12" s="6" t="n"/>
+      <c r="BK12" s="6" t="n"/>
+      <c r="BL12" s="6" t="n"/>
+      <c r="BM12" s="6" t="n"/>
+      <c r="BN12" s="6" t="n"/>
+      <c r="BO12" s="6" t="n"/>
+      <c r="BP12" s="6" t="n"/>
+      <c r="BQ12" s="6" t="n"/>
+      <c r="BR12" s="6" t="n"/>
+      <c r="BS12" s="6" t="n"/>
+      <c r="BT12" s="6" t="n"/>
+      <c r="BU12" s="6" t="n"/>
+      <c r="BV12" s="6" t="n"/>
+      <c r="BW12" s="6" t="n"/>
+      <c r="BX12" s="6" t="n"/>
+      <c r="BY12" s="7" t="n"/>
     </row>
     <row r="13" ht="4.96" customHeight="1">
-      <c r="AT13" s="6" t="n"/>
-      <c r="AU13" s="7" t="n"/>
-      <c r="AV13" s="7" t="n"/>
-      <c r="AW13" s="7" t="n"/>
-      <c r="AX13" s="7" t="n"/>
-      <c r="BU13" s="7" t="n"/>
-      <c r="BV13" s="7" t="n"/>
-      <c r="BW13" s="7" t="n"/>
-      <c r="BX13" s="7" t="n"/>
-      <c r="BY13" s="8" t="n"/>
+      <c r="AT13" s="5" t="n"/>
+      <c r="AU13" s="6" t="n"/>
+      <c r="AV13" s="6" t="n"/>
+      <c r="AW13" s="6" t="n"/>
+      <c r="AX13" s="6" t="n"/>
+      <c r="AY13" s="6" t="n"/>
+      <c r="AZ13" s="6" t="n"/>
+      <c r="BA13" s="6" t="n"/>
+      <c r="BB13" s="6" t="n"/>
+      <c r="BC13" s="6" t="n"/>
+      <c r="BD13" s="6" t="n"/>
+      <c r="BE13" s="6" t="n"/>
+      <c r="BF13" s="6" t="n"/>
+      <c r="BG13" s="6" t="n"/>
+      <c r="BH13" s="6" t="n"/>
+      <c r="BI13" s="6" t="n"/>
+      <c r="BJ13" s="6" t="n"/>
+      <c r="BK13" s="6" t="n"/>
+      <c r="BL13" s="6" t="n"/>
+      <c r="BM13" s="6" t="n"/>
+      <c r="BN13" s="6" t="n"/>
+      <c r="BO13" s="6" t="n"/>
+      <c r="BP13" s="6" t="n"/>
+      <c r="BQ13" s="6" t="n"/>
+      <c r="BR13" s="6" t="n"/>
+      <c r="BS13" s="6" t="n"/>
+      <c r="BT13" s="6" t="n"/>
+      <c r="BU13" s="6" t="n"/>
+      <c r="BV13" s="6" t="n"/>
+      <c r="BW13" s="6" t="n"/>
+      <c r="BX13" s="6" t="n"/>
+      <c r="BY13" s="7" t="n"/>
     </row>
     <row r="14" ht="4.96" customHeight="1">
-      <c r="AT14" s="6" t="n"/>
-      <c r="AU14" s="7" t="n"/>
-      <c r="AV14" s="7" t="n"/>
-      <c r="AW14" s="7" t="n"/>
-      <c r="AX14" s="7" t="n"/>
-      <c r="BU14" s="7" t="n"/>
-      <c r="BV14" s="7" t="n"/>
-      <c r="BW14" s="7" t="n"/>
-      <c r="BX14" s="7" t="n"/>
-      <c r="BY14" s="8" t="n"/>
+      <c r="AT14" s="5" t="n"/>
+      <c r="AU14" s="6" t="n"/>
+      <c r="AV14" s="6" t="n"/>
+      <c r="AW14" s="6" t="n"/>
+      <c r="AX14" s="6" t="n"/>
+      <c r="AY14" s="6" t="n"/>
+      <c r="AZ14" s="6" t="n"/>
+      <c r="BA14" s="6" t="n"/>
+      <c r="BB14" s="6" t="n"/>
+      <c r="BC14" s="6" t="n"/>
+      <c r="BD14" s="6" t="n"/>
+      <c r="BE14" s="6" t="n"/>
+      <c r="BF14" s="6" t="n"/>
+      <c r="BG14" s="6" t="n"/>
+      <c r="BH14" s="6" t="n"/>
+      <c r="BI14" s="6" t="n"/>
+      <c r="BJ14" s="6" t="n"/>
+      <c r="BK14" s="6" t="n"/>
+      <c r="BL14" s="6" t="n"/>
+      <c r="BM14" s="6" t="n"/>
+      <c r="BN14" s="6" t="n"/>
+      <c r="BO14" s="6" t="n"/>
+      <c r="BP14" s="6" t="n"/>
+      <c r="BQ14" s="6" t="n"/>
+      <c r="BR14" s="6" t="n"/>
+      <c r="BS14" s="6" t="n"/>
+      <c r="BT14" s="6" t="n"/>
+      <c r="BU14" s="6" t="n"/>
+      <c r="BV14" s="6" t="n"/>
+      <c r="BW14" s="6" t="n"/>
+      <c r="BX14" s="6" t="n"/>
+      <c r="BY14" s="7" t="n"/>
     </row>
     <row r="15" ht="4.96" customHeight="1">
-      <c r="AT15" s="6" t="n"/>
-      <c r="AU15" s="7" t="n"/>
-      <c r="AV15" s="7" t="n"/>
-      <c r="AW15" s="7" t="n"/>
-      <c r="AX15" s="7" t="n"/>
-      <c r="BU15" s="7" t="n"/>
-      <c r="BV15" s="7" t="n"/>
-      <c r="BW15" s="7" t="n"/>
-      <c r="BX15" s="7" t="n"/>
-      <c r="BY15" s="8" t="n"/>
+      <c r="AT15" s="5" t="n"/>
+      <c r="AU15" s="6" t="n"/>
+      <c r="AV15" s="6" t="n"/>
+      <c r="AW15" s="6" t="n"/>
+      <c r="AX15" s="6" t="n"/>
+      <c r="AY15" s="6" t="n"/>
+      <c r="AZ15" s="6" t="n"/>
+      <c r="BA15" s="6" t="n"/>
+      <c r="BB15" s="6" t="n"/>
+      <c r="BC15" s="6" t="n"/>
+      <c r="BD15" s="6" t="n"/>
+      <c r="BE15" s="6" t="n"/>
+      <c r="BF15" s="6" t="n"/>
+      <c r="BG15" s="6" t="n"/>
+      <c r="BH15" s="6" t="n"/>
+      <c r="BI15" s="6" t="n"/>
+      <c r="BJ15" s="6" t="n"/>
+      <c r="BK15" s="6" t="n"/>
+      <c r="BL15" s="6" t="n"/>
+      <c r="BM15" s="6" t="n"/>
+      <c r="BN15" s="6" t="n"/>
+      <c r="BO15" s="6" t="n"/>
+      <c r="BP15" s="6" t="n"/>
+      <c r="BQ15" s="6" t="n"/>
+      <c r="BR15" s="6" t="n"/>
+      <c r="BS15" s="6" t="n"/>
+      <c r="BT15" s="6" t="n"/>
+      <c r="BU15" s="6" t="n"/>
+      <c r="BV15" s="6" t="n"/>
+      <c r="BW15" s="6" t="n"/>
+      <c r="BX15" s="6" t="n"/>
+      <c r="BY15" s="7" t="n"/>
     </row>
     <row r="16" ht="4.96" customHeight="1">
-      <c r="AT16" s="9" t="n"/>
-      <c r="AU16" s="10" t="n"/>
-      <c r="AV16" s="10" t="n"/>
-      <c r="AW16" s="10" t="n"/>
-      <c r="AX16" s="10" t="n"/>
-      <c r="AY16" s="10" t="n"/>
-      <c r="AZ16" s="10" t="n"/>
-      <c r="BA16" s="10" t="n"/>
-      <c r="BB16" s="10" t="n"/>
-      <c r="BC16" s="10" t="n"/>
-      <c r="BD16" s="10" t="n"/>
-      <c r="BE16" s="10" t="n"/>
-      <c r="BF16" s="10" t="n"/>
-      <c r="BG16" s="10" t="n"/>
-      <c r="BH16" s="10" t="n"/>
-      <c r="BI16" s="10" t="n"/>
-      <c r="BJ16" s="10" t="n"/>
-      <c r="BK16" s="10" t="n"/>
-      <c r="BL16" s="10" t="n"/>
-      <c r="BM16" s="10" t="n"/>
-      <c r="BN16" s="10" t="n"/>
-      <c r="BO16" s="10" t="n"/>
-      <c r="BP16" s="10" t="n"/>
-      <c r="BQ16" s="10" t="n"/>
-      <c r="BR16" s="10" t="n"/>
-      <c r="BS16" s="10" t="n"/>
-      <c r="BT16" s="10" t="n"/>
-      <c r="BU16" s="10" t="n"/>
-      <c r="BV16" s="10" t="n"/>
-      <c r="BW16" s="10" t="n"/>
-      <c r="BX16" s="10" t="n"/>
-      <c r="BY16" s="11" t="n"/>
+      <c r="AT16" s="8" t="n"/>
+      <c r="AU16" s="9" t="n"/>
+      <c r="AV16" s="9" t="n"/>
+      <c r="AW16" s="9" t="n"/>
+      <c r="AX16" s="9" t="n"/>
+      <c r="AY16" s="9" t="n"/>
+      <c r="AZ16" s="9" t="n"/>
+      <c r="BA16" s="9" t="n"/>
+      <c r="BB16" s="9" t="n"/>
+      <c r="BC16" s="9" t="n"/>
+      <c r="BD16" s="9" t="n"/>
+      <c r="BE16" s="9" t="n"/>
+      <c r="BF16" s="9" t="n"/>
+      <c r="BG16" s="9" t="n"/>
+      <c r="BH16" s="9" t="n"/>
+      <c r="BI16" s="9" t="n"/>
+      <c r="BJ16" s="9" t="n"/>
+      <c r="BK16" s="9" t="n"/>
+      <c r="BL16" s="9" t="n"/>
+      <c r="BM16" s="9" t="n"/>
+      <c r="BN16" s="9" t="n"/>
+      <c r="BO16" s="9" t="n"/>
+      <c r="BP16" s="9" t="n"/>
+      <c r="BQ16" s="9" t="n"/>
+      <c r="BR16" s="9" t="n"/>
+      <c r="BS16" s="9" t="n"/>
+      <c r="BT16" s="9" t="n"/>
+      <c r="BU16" s="9" t="n"/>
+      <c r="BV16" s="9" t="n"/>
+      <c r="BW16" s="9" t="n"/>
+      <c r="BX16" s="9" t="n"/>
+      <c r="BY16" s="10" t="n"/>
     </row>
     <row r="17" ht="4.96" customHeight="1"/>
     <row r="18" ht="4.96" customHeight="1"/>
     <row r="19" ht="4.96" customHeight="1"/>
     <row r="20" ht="4.96" customHeight="1">
-      <c r="CC20" s="12" t="inlineStr">
+      <c r="CC20" s="11" t="inlineStr">
         <is>
           <t>見積書Ｎｏ．</t>
+        </is>
+      </c>
+      <c r="CO20" s="11" t="inlineStr">
+        <is>
+          <t>20121119_00001</t>
         </is>
       </c>
     </row>
     <row r="21" ht="4.96" customHeight="1"/>
     <row r="22" ht="4.96" customHeight="1">
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>△△株式会社</t>
         </is>
       </c>
-      <c r="BD22" s="13" t="inlineStr">
+      <c r="BD22" s="12" t="inlineStr">
         <is>
           <t>御中</t>
         </is>
       </c>
+      <c r="CB22" s="2" t="n"/>
+      <c r="CC22" s="2" t="n"/>
+      <c r="CD22" s="2" t="n"/>
+      <c r="CE22" s="2" t="n"/>
+      <c r="CF22" s="2" t="n"/>
+      <c r="CG22" s="2" t="n"/>
+      <c r="CH22" s="2" t="n"/>
+      <c r="CI22" s="2" t="n"/>
+      <c r="CJ22" s="2" t="n"/>
+      <c r="CK22" s="2" t="n"/>
+      <c r="CL22" s="2" t="n"/>
+      <c r="CM22" s="2" t="n"/>
+      <c r="CN22" s="2" t="n"/>
+      <c r="CO22" s="2" t="n"/>
+      <c r="CP22" s="2" t="n"/>
+      <c r="CQ22" s="2" t="n"/>
+      <c r="CR22" s="2" t="n"/>
+      <c r="CS22" s="2" t="n"/>
+      <c r="CT22" s="2" t="n"/>
+      <c r="CU22" s="2" t="n"/>
+      <c r="CV22" s="2" t="n"/>
+      <c r="CW22" s="2" t="n"/>
+      <c r="CX22" s="2" t="n"/>
+      <c r="CY22" s="2" t="n"/>
+      <c r="CZ22" s="2" t="n"/>
+      <c r="DA22" s="2" t="n"/>
+      <c r="DB22" s="2" t="n"/>
+      <c r="DC22" s="2" t="n"/>
+      <c r="DD22" s="2" t="n"/>
+      <c r="DE22" s="2" t="n"/>
     </row>
     <row r="23" ht="4.96" customHeight="1"/>
     <row r="24" ht="4.96" customHeight="1"/>
-    <row r="25" ht="4.96" customHeight="1"/>
-    <row r="26" ht="4.96" customHeight="1"/>
+    <row r="25" ht="4.96" customHeight="1">
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="n"/>
+      <c r="Q25" s="2" t="n"/>
+      <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
+      <c r="T25" s="2" t="n"/>
+      <c r="U25" s="2" t="n"/>
+      <c r="V25" s="2" t="n"/>
+      <c r="W25" s="2" t="n"/>
+      <c r="X25" s="2" t="n"/>
+      <c r="Y25" s="2" t="n"/>
+      <c r="Z25" s="2" t="n"/>
+      <c r="AA25" s="2" t="n"/>
+      <c r="AB25" s="2" t="n"/>
+      <c r="AC25" s="2" t="n"/>
+      <c r="AD25" s="2" t="n"/>
+      <c r="AE25" s="2" t="n"/>
+      <c r="AF25" s="2" t="n"/>
+      <c r="AG25" s="2" t="n"/>
+      <c r="AH25" s="2" t="n"/>
+      <c r="AI25" s="2" t="n"/>
+      <c r="AJ25" s="2" t="n"/>
+      <c r="AK25" s="2" t="n"/>
+      <c r="AL25" s="2" t="n"/>
+      <c r="AM25" s="2" t="n"/>
+      <c r="AN25" s="2" t="n"/>
+      <c r="AO25" s="2" t="n"/>
+      <c r="AP25" s="2" t="n"/>
+      <c r="AQ25" s="2" t="n"/>
+      <c r="AR25" s="2" t="n"/>
+      <c r="AS25" s="2" t="n"/>
+      <c r="AT25" s="2" t="n"/>
+      <c r="AU25" s="2" t="n"/>
+      <c r="AV25" s="2" t="n"/>
+      <c r="AW25" s="2" t="n"/>
+      <c r="AX25" s="2" t="n"/>
+      <c r="AY25" s="2" t="n"/>
+      <c r="AZ25" s="2" t="n"/>
+      <c r="BA25" s="2" t="n"/>
+      <c r="BB25" s="2" t="n"/>
+      <c r="BC25" s="2" t="n"/>
+      <c r="BD25" s="2" t="n"/>
+      <c r="BE25" s="2" t="n"/>
+      <c r="BF25" s="2" t="n"/>
+      <c r="BG25" s="2" t="n"/>
+      <c r="BH25" s="2" t="n"/>
+      <c r="BI25" s="2" t="n"/>
+      <c r="BJ25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="4.96" customHeight="1">
+      <c r="CC26" s="11" t="inlineStr">
+        <is>
+          <t>作成日:</t>
+        </is>
+      </c>
+      <c r="CK26" s="11" t="inlineStr">
+        <is>
+          <t>2012年11月19日</t>
+        </is>
+      </c>
+    </row>
     <row r="27" ht="4.96" customHeight="1"/>
     <row r="28" ht="4.96" customHeight="1"/>
-    <row r="29" ht="4.96" customHeight="1"/>
+    <row r="29" ht="4.96" customHeight="1">
+      <c r="CB29" s="2" t="n"/>
+      <c r="CC29" s="2" t="n"/>
+      <c r="CD29" s="2" t="n"/>
+      <c r="CE29" s="2" t="n"/>
+      <c r="CF29" s="2" t="n"/>
+      <c r="CG29" s="2" t="n"/>
+      <c r="CH29" s="2" t="n"/>
+      <c r="CI29" s="2" t="n"/>
+      <c r="CJ29" s="2" t="n"/>
+      <c r="CK29" s="2" t="n"/>
+      <c r="CL29" s="2" t="n"/>
+      <c r="CM29" s="2" t="n"/>
+      <c r="CN29" s="2" t="n"/>
+      <c r="CO29" s="2" t="n"/>
+      <c r="CP29" s="2" t="n"/>
+      <c r="CQ29" s="2" t="n"/>
+      <c r="CR29" s="2" t="n"/>
+      <c r="CS29" s="2" t="n"/>
+      <c r="CT29" s="2" t="n"/>
+      <c r="CU29" s="2" t="n"/>
+      <c r="CV29" s="2" t="n"/>
+      <c r="CW29" s="2" t="n"/>
+      <c r="CX29" s="2" t="n"/>
+      <c r="CY29" s="2" t="n"/>
+      <c r="CZ29" s="2" t="n"/>
+      <c r="DA29" s="2" t="n"/>
+      <c r="DB29" s="2" t="n"/>
+      <c r="DC29" s="2" t="n"/>
+      <c r="DD29" s="2" t="n"/>
+    </row>
     <row r="30" ht="4.96" customHeight="1"/>
-    <row r="31" ht="4.96" customHeight="1"/>
+    <row r="31" ht="4.96" customHeight="1">
+      <c r="O31" s="13" t="inlineStr">
+        <is>
+          <t>下記のとおり御見積申し上げます。</t>
+        </is>
+      </c>
+    </row>
     <row r="32" ht="4.96" customHeight="1"/>
     <row r="33" ht="4.96" customHeight="1"/>
-    <row r="34" ht="4.96" customHeight="1"/>
+    <row r="34" ht="4.96" customHeight="1">
+      <c r="O34" s="13" t="inlineStr">
+        <is>
+          <t>何卒ご用命の程、お願い申し上げます。</t>
+        </is>
+      </c>
+    </row>
     <row r="35" ht="4.96" customHeight="1"/>
     <row r="36" ht="4.96" customHeight="1"/>
     <row r="37" ht="4.96" customHeight="1"/>
     <row r="38" ht="4.96" customHeight="1"/>
     <row r="39" ht="4.96" customHeight="1"/>
     <row r="40" ht="4.96" customHeight="1"/>
-    <row r="41" ht="4.96" customHeight="1"/>
+    <row r="41" ht="4.96" customHeight="1">
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>受渡期日:</t>
+        </is>
+      </c>
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>別途御打合せ</t>
+        </is>
+      </c>
+    </row>
     <row r="42" ht="4.96" customHeight="1">
       <c r="CC42" s="14" t="inlineStr">
         <is>
@@ -931,45 +1302,424 @@
       </c>
     </row>
     <row r="43" ht="4.96" customHeight="1"/>
-    <row r="44" ht="4.96" customHeight="1"/>
+    <row r="44" ht="4.96" customHeight="1">
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n"/>
+      <c r="S44" s="2" t="n"/>
+      <c r="T44" s="2" t="n"/>
+      <c r="U44" s="2" t="n"/>
+      <c r="V44" s="2" t="n"/>
+      <c r="W44" s="2" t="n"/>
+      <c r="X44" s="2" t="n"/>
+      <c r="Y44" s="2" t="n"/>
+      <c r="Z44" s="2" t="n"/>
+      <c r="AA44" s="2" t="n"/>
+      <c r="AB44" s="2" t="n"/>
+      <c r="AC44" s="2" t="n"/>
+      <c r="AD44" s="2" t="n"/>
+      <c r="AE44" s="2" t="n"/>
+      <c r="AF44" s="2" t="n"/>
+      <c r="AG44" s="2" t="n"/>
+      <c r="AH44" s="2" t="n"/>
+      <c r="AI44" s="2" t="n"/>
+      <c r="AJ44" s="2" t="n"/>
+      <c r="AK44" s="2" t="n"/>
+      <c r="AL44" s="2" t="n"/>
+      <c r="AM44" s="2" t="n"/>
+      <c r="AN44" s="2" t="n"/>
+      <c r="AO44" s="2" t="n"/>
+      <c r="AP44" s="2" t="n"/>
+      <c r="AQ44" s="2" t="n"/>
+      <c r="AR44" s="2" t="n"/>
+      <c r="AS44" s="2" t="n"/>
+      <c r="AT44" s="2" t="n"/>
+      <c r="AU44" s="2" t="n"/>
+      <c r="AV44" s="2" t="n"/>
+      <c r="AW44" s="2" t="n"/>
+      <c r="AX44" s="2" t="n"/>
+      <c r="AY44" s="2" t="n"/>
+      <c r="AZ44" s="2" t="n"/>
+      <c r="BA44" s="2" t="n"/>
+      <c r="BB44" s="2" t="n"/>
+      <c r="BC44" s="2" t="n"/>
+      <c r="BD44" s="2" t="n"/>
+      <c r="BE44" s="2" t="n"/>
+      <c r="BF44" s="2" t="n"/>
+      <c r="BG44" s="2" t="n"/>
+      <c r="BH44" s="2" t="n"/>
+      <c r="BI44" s="2" t="n"/>
+      <c r="BJ44" s="2" t="n"/>
+    </row>
     <row r="45" ht="4.96" customHeight="1"/>
-    <row r="46" ht="4.96" customHeight="1"/>
+    <row r="46" ht="4.96" customHeight="1">
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>取引方法:</t>
+        </is>
+      </c>
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>別途御打合せ</t>
+        </is>
+      </c>
+      <c r="CD46" s="11" t="inlineStr">
+        <is>
+          <t>東京都新宿区千代田９−９−９</t>
+        </is>
+      </c>
+    </row>
     <row r="47" ht="4.96" customHeight="1"/>
     <row r="48" ht="4.96" customHeight="1"/>
-    <row r="49" ht="4.96" customHeight="1"/>
+    <row r="49" ht="4.96" customHeight="1">
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="n"/>
+      <c r="P49" s="2" t="n"/>
+      <c r="Q49" s="2" t="n"/>
+      <c r="R49" s="2" t="n"/>
+      <c r="S49" s="2" t="n"/>
+      <c r="T49" s="2" t="n"/>
+      <c r="U49" s="2" t="n"/>
+      <c r="V49" s="2" t="n"/>
+      <c r="W49" s="2" t="n"/>
+      <c r="X49" s="2" t="n"/>
+      <c r="Y49" s="2" t="n"/>
+      <c r="Z49" s="2" t="n"/>
+      <c r="AA49" s="2" t="n"/>
+      <c r="AB49" s="2" t="n"/>
+      <c r="AC49" s="2" t="n"/>
+      <c r="AD49" s="2" t="n"/>
+      <c r="AE49" s="2" t="n"/>
+      <c r="AF49" s="2" t="n"/>
+      <c r="AG49" s="2" t="n"/>
+      <c r="AH49" s="2" t="n"/>
+      <c r="AI49" s="2" t="n"/>
+      <c r="AJ49" s="2" t="n"/>
+      <c r="AK49" s="2" t="n"/>
+      <c r="AL49" s="2" t="n"/>
+      <c r="AM49" s="2" t="n"/>
+      <c r="AN49" s="2" t="n"/>
+      <c r="AO49" s="2" t="n"/>
+      <c r="AP49" s="2" t="n"/>
+      <c r="AQ49" s="2" t="n"/>
+      <c r="AR49" s="2" t="n"/>
+      <c r="AS49" s="2" t="n"/>
+      <c r="AT49" s="2" t="n"/>
+      <c r="AU49" s="2" t="n"/>
+      <c r="AV49" s="2" t="n"/>
+      <c r="AW49" s="2" t="n"/>
+      <c r="AX49" s="2" t="n"/>
+      <c r="AY49" s="2" t="n"/>
+      <c r="AZ49" s="2" t="n"/>
+      <c r="BA49" s="2" t="n"/>
+      <c r="BB49" s="2" t="n"/>
+      <c r="BC49" s="2" t="n"/>
+      <c r="BD49" s="2" t="n"/>
+      <c r="BE49" s="2" t="n"/>
+      <c r="BF49" s="2" t="n"/>
+      <c r="BG49" s="2" t="n"/>
+      <c r="BH49" s="2" t="n"/>
+      <c r="BI49" s="2" t="n"/>
+      <c r="BJ49" s="2" t="n"/>
+      <c r="CD49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　　　WSビル</t>
+        </is>
+      </c>
+    </row>
     <row r="50" ht="4.96" customHeight="1"/>
-    <row r="51" ht="4.96" customHeight="1"/>
+    <row r="51" ht="4.96" customHeight="1">
+      <c r="F51" s="13" t="inlineStr">
+        <is>
+          <t>有効期限:</t>
+        </is>
+      </c>
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t>発行日から30日</t>
+        </is>
+      </c>
+      <c r="CD51" s="11" t="inlineStr">
+        <is>
+          <t>TEL  ０３-××××−９９９９</t>
+        </is>
+      </c>
+    </row>
     <row r="52" ht="4.96" customHeight="1"/>
     <row r="53" ht="4.96" customHeight="1"/>
-    <row r="54" ht="4.96" customHeight="1"/>
+    <row r="54" ht="4.96" customHeight="1">
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n"/>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
+      <c r="P54" s="2" t="n"/>
+      <c r="Q54" s="2" t="n"/>
+      <c r="R54" s="2" t="n"/>
+      <c r="S54" s="2" t="n"/>
+      <c r="T54" s="2" t="n"/>
+      <c r="U54" s="2" t="n"/>
+      <c r="V54" s="2" t="n"/>
+      <c r="W54" s="2" t="n"/>
+      <c r="X54" s="2" t="n"/>
+      <c r="Y54" s="2" t="n"/>
+      <c r="Z54" s="2" t="n"/>
+      <c r="AA54" s="2" t="n"/>
+      <c r="AB54" s="2" t="n"/>
+      <c r="AC54" s="2" t="n"/>
+      <c r="AD54" s="2" t="n"/>
+      <c r="AE54" s="2" t="n"/>
+      <c r="AF54" s="2" t="n"/>
+      <c r="AG54" s="2" t="n"/>
+      <c r="AH54" s="2" t="n"/>
+      <c r="AI54" s="2" t="n"/>
+      <c r="AJ54" s="2" t="n"/>
+      <c r="AK54" s="2" t="n"/>
+      <c r="AL54" s="2" t="n"/>
+      <c r="AM54" s="2" t="n"/>
+      <c r="AN54" s="2" t="n"/>
+      <c r="AO54" s="2" t="n"/>
+      <c r="AP54" s="2" t="n"/>
+      <c r="AQ54" s="2" t="n"/>
+      <c r="AR54" s="2" t="n"/>
+      <c r="AS54" s="2" t="n"/>
+      <c r="AT54" s="2" t="n"/>
+      <c r="AU54" s="2" t="n"/>
+      <c r="AV54" s="2" t="n"/>
+      <c r="AW54" s="2" t="n"/>
+      <c r="AX54" s="2" t="n"/>
+      <c r="AY54" s="2" t="n"/>
+      <c r="AZ54" s="2" t="n"/>
+      <c r="BA54" s="2" t="n"/>
+      <c r="BB54" s="2" t="n"/>
+      <c r="BC54" s="2" t="n"/>
+      <c r="BD54" s="2" t="n"/>
+      <c r="BE54" s="2" t="n"/>
+      <c r="BF54" s="2" t="n"/>
+      <c r="BG54" s="2" t="n"/>
+      <c r="BH54" s="2" t="n"/>
+      <c r="BI54" s="2" t="n"/>
+      <c r="BJ54" s="2" t="n"/>
+      <c r="CD54" s="11" t="inlineStr">
+        <is>
+          <t>FAX  ０３-９９９９−××××</t>
+        </is>
+      </c>
+    </row>
     <row r="55" ht="4.96" customHeight="1"/>
-    <row r="56" ht="4.96" customHeight="1"/>
-    <row r="57" ht="4.96" customHeight="1"/>
-    <row r="58" ht="4.96" customHeight="1"/>
-    <row r="59" ht="4.96" customHeight="1"/>
-    <row r="60" ht="4.96" customHeight="1"/>
-    <row r="61" ht="4.96" customHeight="1"/>
-    <row r="62" ht="4.96" customHeight="1"/>
-    <row r="63" ht="4.96" customHeight="1"/>
-    <row r="64" ht="4.96" customHeight="1"/>
-    <row r="65" ht="4.96" customHeight="1"/>
-    <row r="66" ht="4.96" customHeight="1"/>
-    <row r="67" ht="4.96" customHeight="1"/>
-    <row r="68" ht="4.96" customHeight="1"/>
+    <row r="56" ht="4.96" customHeight="1">
+      <c r="CD56" s="11" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="4.96" customHeight="1">
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>貴社管理番号：</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="4.96" customHeight="1">
+      <c r="CM58" s="1" t="n"/>
+      <c r="CN58" s="2" t="n"/>
+      <c r="CO58" s="2" t="n"/>
+      <c r="CP58" s="2" t="n"/>
+      <c r="CQ58" s="2" t="n"/>
+      <c r="CR58" s="2" t="n"/>
+      <c r="CS58" s="2" t="n"/>
+      <c r="CT58" s="2" t="n"/>
+      <c r="CU58" s="2" t="n"/>
+      <c r="CV58" s="2" t="n"/>
+      <c r="CW58" s="1" t="n"/>
+      <c r="CX58" s="2" t="n"/>
+      <c r="CY58" s="2" t="n"/>
+      <c r="CZ58" s="2" t="n"/>
+      <c r="DA58" s="2" t="n"/>
+      <c r="DB58" s="2" t="n"/>
+      <c r="DC58" s="2" t="n"/>
+      <c r="DD58" s="2" t="n"/>
+      <c r="DE58" s="2" t="n"/>
+      <c r="DF58" s="2" t="n"/>
+      <c r="DG58" s="1" t="n"/>
+    </row>
+    <row r="59" ht="4.96" customHeight="1">
+      <c r="CM59" s="5" t="n"/>
+      <c r="CP59" s="15" t="inlineStr">
+        <is>
+          <t>承認</t>
+        </is>
+      </c>
+      <c r="CW59" s="5" t="n"/>
+      <c r="CY59" s="15" t="inlineStr">
+        <is>
+          <t>担当営業</t>
+        </is>
+      </c>
+      <c r="DG59" s="5" t="n"/>
+    </row>
+    <row r="60" ht="4.96" customHeight="1">
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="n"/>
+      <c r="N60" s="2" t="n"/>
+      <c r="O60" s="2" t="n"/>
+      <c r="P60" s="2" t="n"/>
+      <c r="Q60" s="2" t="n"/>
+      <c r="R60" s="2" t="n"/>
+      <c r="S60" s="2" t="n"/>
+      <c r="T60" s="2" t="n"/>
+      <c r="U60" s="2" t="n"/>
+      <c r="V60" s="2" t="n"/>
+      <c r="W60" s="2" t="n"/>
+      <c r="X60" s="2" t="n"/>
+      <c r="Y60" s="2" t="n"/>
+      <c r="Z60" s="2" t="n"/>
+      <c r="AA60" s="2" t="n"/>
+      <c r="AB60" s="2" t="n"/>
+      <c r="AC60" s="2" t="n"/>
+      <c r="AD60" s="2" t="n"/>
+      <c r="AE60" s="2" t="n"/>
+      <c r="AF60" s="2" t="n"/>
+      <c r="AG60" s="2" t="n"/>
+      <c r="AH60" s="2" t="n"/>
+      <c r="AI60" s="2" t="n"/>
+      <c r="AJ60" s="2" t="n"/>
+      <c r="AK60" s="2" t="n"/>
+      <c r="AL60" s="2" t="n"/>
+      <c r="AM60" s="2" t="n"/>
+      <c r="AN60" s="2" t="n"/>
+      <c r="AO60" s="2" t="n"/>
+      <c r="AP60" s="2" t="n"/>
+      <c r="AQ60" s="2" t="n"/>
+      <c r="AR60" s="2" t="n"/>
+      <c r="AS60" s="2" t="n"/>
+      <c r="AT60" s="2" t="n"/>
+      <c r="AU60" s="2" t="n"/>
+      <c r="AV60" s="2" t="n"/>
+      <c r="CM60" s="1" t="n"/>
+      <c r="CN60" s="2" t="n"/>
+      <c r="CO60" s="2" t="n"/>
+      <c r="CP60" s="2" t="n"/>
+      <c r="CQ60" s="2" t="n"/>
+      <c r="CR60" s="2" t="n"/>
+      <c r="CS60" s="2" t="n"/>
+      <c r="CT60" s="2" t="n"/>
+      <c r="CU60" s="2" t="n"/>
+      <c r="CV60" s="2" t="n"/>
+      <c r="CW60" s="1" t="n"/>
+      <c r="CX60" s="2" t="n"/>
+      <c r="CY60" s="2" t="n"/>
+      <c r="CZ60" s="2" t="n"/>
+      <c r="DA60" s="2" t="n"/>
+      <c r="DB60" s="2" t="n"/>
+      <c r="DC60" s="2" t="n"/>
+      <c r="DD60" s="2" t="n"/>
+      <c r="DE60" s="2" t="n"/>
+      <c r="DF60" s="2" t="n"/>
+      <c r="DG60" s="1" t="n"/>
+    </row>
+    <row r="61" ht="4.96" customHeight="1">
+      <c r="CM61" s="5" t="n"/>
+      <c r="CW61" s="5" t="n"/>
+      <c r="DG61" s="5" t="n"/>
+    </row>
+    <row r="62" ht="4.96" customHeight="1">
+      <c r="CM62" s="5" t="n"/>
+      <c r="CW62" s="5" t="n"/>
+      <c r="DG62" s="5" t="n"/>
+    </row>
+    <row r="63" ht="4.96" customHeight="1">
+      <c r="CM63" s="5" t="n"/>
+      <c r="CW63" s="5" t="n"/>
+      <c r="DG63" s="5" t="n"/>
+    </row>
+    <row r="64" ht="4.96" customHeight="1">
+      <c r="CM64" s="5" t="n"/>
+      <c r="CW64" s="5" t="n"/>
+      <c r="DG64" s="5" t="n"/>
+    </row>
+    <row r="65" ht="4.96" customHeight="1">
+      <c r="CM65" s="5" t="n"/>
+      <c r="CW65" s="5" t="n"/>
+      <c r="DG65" s="5" t="n"/>
+    </row>
+    <row r="66" ht="4.96" customHeight="1">
+      <c r="CM66" s="5" t="n"/>
+      <c r="CW66" s="5" t="n"/>
+      <c r="DG66" s="5" t="n"/>
+    </row>
+    <row r="67" ht="4.96" customHeight="1">
+      <c r="CM67" s="5" t="n"/>
+      <c r="CW67" s="5" t="n"/>
+      <c r="DG67" s="5" t="n"/>
+    </row>
+    <row r="68" ht="4.96" customHeight="1">
+      <c r="CM68" s="1" t="n"/>
+      <c r="CN68" s="2" t="n"/>
+      <c r="CO68" s="2" t="n"/>
+      <c r="CP68" s="2" t="n"/>
+      <c r="CQ68" s="2" t="n"/>
+      <c r="CR68" s="2" t="n"/>
+      <c r="CS68" s="2" t="n"/>
+      <c r="CT68" s="2" t="n"/>
+      <c r="CU68" s="2" t="n"/>
+      <c r="CV68" s="2" t="n"/>
+      <c r="CW68" s="1" t="n"/>
+      <c r="CX68" s="2" t="n"/>
+      <c r="CY68" s="2" t="n"/>
+      <c r="CZ68" s="2" t="n"/>
+      <c r="DA68" s="2" t="n"/>
+      <c r="DB68" s="2" t="n"/>
+      <c r="DC68" s="2" t="n"/>
+      <c r="DD68" s="2" t="n"/>
+      <c r="DE68" s="2" t="n"/>
+      <c r="DF68" s="2" t="n"/>
+      <c r="DG68" s="1" t="n"/>
+    </row>
     <row r="69" ht="4.96" customHeight="1">
-      <c r="AY69" s="15" t="inlineStr">
+      <c r="AY69" s="16" t="inlineStr">
         <is>
           <t>\3,700,000</t>
         </is>
       </c>
     </row>
     <row r="70" ht="4.96" customHeight="1">
-      <c r="W70" s="16" t="inlineStr">
+      <c r="W70" s="17" t="inlineStr">
         <is>
           <t>合計金額：</t>
         </is>
       </c>
-      <c r="BP70" s="17" t="inlineStr">
+      <c r="BP70" s="18" t="inlineStr">
         <is>
           <t>(消費税別)</t>
         </is>
@@ -978,11 +1728,118 @@
     <row r="71" ht="4.96" customHeight="1"/>
     <row r="72" ht="4.96" customHeight="1"/>
     <row r="73" ht="4.96" customHeight="1"/>
-    <row r="74" ht="4.96" customHeight="1"/>
+    <row r="74" ht="4.96" customHeight="1">
+      <c r="L74" s="19" t="n"/>
+      <c r="M74" s="19" t="n"/>
+      <c r="N74" s="19" t="n"/>
+      <c r="O74" s="19" t="n"/>
+      <c r="P74" s="19" t="n"/>
+      <c r="Q74" s="19" t="n"/>
+      <c r="R74" s="19" t="n"/>
+      <c r="S74" s="19" t="n"/>
+      <c r="T74" s="19" t="n"/>
+      <c r="U74" s="19" t="n"/>
+      <c r="V74" s="19" t="n"/>
+      <c r="W74" s="19" t="n"/>
+      <c r="X74" s="19" t="n"/>
+      <c r="Y74" s="19" t="n"/>
+      <c r="Z74" s="19" t="n"/>
+      <c r="AA74" s="19" t="n"/>
+      <c r="AB74" s="19" t="n"/>
+      <c r="AC74" s="19" t="n"/>
+      <c r="AD74" s="19" t="n"/>
+      <c r="AE74" s="19" t="n"/>
+      <c r="AF74" s="19" t="n"/>
+      <c r="AG74" s="19" t="n"/>
+      <c r="AH74" s="19" t="n"/>
+      <c r="AI74" s="19" t="n"/>
+      <c r="AJ74" s="19" t="n"/>
+      <c r="AK74" s="19" t="n"/>
+      <c r="AL74" s="19" t="n"/>
+      <c r="AM74" s="19" t="n"/>
+      <c r="AN74" s="19" t="n"/>
+      <c r="AO74" s="19" t="n"/>
+      <c r="AP74" s="19" t="n"/>
+      <c r="AQ74" s="19" t="n"/>
+      <c r="AR74" s="19" t="n"/>
+      <c r="AS74" s="19" t="n"/>
+      <c r="AT74" s="19" t="n"/>
+      <c r="AU74" s="19" t="n"/>
+      <c r="AV74" s="19" t="n"/>
+      <c r="AW74" s="19" t="n"/>
+      <c r="AX74" s="19" t="n"/>
+      <c r="AY74" s="19" t="n"/>
+      <c r="AZ74" s="19" t="n"/>
+      <c r="BA74" s="19" t="n"/>
+      <c r="BB74" s="19" t="n"/>
+      <c r="BC74" s="19" t="n"/>
+      <c r="BD74" s="19" t="n"/>
+      <c r="BE74" s="19" t="n"/>
+      <c r="BF74" s="19" t="n"/>
+      <c r="BG74" s="19" t="n"/>
+      <c r="BH74" s="19" t="n"/>
+      <c r="BI74" s="19" t="n"/>
+      <c r="BJ74" s="19" t="n"/>
+      <c r="BK74" s="19" t="n"/>
+      <c r="BL74" s="19" t="n"/>
+      <c r="BM74" s="19" t="n"/>
+      <c r="BN74" s="19" t="n"/>
+      <c r="BO74" s="19" t="n"/>
+      <c r="BP74" s="19" t="n"/>
+      <c r="BQ74" s="19" t="n"/>
+      <c r="BR74" s="19" t="n"/>
+      <c r="BS74" s="19" t="n"/>
+      <c r="BT74" s="19" t="n"/>
+      <c r="BU74" s="19" t="n"/>
+      <c r="BV74" s="19" t="n"/>
+      <c r="BW74" s="19" t="n"/>
+      <c r="BX74" s="19" t="n"/>
+      <c r="BY74" s="19" t="n"/>
+      <c r="BZ74" s="19" t="n"/>
+      <c r="CA74" s="19" t="n"/>
+      <c r="CB74" s="19" t="n"/>
+      <c r="CC74" s="19" t="n"/>
+      <c r="CD74" s="19" t="n"/>
+      <c r="CE74" s="19" t="n"/>
+      <c r="CF74" s="19" t="n"/>
+      <c r="CG74" s="19" t="n"/>
+      <c r="CH74" s="19" t="n"/>
+      <c r="CI74" s="19" t="n"/>
+      <c r="CJ74" s="19" t="n"/>
+      <c r="CK74" s="19" t="n"/>
+      <c r="CL74" s="19" t="n"/>
+      <c r="CM74" s="19" t="n"/>
+      <c r="CN74" s="19" t="n"/>
+      <c r="CO74" s="19" t="n"/>
+      <c r="CP74" s="19" t="n"/>
+      <c r="CQ74" s="19" t="n"/>
+      <c r="CR74" s="19" t="n"/>
+      <c r="CS74" s="19" t="n"/>
+      <c r="CT74" s="19" t="n"/>
+      <c r="CU74" s="19" t="n"/>
+      <c r="CV74" s="19" t="n"/>
+      <c r="CW74" s="19" t="n"/>
+      <c r="CX74" s="19" t="n"/>
+      <c r="CY74" s="19" t="n"/>
+      <c r="CZ74" s="19" t="n"/>
+      <c r="DA74" s="19" t="n"/>
+      <c r="DB74" s="19" t="n"/>
+      <c r="DC74" s="19" t="n"/>
+      <c r="DD74" s="19" t="n"/>
+      <c r="DE74" s="19" t="n"/>
+      <c r="DF74" s="19" t="n"/>
+      <c r="DG74" s="19" t="n"/>
+      <c r="DH74" s="19" t="n"/>
+      <c r="DI74" s="19" t="n"/>
+    </row>
     <row r="75" ht="4.96" customHeight="1"/>
     <row r="76" ht="4.96" customHeight="1"/>
     <row r="77" ht="4.96" customHeight="1">
-      <c r="L77" s="1" t="n"/>
+      <c r="L77" s="20" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
       <c r="M77" s="2" t="n"/>
       <c r="N77" s="2" t="n"/>
       <c r="O77" s="2" t="n"/>
@@ -999,20 +1856,20 @@
       <c r="Z77" s="2" t="n"/>
       <c r="AA77" s="2" t="n"/>
       <c r="AB77" s="2" t="n"/>
-      <c r="AC77" s="18" t="inlineStr">
+      <c r="AC77" s="21" t="inlineStr">
         <is>
           <t>摘　　要</t>
         </is>
       </c>
-      <c r="AD77" s="4" t="n"/>
-      <c r="AE77" s="4" t="n"/>
-      <c r="AF77" s="4" t="n"/>
-      <c r="AG77" s="4" t="n"/>
-      <c r="AH77" s="4" t="n"/>
-      <c r="AI77" s="4" t="n"/>
-      <c r="AJ77" s="4" t="n"/>
-      <c r="AK77" s="4" t="n"/>
-      <c r="AL77" s="4" t="n"/>
+      <c r="AD77" s="2" t="n"/>
+      <c r="AE77" s="2" t="n"/>
+      <c r="AF77" s="2" t="n"/>
+      <c r="AG77" s="2" t="n"/>
+      <c r="AH77" s="2" t="n"/>
+      <c r="AI77" s="2" t="n"/>
+      <c r="AJ77" s="2" t="n"/>
+      <c r="AK77" s="2" t="n"/>
+      <c r="AL77" s="2" t="n"/>
       <c r="AM77" s="2" t="n"/>
       <c r="AN77" s="2" t="n"/>
       <c r="AO77" s="2" t="n"/>
@@ -1038,81 +1895,81 @@
       <c r="BI77" s="2" t="n"/>
       <c r="BJ77" s="2" t="n"/>
       <c r="BK77" s="1" t="n"/>
-      <c r="BL77" s="18" t="inlineStr">
+      <c r="BL77" s="21" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="BM77" s="4" t="n"/>
-      <c r="BN77" s="4" t="n"/>
-      <c r="BO77" s="4" t="n"/>
-      <c r="BP77" s="4" t="n"/>
-      <c r="BQ77" s="4" t="n"/>
+      <c r="BM77" s="2" t="n"/>
+      <c r="BN77" s="2" t="n"/>
+      <c r="BO77" s="2" t="n"/>
+      <c r="BP77" s="2" t="n"/>
+      <c r="BQ77" s="2" t="n"/>
       <c r="BR77" s="2" t="n"/>
       <c r="BS77" s="1" t="n"/>
       <c r="BT77" s="2" t="n"/>
-      <c r="BU77" s="18" t="inlineStr">
+      <c r="BU77" s="21" t="inlineStr">
         <is>
           <t>標準価格</t>
         </is>
       </c>
-      <c r="BV77" s="4" t="n"/>
-      <c r="BW77" s="4" t="n"/>
-      <c r="BX77" s="4" t="n"/>
-      <c r="BY77" s="4" t="n"/>
-      <c r="BZ77" s="4" t="n"/>
-      <c r="CA77" s="4" t="n"/>
-      <c r="CB77" s="4" t="n"/>
-      <c r="CC77" s="4" t="n"/>
-      <c r="CD77" s="4" t="n"/>
+      <c r="BV77" s="2" t="n"/>
+      <c r="BW77" s="2" t="n"/>
+      <c r="BX77" s="2" t="n"/>
+      <c r="BY77" s="2" t="n"/>
+      <c r="BZ77" s="2" t="n"/>
+      <c r="CA77" s="2" t="n"/>
+      <c r="CB77" s="2" t="n"/>
+      <c r="CC77" s="2" t="n"/>
+      <c r="CD77" s="2" t="n"/>
       <c r="CE77" s="2" t="n"/>
       <c r="CF77" s="1" t="n"/>
       <c r="CG77" s="2" t="n"/>
       <c r="CH77" s="2" t="n"/>
-      <c r="CI77" s="18" t="inlineStr">
+      <c r="CI77" s="21" t="inlineStr">
         <is>
           <t>見積価格</t>
         </is>
       </c>
-      <c r="CJ77" s="4" t="n"/>
-      <c r="CK77" s="4" t="n"/>
-      <c r="CL77" s="4" t="n"/>
-      <c r="CM77" s="4" t="n"/>
-      <c r="CN77" s="4" t="n"/>
-      <c r="CO77" s="4" t="n"/>
-      <c r="CP77" s="4" t="n"/>
-      <c r="CQ77" s="4" t="n"/>
-      <c r="CR77" s="4" t="n"/>
+      <c r="CJ77" s="2" t="n"/>
+      <c r="CK77" s="2" t="n"/>
+      <c r="CL77" s="2" t="n"/>
+      <c r="CM77" s="2" t="n"/>
+      <c r="CN77" s="2" t="n"/>
+      <c r="CO77" s="2" t="n"/>
+      <c r="CP77" s="2" t="n"/>
+      <c r="CQ77" s="2" t="n"/>
+      <c r="CR77" s="2" t="n"/>
       <c r="CS77" s="2" t="n"/>
       <c r="CT77" s="1" t="n"/>
       <c r="CU77" s="2" t="n"/>
       <c r="CV77" s="2" t="n"/>
-      <c r="CW77" s="18" t="inlineStr">
+      <c r="CW77" s="21" t="inlineStr">
         <is>
           <t>合計金額</t>
         </is>
       </c>
-      <c r="CX77" s="4" t="n"/>
-      <c r="CY77" s="4" t="n"/>
-      <c r="CZ77" s="4" t="n"/>
-      <c r="DA77" s="4" t="n"/>
-      <c r="DB77" s="4" t="n"/>
-      <c r="DC77" s="4" t="n"/>
-      <c r="DD77" s="4" t="n"/>
-      <c r="DE77" s="4" t="n"/>
-      <c r="DF77" s="4" t="n"/>
+      <c r="CX77" s="2" t="n"/>
+      <c r="CY77" s="2" t="n"/>
+      <c r="CZ77" s="2" t="n"/>
+      <c r="DA77" s="2" t="n"/>
+      <c r="DB77" s="2" t="n"/>
+      <c r="DC77" s="2" t="n"/>
+      <c r="DD77" s="2" t="n"/>
+      <c r="DE77" s="2" t="n"/>
+      <c r="DF77" s="2" t="n"/>
       <c r="DG77" s="2" t="n"/>
       <c r="DH77" s="2" t="n"/>
       <c r="DI77" s="1" t="n"/>
     </row>
     <row r="78" ht="4.96" customHeight="1">
-      <c r="L78" s="6" t="n"/>
-      <c r="P78" s="6" t="n"/>
-      <c r="BK78" s="6" t="n"/>
-      <c r="BS78" s="6" t="n"/>
-      <c r="CF78" s="6" t="n"/>
-      <c r="CT78" s="6" t="n"/>
-      <c r="DI78" s="6" t="n"/>
+      <c r="L78" s="5" t="n"/>
+      <c r="P78" s="5" t="n"/>
+      <c r="BK78" s="5" t="n"/>
+      <c r="BS78" s="5" t="n"/>
+      <c r="CF78" s="5" t="n"/>
+      <c r="CT78" s="5" t="n"/>
+      <c r="DI78" s="5" t="n"/>
     </row>
     <row r="79" ht="4.96" customHeight="1">
       <c r="L79" s="1" t="n"/>
@@ -1132,6 +1989,16 @@
       <c r="Z79" s="2" t="n"/>
       <c r="AA79" s="2" t="n"/>
       <c r="AB79" s="2" t="n"/>
+      <c r="AC79" s="2" t="n"/>
+      <c r="AD79" s="2" t="n"/>
+      <c r="AE79" s="2" t="n"/>
+      <c r="AF79" s="2" t="n"/>
+      <c r="AG79" s="2" t="n"/>
+      <c r="AH79" s="2" t="n"/>
+      <c r="AI79" s="2" t="n"/>
+      <c r="AJ79" s="2" t="n"/>
+      <c r="AK79" s="2" t="n"/>
+      <c r="AL79" s="2" t="n"/>
       <c r="AM79" s="2" t="n"/>
       <c r="AN79" s="2" t="n"/>
       <c r="AO79" s="2" t="n"/>
@@ -1157,847 +2024,3332 @@
       <c r="BI79" s="2" t="n"/>
       <c r="BJ79" s="2" t="n"/>
       <c r="BK79" s="1" t="n"/>
+      <c r="BL79" s="2" t="n"/>
+      <c r="BM79" s="2" t="n"/>
+      <c r="BN79" s="2" t="n"/>
+      <c r="BO79" s="2" t="n"/>
+      <c r="BP79" s="2" t="n"/>
+      <c r="BQ79" s="2" t="n"/>
       <c r="BR79" s="2" t="n"/>
       <c r="BS79" s="1" t="n"/>
       <c r="BT79" s="2" t="n"/>
+      <c r="BU79" s="2" t="n"/>
+      <c r="BV79" s="2" t="n"/>
+      <c r="BW79" s="2" t="n"/>
+      <c r="BX79" s="2" t="n"/>
+      <c r="BY79" s="2" t="n"/>
+      <c r="BZ79" s="2" t="n"/>
+      <c r="CA79" s="2" t="n"/>
+      <c r="CB79" s="2" t="n"/>
+      <c r="CC79" s="2" t="n"/>
+      <c r="CD79" s="2" t="n"/>
       <c r="CE79" s="2" t="n"/>
       <c r="CF79" s="1" t="n"/>
       <c r="CG79" s="2" t="n"/>
       <c r="CH79" s="2" t="n"/>
+      <c r="CI79" s="2" t="n"/>
+      <c r="CJ79" s="2" t="n"/>
+      <c r="CK79" s="2" t="n"/>
+      <c r="CL79" s="2" t="n"/>
+      <c r="CM79" s="2" t="n"/>
+      <c r="CN79" s="2" t="n"/>
+      <c r="CO79" s="2" t="n"/>
+      <c r="CP79" s="2" t="n"/>
+      <c r="CQ79" s="2" t="n"/>
+      <c r="CR79" s="2" t="n"/>
       <c r="CS79" s="2" t="n"/>
       <c r="CT79" s="1" t="n"/>
       <c r="CU79" s="2" t="n"/>
       <c r="CV79" s="2" t="n"/>
+      <c r="CW79" s="2" t="n"/>
+      <c r="CX79" s="2" t="n"/>
+      <c r="CY79" s="2" t="n"/>
+      <c r="CZ79" s="2" t="n"/>
+      <c r="DA79" s="2" t="n"/>
+      <c r="DB79" s="2" t="n"/>
+      <c r="DC79" s="2" t="n"/>
+      <c r="DD79" s="2" t="n"/>
+      <c r="DE79" s="2" t="n"/>
+      <c r="DF79" s="2" t="n"/>
       <c r="DG79" s="2" t="n"/>
       <c r="DH79" s="2" t="n"/>
       <c r="DI79" s="1" t="n"/>
     </row>
     <row r="80" ht="4.96" customHeight="1">
-      <c r="L80" s="6" t="n"/>
-      <c r="P80" s="6" t="n"/>
-      <c r="BK80" s="6" t="n"/>
-      <c r="BS80" s="6" t="n"/>
-      <c r="CF80" s="6" t="n"/>
-      <c r="CT80" s="6" t="n"/>
-      <c r="DI80" s="6" t="n"/>
+      <c r="L80" s="1" t="n"/>
+      <c r="M80" s="2" t="n"/>
+      <c r="N80" s="2" t="n"/>
+      <c r="O80" s="2" t="n"/>
+      <c r="P80" s="1" t="n"/>
+      <c r="Q80" s="2" t="n"/>
+      <c r="R80" s="2" t="n"/>
+      <c r="S80" s="2" t="n"/>
+      <c r="T80" s="2" t="n"/>
+      <c r="U80" s="2" t="n"/>
+      <c r="V80" s="2" t="n"/>
+      <c r="W80" s="2" t="n"/>
+      <c r="X80" s="2" t="n"/>
+      <c r="Y80" s="2" t="n"/>
+      <c r="Z80" s="2" t="n"/>
+      <c r="AA80" s="2" t="n"/>
+      <c r="AB80" s="2" t="n"/>
+      <c r="AC80" s="2" t="n"/>
+      <c r="AD80" s="2" t="n"/>
+      <c r="AE80" s="2" t="n"/>
+      <c r="AF80" s="2" t="n"/>
+      <c r="AG80" s="2" t="n"/>
+      <c r="AH80" s="2" t="n"/>
+      <c r="AI80" s="2" t="n"/>
+      <c r="AJ80" s="2" t="n"/>
+      <c r="AK80" s="2" t="n"/>
+      <c r="AL80" s="2" t="n"/>
+      <c r="AM80" s="2" t="n"/>
+      <c r="AN80" s="2" t="n"/>
+      <c r="AO80" s="2" t="n"/>
+      <c r="AP80" s="2" t="n"/>
+      <c r="AQ80" s="2" t="n"/>
+      <c r="AR80" s="2" t="n"/>
+      <c r="AS80" s="2" t="n"/>
+      <c r="AT80" s="2" t="n"/>
+      <c r="AU80" s="2" t="n"/>
+      <c r="AV80" s="2" t="n"/>
+      <c r="AW80" s="2" t="n"/>
+      <c r="AX80" s="2" t="n"/>
+      <c r="AY80" s="2" t="n"/>
+      <c r="AZ80" s="2" t="n"/>
+      <c r="BA80" s="2" t="n"/>
+      <c r="BB80" s="2" t="n"/>
+      <c r="BC80" s="2" t="n"/>
+      <c r="BD80" s="2" t="n"/>
+      <c r="BE80" s="2" t="n"/>
+      <c r="BF80" s="2" t="n"/>
+      <c r="BG80" s="2" t="n"/>
+      <c r="BH80" s="2" t="n"/>
+      <c r="BI80" s="2" t="n"/>
+      <c r="BJ80" s="2" t="n"/>
+      <c r="BK80" s="1" t="n"/>
+      <c r="BL80" s="2" t="n"/>
+      <c r="BM80" s="2" t="n"/>
+      <c r="BN80" s="2" t="n"/>
+      <c r="BO80" s="2" t="n"/>
+      <c r="BP80" s="2" t="n"/>
+      <c r="BQ80" s="2" t="n"/>
+      <c r="BR80" s="2" t="n"/>
+      <c r="BS80" s="1" t="n"/>
+      <c r="BT80" s="2" t="n"/>
+      <c r="BU80" s="2" t="n"/>
+      <c r="BV80" s="2" t="n"/>
+      <c r="BW80" s="2" t="n"/>
+      <c r="BX80" s="2" t="n"/>
+      <c r="BY80" s="2" t="n"/>
+      <c r="BZ80" s="2" t="n"/>
+      <c r="CA80" s="2" t="n"/>
+      <c r="CB80" s="2" t="n"/>
+      <c r="CC80" s="2" t="n"/>
+      <c r="CD80" s="2" t="n"/>
+      <c r="CE80" s="2" t="n"/>
+      <c r="CF80" s="1" t="n"/>
+      <c r="CG80" s="2" t="n"/>
+      <c r="CH80" s="2" t="n"/>
+      <c r="CI80" s="2" t="n"/>
+      <c r="CJ80" s="2" t="n"/>
+      <c r="CK80" s="2" t="n"/>
+      <c r="CL80" s="2" t="n"/>
+      <c r="CM80" s="2" t="n"/>
+      <c r="CN80" s="2" t="n"/>
+      <c r="CO80" s="2" t="n"/>
+      <c r="CP80" s="2" t="n"/>
+      <c r="CQ80" s="2" t="n"/>
+      <c r="CR80" s="2" t="n"/>
+      <c r="CS80" s="2" t="n"/>
+      <c r="CT80" s="1" t="n"/>
+      <c r="CU80" s="2" t="n"/>
+      <c r="CV80" s="2" t="n"/>
+      <c r="CW80" s="2" t="n"/>
+      <c r="CX80" s="2" t="n"/>
+      <c r="CY80" s="2" t="n"/>
+      <c r="CZ80" s="2" t="n"/>
+      <c r="DA80" s="2" t="n"/>
+      <c r="DB80" s="2" t="n"/>
+      <c r="DC80" s="2" t="n"/>
+      <c r="DD80" s="2" t="n"/>
+      <c r="DE80" s="2" t="n"/>
+      <c r="DF80" s="2" t="n"/>
+      <c r="DG80" s="2" t="n"/>
+      <c r="DH80" s="2" t="n"/>
+      <c r="DI80" s="1" t="n"/>
     </row>
     <row r="81" ht="4.96" customHeight="1">
-      <c r="L81" s="6" t="n"/>
-      <c r="M81" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P81" s="6" t="n"/>
-      <c r="Q81" s="12" t="inlineStr">
+      <c r="L81" s="5" t="n"/>
+      <c r="M81" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1</t>
+        </is>
+      </c>
+      <c r="P81" s="5" t="n"/>
+      <c r="Q81" s="11" t="inlineStr">
         <is>
           <t>ワークフローシステム　30ユーザーライセンス</t>
         </is>
       </c>
-      <c r="BK81" s="6" t="n"/>
-      <c r="BS81" s="6" t="n"/>
-      <c r="CF81" s="6" t="n"/>
-      <c r="CT81" s="6" t="n"/>
-      <c r="CZ81" s="12" t="inlineStr">
+      <c r="BK81" s="5" t="n"/>
+      <c r="BQ81" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BS81" s="5" t="n"/>
+      <c r="BW81" s="23" t="inlineStr">
         <is>
           <t>2,700,000</t>
         </is>
       </c>
-      <c r="DI81" s="6" t="n"/>
+      <c r="CF81" s="5" t="n"/>
+      <c r="CK81" s="23" t="inlineStr">
+        <is>
+          <t>2,700,000</t>
+        </is>
+      </c>
+      <c r="CT81" s="5" t="n"/>
+      <c r="CZ81" s="23" t="inlineStr">
+        <is>
+          <t>2,700,000</t>
+        </is>
+      </c>
+      <c r="DI81" s="5" t="n"/>
     </row>
     <row r="82" ht="4.96" customHeight="1">
-      <c r="L82" s="6" t="n"/>
-      <c r="P82" s="6" t="n"/>
-      <c r="BK82" s="6" t="n"/>
-      <c r="BS82" s="6" t="n"/>
-      <c r="CF82" s="6" t="n"/>
-      <c r="CT82" s="6" t="n"/>
-      <c r="DI82" s="6" t="n"/>
+      <c r="L82" s="5" t="n"/>
+      <c r="P82" s="5" t="n"/>
+      <c r="BK82" s="5" t="n"/>
+      <c r="BS82" s="5" t="n"/>
+      <c r="CF82" s="5" t="n"/>
+      <c r="CT82" s="5" t="n"/>
+      <c r="DI82" s="5" t="n"/>
     </row>
     <row r="83" ht="4.96" customHeight="1">
-      <c r="L83" s="6" t="n"/>
-      <c r="P83" s="6" t="n"/>
-      <c r="BK83" s="6" t="n"/>
-      <c r="BS83" s="6" t="n"/>
-      <c r="CF83" s="6" t="n"/>
-      <c r="CT83" s="6" t="n"/>
-      <c r="DI83" s="6" t="n"/>
+      <c r="L83" s="1" t="n"/>
+      <c r="M83" s="2" t="n"/>
+      <c r="N83" s="2" t="n"/>
+      <c r="O83" s="2" t="n"/>
+      <c r="P83" s="1" t="n"/>
+      <c r="Q83" s="2" t="n"/>
+      <c r="R83" s="2" t="n"/>
+      <c r="S83" s="2" t="n"/>
+      <c r="T83" s="2" t="n"/>
+      <c r="U83" s="2" t="n"/>
+      <c r="V83" s="2" t="n"/>
+      <c r="W83" s="2" t="n"/>
+      <c r="X83" s="2" t="n"/>
+      <c r="Y83" s="2" t="n"/>
+      <c r="Z83" s="2" t="n"/>
+      <c r="AA83" s="2" t="n"/>
+      <c r="AB83" s="2" t="n"/>
+      <c r="AC83" s="2" t="n"/>
+      <c r="AD83" s="2" t="n"/>
+      <c r="AE83" s="2" t="n"/>
+      <c r="AF83" s="2" t="n"/>
+      <c r="AG83" s="2" t="n"/>
+      <c r="AH83" s="2" t="n"/>
+      <c r="AI83" s="2" t="n"/>
+      <c r="AJ83" s="2" t="n"/>
+      <c r="AK83" s="2" t="n"/>
+      <c r="AL83" s="2" t="n"/>
+      <c r="AM83" s="2" t="n"/>
+      <c r="AN83" s="2" t="n"/>
+      <c r="AO83" s="2" t="n"/>
+      <c r="AP83" s="2" t="n"/>
+      <c r="AQ83" s="2" t="n"/>
+      <c r="AR83" s="2" t="n"/>
+      <c r="AS83" s="2" t="n"/>
+      <c r="AT83" s="2" t="n"/>
+      <c r="AU83" s="2" t="n"/>
+      <c r="AV83" s="2" t="n"/>
+      <c r="AW83" s="2" t="n"/>
+      <c r="AX83" s="2" t="n"/>
+      <c r="AY83" s="2" t="n"/>
+      <c r="AZ83" s="2" t="n"/>
+      <c r="BA83" s="2" t="n"/>
+      <c r="BB83" s="2" t="n"/>
+      <c r="BC83" s="2" t="n"/>
+      <c r="BD83" s="2" t="n"/>
+      <c r="BE83" s="2" t="n"/>
+      <c r="BF83" s="2" t="n"/>
+      <c r="BG83" s="2" t="n"/>
+      <c r="BH83" s="2" t="n"/>
+      <c r="BI83" s="2" t="n"/>
+      <c r="BJ83" s="2" t="n"/>
+      <c r="BK83" s="1" t="n"/>
+      <c r="BL83" s="2" t="n"/>
+      <c r="BM83" s="2" t="n"/>
+      <c r="BN83" s="2" t="n"/>
+      <c r="BO83" s="2" t="n"/>
+      <c r="BP83" s="2" t="n"/>
+      <c r="BQ83" s="2" t="n"/>
+      <c r="BR83" s="2" t="n"/>
+      <c r="BS83" s="1" t="n"/>
+      <c r="BT83" s="2" t="n"/>
+      <c r="BU83" s="2" t="n"/>
+      <c r="BV83" s="2" t="n"/>
+      <c r="BW83" s="2" t="n"/>
+      <c r="BX83" s="2" t="n"/>
+      <c r="BY83" s="2" t="n"/>
+      <c r="BZ83" s="2" t="n"/>
+      <c r="CA83" s="2" t="n"/>
+      <c r="CB83" s="2" t="n"/>
+      <c r="CC83" s="2" t="n"/>
+      <c r="CD83" s="2" t="n"/>
+      <c r="CE83" s="2" t="n"/>
+      <c r="CF83" s="1" t="n"/>
+      <c r="CG83" s="2" t="n"/>
+      <c r="CH83" s="2" t="n"/>
+      <c r="CI83" s="2" t="n"/>
+      <c r="CJ83" s="2" t="n"/>
+      <c r="CK83" s="2" t="n"/>
+      <c r="CL83" s="2" t="n"/>
+      <c r="CM83" s="2" t="n"/>
+      <c r="CN83" s="2" t="n"/>
+      <c r="CO83" s="2" t="n"/>
+      <c r="CP83" s="2" t="n"/>
+      <c r="CQ83" s="2" t="n"/>
+      <c r="CR83" s="2" t="n"/>
+      <c r="CS83" s="2" t="n"/>
+      <c r="CT83" s="1" t="n"/>
+      <c r="CU83" s="2" t="n"/>
+      <c r="CV83" s="2" t="n"/>
+      <c r="CW83" s="2" t="n"/>
+      <c r="CX83" s="2" t="n"/>
+      <c r="CY83" s="2" t="n"/>
+      <c r="CZ83" s="2" t="n"/>
+      <c r="DA83" s="2" t="n"/>
+      <c r="DB83" s="2" t="n"/>
+      <c r="DC83" s="2" t="n"/>
+      <c r="DD83" s="2" t="n"/>
+      <c r="DE83" s="2" t="n"/>
+      <c r="DF83" s="2" t="n"/>
+      <c r="DG83" s="2" t="n"/>
+      <c r="DH83" s="2" t="n"/>
+      <c r="DI83" s="1" t="n"/>
     </row>
     <row r="84" ht="4.96" customHeight="1">
-      <c r="L84" s="6" t="n"/>
-      <c r="M84" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="P84" s="6" t="n"/>
-      <c r="BK84" s="6" t="n"/>
-      <c r="BS84" s="6" t="n"/>
-      <c r="CF84" s="6" t="n"/>
-      <c r="CT84" s="6" t="n"/>
-      <c r="DI84" s="6" t="n"/>
+      <c r="L84" s="5" t="n"/>
+      <c r="M84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2</t>
+        </is>
+      </c>
+      <c r="P84" s="5" t="n"/>
+      <c r="Q84" s="11" t="inlineStr">
+        <is>
+          <t>初期設定費用</t>
+        </is>
+      </c>
+      <c r="BK84" s="5" t="n"/>
+      <c r="BQ84" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BS84" s="5" t="n"/>
+      <c r="BY84" s="23" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
+      <c r="CF84" s="5" t="n"/>
+      <c r="CM84" s="23" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
+      <c r="CT84" s="5" t="n"/>
+      <c r="DB84" s="23" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
+      <c r="DI84" s="5" t="n"/>
     </row>
     <row r="85" ht="4.96" customHeight="1">
-      <c r="L85" s="6" t="n"/>
-      <c r="P85" s="6" t="n"/>
-      <c r="BK85" s="6" t="n"/>
-      <c r="BS85" s="6" t="n"/>
-      <c r="CF85" s="6" t="n"/>
-      <c r="CT85" s="6" t="n"/>
-      <c r="DI85" s="6" t="n"/>
+      <c r="L85" s="5" t="n"/>
+      <c r="P85" s="5" t="n"/>
+      <c r="BK85" s="5" t="n"/>
+      <c r="BS85" s="5" t="n"/>
+      <c r="CF85" s="5" t="n"/>
+      <c r="CT85" s="5" t="n"/>
+      <c r="DI85" s="5" t="n"/>
     </row>
     <row r="86" ht="4.96" customHeight="1">
-      <c r="L86" s="6" t="n"/>
-      <c r="P86" s="6" t="n"/>
-      <c r="BK86" s="6" t="n"/>
-      <c r="BS86" s="6" t="n"/>
-      <c r="CF86" s="6" t="n"/>
-      <c r="CT86" s="6" t="n"/>
-      <c r="DI86" s="6" t="n"/>
+      <c r="L86" s="5" t="n"/>
+      <c r="P86" s="5" t="n"/>
+      <c r="BK86" s="5" t="n"/>
+      <c r="BS86" s="5" t="n"/>
+      <c r="CF86" s="5" t="n"/>
+      <c r="CT86" s="5" t="n"/>
+      <c r="DI86" s="5" t="n"/>
     </row>
     <row r="87" ht="4.96" customHeight="1">
-      <c r="L87" s="6" t="n"/>
-      <c r="M87" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="P87" s="6" t="n"/>
-      <c r="BK87" s="6" t="n"/>
-      <c r="BS87" s="6" t="n"/>
-      <c r="CF87" s="6" t="n"/>
-      <c r="CT87" s="6" t="n"/>
-      <c r="DI87" s="6" t="n"/>
+      <c r="L87" s="1" t="n"/>
+      <c r="M87" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 3</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="n"/>
+      <c r="O87" s="2" t="n"/>
+      <c r="P87" s="1" t="n"/>
+      <c r="Q87" s="25" t="inlineStr">
+        <is>
+          <t>管理者費用</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="n"/>
+      <c r="S87" s="2" t="n"/>
+      <c r="T87" s="2" t="n"/>
+      <c r="U87" s="2" t="n"/>
+      <c r="V87" s="2" t="n"/>
+      <c r="W87" s="2" t="n"/>
+      <c r="X87" s="2" t="n"/>
+      <c r="Y87" s="2" t="n"/>
+      <c r="Z87" s="2" t="n"/>
+      <c r="AA87" s="2" t="n"/>
+      <c r="AB87" s="2" t="n"/>
+      <c r="AC87" s="2" t="n"/>
+      <c r="AD87" s="2" t="n"/>
+      <c r="AE87" s="2" t="n"/>
+      <c r="AF87" s="2" t="n"/>
+      <c r="AG87" s="2" t="n"/>
+      <c r="AH87" s="2" t="n"/>
+      <c r="AI87" s="2" t="n"/>
+      <c r="AJ87" s="2" t="n"/>
+      <c r="AK87" s="2" t="n"/>
+      <c r="AL87" s="2" t="n"/>
+      <c r="AM87" s="2" t="n"/>
+      <c r="AN87" s="2" t="n"/>
+      <c r="AO87" s="2" t="n"/>
+      <c r="AP87" s="2" t="n"/>
+      <c r="AQ87" s="2" t="n"/>
+      <c r="AR87" s="2" t="n"/>
+      <c r="AS87" s="2" t="n"/>
+      <c r="AT87" s="2" t="n"/>
+      <c r="AU87" s="2" t="n"/>
+      <c r="AV87" s="2" t="n"/>
+      <c r="AW87" s="2" t="n"/>
+      <c r="AX87" s="2" t="n"/>
+      <c r="AY87" s="2" t="n"/>
+      <c r="AZ87" s="2" t="n"/>
+      <c r="BA87" s="2" t="n"/>
+      <c r="BB87" s="2" t="n"/>
+      <c r="BC87" s="2" t="n"/>
+      <c r="BD87" s="2" t="n"/>
+      <c r="BE87" s="2" t="n"/>
+      <c r="BF87" s="2" t="n"/>
+      <c r="BG87" s="2" t="n"/>
+      <c r="BH87" s="2" t="n"/>
+      <c r="BI87" s="2" t="n"/>
+      <c r="BJ87" s="2" t="n"/>
+      <c r="BK87" s="1" t="n"/>
+      <c r="BL87" s="2" t="n"/>
+      <c r="BM87" s="2" t="n"/>
+      <c r="BN87" s="2" t="n"/>
+      <c r="BO87" s="2" t="n"/>
+      <c r="BP87" s="2" t="n"/>
+      <c r="BQ87" s="26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BR87" s="2" t="n"/>
+      <c r="BS87" s="1" t="n"/>
+      <c r="BT87" s="2" t="n"/>
+      <c r="BU87" s="2" t="n"/>
+      <c r="BV87" s="2" t="n"/>
+      <c r="BW87" s="2" t="n"/>
+      <c r="BX87" s="2" t="n"/>
+      <c r="BY87" s="26" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
+      <c r="BZ87" s="2" t="n"/>
+      <c r="CA87" s="2" t="n"/>
+      <c r="CB87" s="2" t="n"/>
+      <c r="CC87" s="2" t="n"/>
+      <c r="CD87" s="2" t="n"/>
+      <c r="CE87" s="2" t="n"/>
+      <c r="CF87" s="1" t="n"/>
+      <c r="CG87" s="2" t="n"/>
+      <c r="CH87" s="2" t="n"/>
+      <c r="CI87" s="2" t="n"/>
+      <c r="CJ87" s="2" t="n"/>
+      <c r="CK87" s="2" t="n"/>
+      <c r="CL87" s="2" t="n"/>
+      <c r="CM87" s="26" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
+      <c r="CN87" s="2" t="n"/>
+      <c r="CO87" s="2" t="n"/>
+      <c r="CP87" s="2" t="n"/>
+      <c r="CQ87" s="2" t="n"/>
+      <c r="CR87" s="2" t="n"/>
+      <c r="CS87" s="2" t="n"/>
+      <c r="CT87" s="1" t="n"/>
+      <c r="CU87" s="2" t="n"/>
+      <c r="CV87" s="2" t="n"/>
+      <c r="CW87" s="2" t="n"/>
+      <c r="CX87" s="2" t="n"/>
+      <c r="CY87" s="2" t="n"/>
+      <c r="CZ87" s="2" t="n"/>
+      <c r="DA87" s="2" t="n"/>
+      <c r="DB87" s="26" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
+      <c r="DC87" s="2" t="n"/>
+      <c r="DD87" s="2" t="n"/>
+      <c r="DE87" s="2" t="n"/>
+      <c r="DF87" s="2" t="n"/>
+      <c r="DG87" s="2" t="n"/>
+      <c r="DH87" s="2" t="n"/>
+      <c r="DI87" s="1" t="n"/>
     </row>
     <row r="88" ht="4.96" customHeight="1">
-      <c r="L88" s="6" t="n"/>
-      <c r="P88" s="6" t="n"/>
-      <c r="BK88" s="6" t="n"/>
-      <c r="BS88" s="6" t="n"/>
-      <c r="CF88" s="6" t="n"/>
-      <c r="CT88" s="6" t="n"/>
-      <c r="DI88" s="6" t="n"/>
+      <c r="L88" s="5" t="n"/>
+      <c r="P88" s="5" t="n"/>
+      <c r="BK88" s="5" t="n"/>
+      <c r="BS88" s="5" t="n"/>
+      <c r="CF88" s="5" t="n"/>
+      <c r="CT88" s="5" t="n"/>
+      <c r="DI88" s="5" t="n"/>
     </row>
     <row r="89" ht="4.96" customHeight="1">
-      <c r="L89" s="6" t="n"/>
-      <c r="P89" s="6" t="n"/>
-      <c r="BK89" s="6" t="n"/>
-      <c r="BS89" s="6" t="n"/>
-      <c r="CF89" s="6" t="n"/>
-      <c r="CT89" s="6" t="n"/>
-      <c r="DI89" s="6" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
+      <c r="BK89" s="5" t="n"/>
+      <c r="BS89" s="5" t="n"/>
+      <c r="CF89" s="5" t="n"/>
+      <c r="CT89" s="5" t="n"/>
+      <c r="DI89" s="5" t="n"/>
     </row>
     <row r="90" ht="4.96" customHeight="1">
-      <c r="L90" s="6" t="n"/>
-      <c r="P90" s="6" t="n"/>
-      <c r="BK90" s="6" t="n"/>
-      <c r="BS90" s="6" t="n"/>
-      <c r="CF90" s="6" t="n"/>
-      <c r="CT90" s="6" t="n"/>
-      <c r="DI90" s="6" t="n"/>
+      <c r="L90" s="1" t="n"/>
+      <c r="M90" s="2" t="n"/>
+      <c r="N90" s="2" t="n"/>
+      <c r="O90" s="2" t="n"/>
+      <c r="P90" s="1" t="n"/>
+      <c r="Q90" s="2" t="n"/>
+      <c r="R90" s="2" t="n"/>
+      <c r="S90" s="2" t="n"/>
+      <c r="T90" s="2" t="n"/>
+      <c r="U90" s="2" t="n"/>
+      <c r="V90" s="2" t="n"/>
+      <c r="W90" s="2" t="n"/>
+      <c r="X90" s="2" t="n"/>
+      <c r="Y90" s="2" t="n"/>
+      <c r="Z90" s="2" t="n"/>
+      <c r="AA90" s="2" t="n"/>
+      <c r="AB90" s="2" t="n"/>
+      <c r="AC90" s="2" t="n"/>
+      <c r="AD90" s="2" t="n"/>
+      <c r="AE90" s="2" t="n"/>
+      <c r="AF90" s="2" t="n"/>
+      <c r="AG90" s="2" t="n"/>
+      <c r="AH90" s="2" t="n"/>
+      <c r="AI90" s="2" t="n"/>
+      <c r="AJ90" s="2" t="n"/>
+      <c r="AK90" s="2" t="n"/>
+      <c r="AL90" s="2" t="n"/>
+      <c r="AM90" s="2" t="n"/>
+      <c r="AN90" s="2" t="n"/>
+      <c r="AO90" s="2" t="n"/>
+      <c r="AP90" s="2" t="n"/>
+      <c r="AQ90" s="2" t="n"/>
+      <c r="AR90" s="2" t="n"/>
+      <c r="AS90" s="2" t="n"/>
+      <c r="AT90" s="2" t="n"/>
+      <c r="AU90" s="2" t="n"/>
+      <c r="AV90" s="2" t="n"/>
+      <c r="AW90" s="2" t="n"/>
+      <c r="AX90" s="2" t="n"/>
+      <c r="AY90" s="2" t="n"/>
+      <c r="AZ90" s="2" t="n"/>
+      <c r="BA90" s="2" t="n"/>
+      <c r="BB90" s="2" t="n"/>
+      <c r="BC90" s="2" t="n"/>
+      <c r="BD90" s="2" t="n"/>
+      <c r="BE90" s="2" t="n"/>
+      <c r="BF90" s="2" t="n"/>
+      <c r="BG90" s="2" t="n"/>
+      <c r="BH90" s="2" t="n"/>
+      <c r="BI90" s="2" t="n"/>
+      <c r="BJ90" s="2" t="n"/>
+      <c r="BK90" s="1" t="n"/>
+      <c r="BL90" s="2" t="n"/>
+      <c r="BM90" s="2" t="n"/>
+      <c r="BN90" s="2" t="n"/>
+      <c r="BO90" s="2" t="n"/>
+      <c r="BP90" s="2" t="n"/>
+      <c r="BQ90" s="2" t="n"/>
+      <c r="BR90" s="2" t="n"/>
+      <c r="BS90" s="1" t="n"/>
+      <c r="BT90" s="2" t="n"/>
+      <c r="BU90" s="2" t="n"/>
+      <c r="BV90" s="2" t="n"/>
+      <c r="BW90" s="2" t="n"/>
+      <c r="BX90" s="2" t="n"/>
+      <c r="BY90" s="2" t="n"/>
+      <c r="BZ90" s="2" t="n"/>
+      <c r="CA90" s="2" t="n"/>
+      <c r="CB90" s="2" t="n"/>
+      <c r="CC90" s="2" t="n"/>
+      <c r="CD90" s="2" t="n"/>
+      <c r="CE90" s="2" t="n"/>
+      <c r="CF90" s="1" t="n"/>
+      <c r="CG90" s="2" t="n"/>
+      <c r="CH90" s="2" t="n"/>
+      <c r="CI90" s="2" t="n"/>
+      <c r="CJ90" s="2" t="n"/>
+      <c r="CK90" s="2" t="n"/>
+      <c r="CL90" s="2" t="n"/>
+      <c r="CM90" s="2" t="n"/>
+      <c r="CN90" s="2" t="n"/>
+      <c r="CO90" s="2" t="n"/>
+      <c r="CP90" s="2" t="n"/>
+      <c r="CQ90" s="2" t="n"/>
+      <c r="CR90" s="2" t="n"/>
+      <c r="CS90" s="2" t="n"/>
+      <c r="CT90" s="1" t="n"/>
+      <c r="CU90" s="2" t="n"/>
+      <c r="CV90" s="2" t="n"/>
+      <c r="CW90" s="2" t="n"/>
+      <c r="CX90" s="2" t="n"/>
+      <c r="CY90" s="2" t="n"/>
+      <c r="CZ90" s="2" t="n"/>
+      <c r="DA90" s="2" t="n"/>
+      <c r="DB90" s="2" t="n"/>
+      <c r="DC90" s="2" t="n"/>
+      <c r="DD90" s="2" t="n"/>
+      <c r="DE90" s="2" t="n"/>
+      <c r="DF90" s="2" t="n"/>
+      <c r="DG90" s="2" t="n"/>
+      <c r="DH90" s="2" t="n"/>
+      <c r="DI90" s="1" t="n"/>
     </row>
     <row r="91" ht="4.96" customHeight="1">
-      <c r="L91" s="6" t="n"/>
-      <c r="M91" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="P91" s="6" t="n"/>
-      <c r="BK91" s="6" t="n"/>
-      <c r="BS91" s="6" t="n"/>
-      <c r="CF91" s="6" t="n"/>
-      <c r="CT91" s="6" t="n"/>
-      <c r="DI91" s="6" t="n"/>
+      <c r="L91" s="5" t="n"/>
+      <c r="M91" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 4</t>
+        </is>
+      </c>
+      <c r="P91" s="5" t="n"/>
+      <c r="BK91" s="5" t="n"/>
+      <c r="BS91" s="5" t="n"/>
+      <c r="CF91" s="5" t="n"/>
+      <c r="CT91" s="5" t="n"/>
+      <c r="DI91" s="5" t="n"/>
     </row>
     <row r="92" ht="4.96" customHeight="1">
-      <c r="L92" s="6" t="n"/>
-      <c r="P92" s="6" t="n"/>
-      <c r="BK92" s="6" t="n"/>
-      <c r="BS92" s="6" t="n"/>
-      <c r="CF92" s="6" t="n"/>
-      <c r="CT92" s="6" t="n"/>
-      <c r="DI92" s="6" t="n"/>
+      <c r="L92" s="5" t="n"/>
+      <c r="P92" s="5" t="n"/>
+      <c r="BK92" s="5" t="n"/>
+      <c r="BS92" s="5" t="n"/>
+      <c r="CF92" s="5" t="n"/>
+      <c r="CT92" s="5" t="n"/>
+      <c r="DI92" s="5" t="n"/>
     </row>
     <row r="93" ht="4.96" customHeight="1">
-      <c r="L93" s="6" t="n"/>
-      <c r="P93" s="6" t="n"/>
-      <c r="BK93" s="6" t="n"/>
-      <c r="BS93" s="6" t="n"/>
-      <c r="CF93" s="6" t="n"/>
-      <c r="CT93" s="6" t="n"/>
-      <c r="DI93" s="6" t="n"/>
+      <c r="L93" s="1" t="n"/>
+      <c r="M93" s="2" t="n"/>
+      <c r="N93" s="2" t="n"/>
+      <c r="O93" s="2" t="n"/>
+      <c r="P93" s="1" t="n"/>
+      <c r="Q93" s="2" t="n"/>
+      <c r="R93" s="2" t="n"/>
+      <c r="S93" s="2" t="n"/>
+      <c r="T93" s="2" t="n"/>
+      <c r="U93" s="2" t="n"/>
+      <c r="V93" s="2" t="n"/>
+      <c r="W93" s="2" t="n"/>
+      <c r="X93" s="2" t="n"/>
+      <c r="Y93" s="2" t="n"/>
+      <c r="Z93" s="2" t="n"/>
+      <c r="AA93" s="2" t="n"/>
+      <c r="AB93" s="2" t="n"/>
+      <c r="AC93" s="2" t="n"/>
+      <c r="AD93" s="2" t="n"/>
+      <c r="AE93" s="2" t="n"/>
+      <c r="AF93" s="2" t="n"/>
+      <c r="AG93" s="2" t="n"/>
+      <c r="AH93" s="2" t="n"/>
+      <c r="AI93" s="2" t="n"/>
+      <c r="AJ93" s="2" t="n"/>
+      <c r="AK93" s="2" t="n"/>
+      <c r="AL93" s="2" t="n"/>
+      <c r="AM93" s="2" t="n"/>
+      <c r="AN93" s="2" t="n"/>
+      <c r="AO93" s="2" t="n"/>
+      <c r="AP93" s="2" t="n"/>
+      <c r="AQ93" s="2" t="n"/>
+      <c r="AR93" s="2" t="n"/>
+      <c r="AS93" s="2" t="n"/>
+      <c r="AT93" s="2" t="n"/>
+      <c r="AU93" s="2" t="n"/>
+      <c r="AV93" s="2" t="n"/>
+      <c r="AW93" s="2" t="n"/>
+      <c r="AX93" s="2" t="n"/>
+      <c r="AY93" s="2" t="n"/>
+      <c r="AZ93" s="2" t="n"/>
+      <c r="BA93" s="2" t="n"/>
+      <c r="BB93" s="2" t="n"/>
+      <c r="BC93" s="2" t="n"/>
+      <c r="BD93" s="2" t="n"/>
+      <c r="BE93" s="2" t="n"/>
+      <c r="BF93" s="2" t="n"/>
+      <c r="BG93" s="2" t="n"/>
+      <c r="BH93" s="2" t="n"/>
+      <c r="BI93" s="2" t="n"/>
+      <c r="BJ93" s="2" t="n"/>
+      <c r="BK93" s="1" t="n"/>
+      <c r="BL93" s="2" t="n"/>
+      <c r="BM93" s="2" t="n"/>
+      <c r="BN93" s="2" t="n"/>
+      <c r="BO93" s="2" t="n"/>
+      <c r="BP93" s="2" t="n"/>
+      <c r="BQ93" s="2" t="n"/>
+      <c r="BR93" s="2" t="n"/>
+      <c r="BS93" s="1" t="n"/>
+      <c r="BT93" s="2" t="n"/>
+      <c r="BU93" s="2" t="n"/>
+      <c r="BV93" s="2" t="n"/>
+      <c r="BW93" s="2" t="n"/>
+      <c r="BX93" s="2" t="n"/>
+      <c r="BY93" s="2" t="n"/>
+      <c r="BZ93" s="2" t="n"/>
+      <c r="CA93" s="2" t="n"/>
+      <c r="CB93" s="2" t="n"/>
+      <c r="CC93" s="2" t="n"/>
+      <c r="CD93" s="2" t="n"/>
+      <c r="CE93" s="2" t="n"/>
+      <c r="CF93" s="1" t="n"/>
+      <c r="CG93" s="2" t="n"/>
+      <c r="CH93" s="2" t="n"/>
+      <c r="CI93" s="2" t="n"/>
+      <c r="CJ93" s="2" t="n"/>
+      <c r="CK93" s="2" t="n"/>
+      <c r="CL93" s="2" t="n"/>
+      <c r="CM93" s="2" t="n"/>
+      <c r="CN93" s="2" t="n"/>
+      <c r="CO93" s="2" t="n"/>
+      <c r="CP93" s="2" t="n"/>
+      <c r="CQ93" s="2" t="n"/>
+      <c r="CR93" s="2" t="n"/>
+      <c r="CS93" s="2" t="n"/>
+      <c r="CT93" s="1" t="n"/>
+      <c r="CU93" s="2" t="n"/>
+      <c r="CV93" s="2" t="n"/>
+      <c r="CW93" s="2" t="n"/>
+      <c r="CX93" s="2" t="n"/>
+      <c r="CY93" s="2" t="n"/>
+      <c r="CZ93" s="2" t="n"/>
+      <c r="DA93" s="2" t="n"/>
+      <c r="DB93" s="2" t="n"/>
+      <c r="DC93" s="2" t="n"/>
+      <c r="DD93" s="2" t="n"/>
+      <c r="DE93" s="2" t="n"/>
+      <c r="DF93" s="2" t="n"/>
+      <c r="DG93" s="2" t="n"/>
+      <c r="DH93" s="2" t="n"/>
+      <c r="DI93" s="1" t="n"/>
     </row>
     <row r="94" ht="4.96" customHeight="1">
-      <c r="L94" s="6" t="n"/>
-      <c r="M94" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="P94" s="6" t="n"/>
-      <c r="BK94" s="6" t="n"/>
-      <c r="BS94" s="6" t="n"/>
-      <c r="CF94" s="6" t="n"/>
-      <c r="CT94" s="6" t="n"/>
-      <c r="DI94" s="6" t="n"/>
+      <c r="L94" s="5" t="n"/>
+      <c r="M94" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 5</t>
+        </is>
+      </c>
+      <c r="P94" s="5" t="n"/>
+      <c r="BK94" s="5" t="n"/>
+      <c r="BS94" s="5" t="n"/>
+      <c r="CF94" s="5" t="n"/>
+      <c r="CT94" s="5" t="n"/>
+      <c r="DI94" s="5" t="n"/>
     </row>
     <row r="95" ht="4.96" customHeight="1">
-      <c r="L95" s="6" t="n"/>
-      <c r="P95" s="6" t="n"/>
-      <c r="BK95" s="6" t="n"/>
-      <c r="BS95" s="6" t="n"/>
-      <c r="CF95" s="6" t="n"/>
-      <c r="CT95" s="6" t="n"/>
-      <c r="DI95" s="6" t="n"/>
+      <c r="L95" s="5" t="n"/>
+      <c r="P95" s="5" t="n"/>
+      <c r="BK95" s="5" t="n"/>
+      <c r="BS95" s="5" t="n"/>
+      <c r="CF95" s="5" t="n"/>
+      <c r="CT95" s="5" t="n"/>
+      <c r="DI95" s="5" t="n"/>
     </row>
     <row r="96" ht="4.96" customHeight="1">
-      <c r="L96" s="6" t="n"/>
-      <c r="P96" s="6" t="n"/>
-      <c r="BK96" s="6" t="n"/>
-      <c r="BS96" s="6" t="n"/>
-      <c r="CF96" s="6" t="n"/>
-      <c r="CT96" s="6" t="n"/>
-      <c r="DI96" s="6" t="n"/>
+      <c r="L96" s="5" t="n"/>
+      <c r="P96" s="5" t="n"/>
+      <c r="BK96" s="5" t="n"/>
+      <c r="BS96" s="5" t="n"/>
+      <c r="CF96" s="5" t="n"/>
+      <c r="CT96" s="5" t="n"/>
+      <c r="DI96" s="5" t="n"/>
     </row>
     <row r="97" ht="4.96" customHeight="1">
-      <c r="L97" s="6" t="n"/>
-      <c r="P97" s="6" t="n"/>
-      <c r="BK97" s="6" t="n"/>
-      <c r="BS97" s="6" t="n"/>
-      <c r="CF97" s="6" t="n"/>
-      <c r="CT97" s="6" t="n"/>
-      <c r="DI97" s="6" t="n"/>
+      <c r="L97" s="1" t="n"/>
+      <c r="M97" s="2" t="n"/>
+      <c r="N97" s="2" t="n"/>
+      <c r="O97" s="2" t="n"/>
+      <c r="P97" s="1" t="n"/>
+      <c r="Q97" s="2" t="n"/>
+      <c r="R97" s="2" t="n"/>
+      <c r="S97" s="2" t="n"/>
+      <c r="T97" s="2" t="n"/>
+      <c r="U97" s="2" t="n"/>
+      <c r="V97" s="2" t="n"/>
+      <c r="W97" s="2" t="n"/>
+      <c r="X97" s="2" t="n"/>
+      <c r="Y97" s="2" t="n"/>
+      <c r="Z97" s="2" t="n"/>
+      <c r="AA97" s="2" t="n"/>
+      <c r="AB97" s="2" t="n"/>
+      <c r="AC97" s="2" t="n"/>
+      <c r="AD97" s="2" t="n"/>
+      <c r="AE97" s="2" t="n"/>
+      <c r="AF97" s="2" t="n"/>
+      <c r="AG97" s="2" t="n"/>
+      <c r="AH97" s="2" t="n"/>
+      <c r="AI97" s="2" t="n"/>
+      <c r="AJ97" s="2" t="n"/>
+      <c r="AK97" s="2" t="n"/>
+      <c r="AL97" s="2" t="n"/>
+      <c r="AM97" s="2" t="n"/>
+      <c r="AN97" s="2" t="n"/>
+      <c r="AO97" s="2" t="n"/>
+      <c r="AP97" s="2" t="n"/>
+      <c r="AQ97" s="2" t="n"/>
+      <c r="AR97" s="2" t="n"/>
+      <c r="AS97" s="2" t="n"/>
+      <c r="AT97" s="2" t="n"/>
+      <c r="AU97" s="2" t="n"/>
+      <c r="AV97" s="2" t="n"/>
+      <c r="AW97" s="2" t="n"/>
+      <c r="AX97" s="2" t="n"/>
+      <c r="AY97" s="2" t="n"/>
+      <c r="AZ97" s="2" t="n"/>
+      <c r="BA97" s="2" t="n"/>
+      <c r="BB97" s="2" t="n"/>
+      <c r="BC97" s="2" t="n"/>
+      <c r="BD97" s="2" t="n"/>
+      <c r="BE97" s="2" t="n"/>
+      <c r="BF97" s="2" t="n"/>
+      <c r="BG97" s="2" t="n"/>
+      <c r="BH97" s="2" t="n"/>
+      <c r="BI97" s="2" t="n"/>
+      <c r="BJ97" s="2" t="n"/>
+      <c r="BK97" s="1" t="n"/>
+      <c r="BL97" s="2" t="n"/>
+      <c r="BM97" s="2" t="n"/>
+      <c r="BN97" s="2" t="n"/>
+      <c r="BO97" s="2" t="n"/>
+      <c r="BP97" s="2" t="n"/>
+      <c r="BQ97" s="2" t="n"/>
+      <c r="BR97" s="2" t="n"/>
+      <c r="BS97" s="1" t="n"/>
+      <c r="BT97" s="2" t="n"/>
+      <c r="BU97" s="2" t="n"/>
+      <c r="BV97" s="2" t="n"/>
+      <c r="BW97" s="2" t="n"/>
+      <c r="BX97" s="2" t="n"/>
+      <c r="BY97" s="2" t="n"/>
+      <c r="BZ97" s="2" t="n"/>
+      <c r="CA97" s="2" t="n"/>
+      <c r="CB97" s="2" t="n"/>
+      <c r="CC97" s="2" t="n"/>
+      <c r="CD97" s="2" t="n"/>
+      <c r="CE97" s="2" t="n"/>
+      <c r="CF97" s="1" t="n"/>
+      <c r="CG97" s="2" t="n"/>
+      <c r="CH97" s="2" t="n"/>
+      <c r="CI97" s="2" t="n"/>
+      <c r="CJ97" s="2" t="n"/>
+      <c r="CK97" s="2" t="n"/>
+      <c r="CL97" s="2" t="n"/>
+      <c r="CM97" s="2" t="n"/>
+      <c r="CN97" s="2" t="n"/>
+      <c r="CO97" s="2" t="n"/>
+      <c r="CP97" s="2" t="n"/>
+      <c r="CQ97" s="2" t="n"/>
+      <c r="CR97" s="2" t="n"/>
+      <c r="CS97" s="2" t="n"/>
+      <c r="CT97" s="1" t="n"/>
+      <c r="CU97" s="2" t="n"/>
+      <c r="CV97" s="2" t="n"/>
+      <c r="CW97" s="2" t="n"/>
+      <c r="CX97" s="2" t="n"/>
+      <c r="CY97" s="2" t="n"/>
+      <c r="CZ97" s="2" t="n"/>
+      <c r="DA97" s="2" t="n"/>
+      <c r="DB97" s="2" t="n"/>
+      <c r="DC97" s="2" t="n"/>
+      <c r="DD97" s="2" t="n"/>
+      <c r="DE97" s="2" t="n"/>
+      <c r="DF97" s="2" t="n"/>
+      <c r="DG97" s="2" t="n"/>
+      <c r="DH97" s="2" t="n"/>
+      <c r="DI97" s="1" t="n"/>
     </row>
     <row r="98" ht="4.96" customHeight="1">
-      <c r="L98" s="6" t="n"/>
-      <c r="M98" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="P98" s="6" t="n"/>
-      <c r="BK98" s="6" t="n"/>
-      <c r="BS98" s="6" t="n"/>
-      <c r="CF98" s="6" t="n"/>
-      <c r="CT98" s="6" t="n"/>
-      <c r="DI98" s="6" t="n"/>
+      <c r="L98" s="5" t="n"/>
+      <c r="M98" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 6</t>
+        </is>
+      </c>
+      <c r="P98" s="5" t="n"/>
+      <c r="BK98" s="5" t="n"/>
+      <c r="BS98" s="5" t="n"/>
+      <c r="CF98" s="5" t="n"/>
+      <c r="CT98" s="5" t="n"/>
+      <c r="DI98" s="5" t="n"/>
     </row>
     <row r="99" ht="4.96" customHeight="1">
-      <c r="L99" s="6" t="n"/>
-      <c r="P99" s="6" t="n"/>
-      <c r="BK99" s="6" t="n"/>
-      <c r="BS99" s="6" t="n"/>
-      <c r="CF99" s="6" t="n"/>
-      <c r="CT99" s="6" t="n"/>
-      <c r="DI99" s="6" t="n"/>
+      <c r="L99" s="5" t="n"/>
+      <c r="P99" s="5" t="n"/>
+      <c r="BK99" s="5" t="n"/>
+      <c r="BS99" s="5" t="n"/>
+      <c r="CF99" s="5" t="n"/>
+      <c r="CT99" s="5" t="n"/>
+      <c r="DI99" s="5" t="n"/>
     </row>
     <row r="100" ht="4.96" customHeight="1">
-      <c r="L100" s="6" t="n"/>
-      <c r="P100" s="6" t="n"/>
-      <c r="BK100" s="6" t="n"/>
-      <c r="BS100" s="6" t="n"/>
-      <c r="CF100" s="6" t="n"/>
-      <c r="CT100" s="6" t="n"/>
-      <c r="DI100" s="6" t="n"/>
+      <c r="L100" s="1" t="n"/>
+      <c r="M100" s="2" t="n"/>
+      <c r="N100" s="2" t="n"/>
+      <c r="O100" s="2" t="n"/>
+      <c r="P100" s="1" t="n"/>
+      <c r="Q100" s="2" t="n"/>
+      <c r="R100" s="2" t="n"/>
+      <c r="S100" s="2" t="n"/>
+      <c r="T100" s="2" t="n"/>
+      <c r="U100" s="2" t="n"/>
+      <c r="V100" s="2" t="n"/>
+      <c r="W100" s="2" t="n"/>
+      <c r="X100" s="2" t="n"/>
+      <c r="Y100" s="2" t="n"/>
+      <c r="Z100" s="2" t="n"/>
+      <c r="AA100" s="2" t="n"/>
+      <c r="AB100" s="2" t="n"/>
+      <c r="AC100" s="2" t="n"/>
+      <c r="AD100" s="2" t="n"/>
+      <c r="AE100" s="2" t="n"/>
+      <c r="AF100" s="2" t="n"/>
+      <c r="AG100" s="2" t="n"/>
+      <c r="AH100" s="2" t="n"/>
+      <c r="AI100" s="2" t="n"/>
+      <c r="AJ100" s="2" t="n"/>
+      <c r="AK100" s="2" t="n"/>
+      <c r="AL100" s="2" t="n"/>
+      <c r="AM100" s="2" t="n"/>
+      <c r="AN100" s="2" t="n"/>
+      <c r="AO100" s="2" t="n"/>
+      <c r="AP100" s="2" t="n"/>
+      <c r="AQ100" s="2" t="n"/>
+      <c r="AR100" s="2" t="n"/>
+      <c r="AS100" s="2" t="n"/>
+      <c r="AT100" s="2" t="n"/>
+      <c r="AU100" s="2" t="n"/>
+      <c r="AV100" s="2" t="n"/>
+      <c r="AW100" s="2" t="n"/>
+      <c r="AX100" s="2" t="n"/>
+      <c r="AY100" s="2" t="n"/>
+      <c r="AZ100" s="2" t="n"/>
+      <c r="BA100" s="2" t="n"/>
+      <c r="BB100" s="2" t="n"/>
+      <c r="BC100" s="2" t="n"/>
+      <c r="BD100" s="2" t="n"/>
+      <c r="BE100" s="2" t="n"/>
+      <c r="BF100" s="2" t="n"/>
+      <c r="BG100" s="2" t="n"/>
+      <c r="BH100" s="2" t="n"/>
+      <c r="BI100" s="2" t="n"/>
+      <c r="BJ100" s="2" t="n"/>
+      <c r="BK100" s="1" t="n"/>
+      <c r="BL100" s="2" t="n"/>
+      <c r="BM100" s="2" t="n"/>
+      <c r="BN100" s="2" t="n"/>
+      <c r="BO100" s="2" t="n"/>
+      <c r="BP100" s="2" t="n"/>
+      <c r="BQ100" s="2" t="n"/>
+      <c r="BR100" s="2" t="n"/>
+      <c r="BS100" s="1" t="n"/>
+      <c r="BT100" s="2" t="n"/>
+      <c r="BU100" s="2" t="n"/>
+      <c r="BV100" s="2" t="n"/>
+      <c r="BW100" s="2" t="n"/>
+      <c r="BX100" s="2" t="n"/>
+      <c r="BY100" s="2" t="n"/>
+      <c r="BZ100" s="2" t="n"/>
+      <c r="CA100" s="2" t="n"/>
+      <c r="CB100" s="2" t="n"/>
+      <c r="CC100" s="2" t="n"/>
+      <c r="CD100" s="2" t="n"/>
+      <c r="CE100" s="2" t="n"/>
+      <c r="CF100" s="1" t="n"/>
+      <c r="CG100" s="2" t="n"/>
+      <c r="CH100" s="2" t="n"/>
+      <c r="CI100" s="2" t="n"/>
+      <c r="CJ100" s="2" t="n"/>
+      <c r="CK100" s="2" t="n"/>
+      <c r="CL100" s="2" t="n"/>
+      <c r="CM100" s="2" t="n"/>
+      <c r="CN100" s="2" t="n"/>
+      <c r="CO100" s="2" t="n"/>
+      <c r="CP100" s="2" t="n"/>
+      <c r="CQ100" s="2" t="n"/>
+      <c r="CR100" s="2" t="n"/>
+      <c r="CS100" s="2" t="n"/>
+      <c r="CT100" s="1" t="n"/>
+      <c r="CU100" s="2" t="n"/>
+      <c r="CV100" s="2" t="n"/>
+      <c r="CW100" s="2" t="n"/>
+      <c r="CX100" s="2" t="n"/>
+      <c r="CY100" s="2" t="n"/>
+      <c r="CZ100" s="2" t="n"/>
+      <c r="DA100" s="2" t="n"/>
+      <c r="DB100" s="2" t="n"/>
+      <c r="DC100" s="2" t="n"/>
+      <c r="DD100" s="2" t="n"/>
+      <c r="DE100" s="2" t="n"/>
+      <c r="DF100" s="2" t="n"/>
+      <c r="DG100" s="2" t="n"/>
+      <c r="DH100" s="2" t="n"/>
+      <c r="DI100" s="1" t="n"/>
     </row>
     <row r="101" ht="4.96" customHeight="1">
-      <c r="L101" s="6" t="n"/>
-      <c r="M101" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="P101" s="6" t="n"/>
-      <c r="BK101" s="6" t="n"/>
-      <c r="BS101" s="6" t="n"/>
-      <c r="CF101" s="6" t="n"/>
-      <c r="CT101" s="6" t="n"/>
-      <c r="DI101" s="6" t="n"/>
+      <c r="L101" s="5" t="n"/>
+      <c r="M101" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 7</t>
+        </is>
+      </c>
+      <c r="P101" s="5" t="n"/>
+      <c r="BK101" s="5" t="n"/>
+      <c r="BS101" s="5" t="n"/>
+      <c r="CF101" s="5" t="n"/>
+      <c r="CT101" s="5" t="n"/>
+      <c r="DI101" s="5" t="n"/>
     </row>
     <row r="102" ht="4.96" customHeight="1">
-      <c r="L102" s="6" t="n"/>
-      <c r="P102" s="6" t="n"/>
-      <c r="BK102" s="6" t="n"/>
-      <c r="BS102" s="6" t="n"/>
-      <c r="CF102" s="6" t="n"/>
-      <c r="CT102" s="6" t="n"/>
-      <c r="DI102" s="6" t="n"/>
+      <c r="L102" s="5" t="n"/>
+      <c r="P102" s="5" t="n"/>
+      <c r="BK102" s="5" t="n"/>
+      <c r="BS102" s="5" t="n"/>
+      <c r="CF102" s="5" t="n"/>
+      <c r="CT102" s="5" t="n"/>
+      <c r="DI102" s="5" t="n"/>
     </row>
     <row r="103" ht="4.96" customHeight="1">
-      <c r="L103" s="6" t="n"/>
-      <c r="P103" s="6" t="n"/>
-      <c r="BK103" s="6" t="n"/>
-      <c r="BS103" s="6" t="n"/>
-      <c r="CF103" s="6" t="n"/>
-      <c r="CT103" s="6" t="n"/>
-      <c r="DI103" s="6" t="n"/>
+      <c r="L103" s="5" t="n"/>
+      <c r="P103" s="5" t="n"/>
+      <c r="BK103" s="5" t="n"/>
+      <c r="BS103" s="5" t="n"/>
+      <c r="CF103" s="5" t="n"/>
+      <c r="CT103" s="5" t="n"/>
+      <c r="DI103" s="5" t="n"/>
     </row>
     <row r="104" ht="4.96" customHeight="1">
-      <c r="L104" s="6" t="n"/>
-      <c r="P104" s="6" t="n"/>
-      <c r="BK104" s="6" t="n"/>
-      <c r="BS104" s="6" t="n"/>
-      <c r="CF104" s="6" t="n"/>
-      <c r="CT104" s="6" t="n"/>
-      <c r="DI104" s="6" t="n"/>
+      <c r="L104" s="1" t="n"/>
+      <c r="M104" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 8</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="n"/>
+      <c r="O104" s="2" t="n"/>
+      <c r="P104" s="1" t="n"/>
+      <c r="Q104" s="2" t="n"/>
+      <c r="R104" s="2" t="n"/>
+      <c r="S104" s="2" t="n"/>
+      <c r="T104" s="2" t="n"/>
+      <c r="U104" s="2" t="n"/>
+      <c r="V104" s="2" t="n"/>
+      <c r="W104" s="2" t="n"/>
+      <c r="X104" s="2" t="n"/>
+      <c r="Y104" s="2" t="n"/>
+      <c r="Z104" s="2" t="n"/>
+      <c r="AA104" s="2" t="n"/>
+      <c r="AB104" s="2" t="n"/>
+      <c r="AC104" s="2" t="n"/>
+      <c r="AD104" s="2" t="n"/>
+      <c r="AE104" s="2" t="n"/>
+      <c r="AF104" s="2" t="n"/>
+      <c r="AG104" s="2" t="n"/>
+      <c r="AH104" s="2" t="n"/>
+      <c r="AI104" s="2" t="n"/>
+      <c r="AJ104" s="2" t="n"/>
+      <c r="AK104" s="2" t="n"/>
+      <c r="AL104" s="2" t="n"/>
+      <c r="AM104" s="2" t="n"/>
+      <c r="AN104" s="2" t="n"/>
+      <c r="AO104" s="2" t="n"/>
+      <c r="AP104" s="2" t="n"/>
+      <c r="AQ104" s="2" t="n"/>
+      <c r="AR104" s="2" t="n"/>
+      <c r="AS104" s="2" t="n"/>
+      <c r="AT104" s="2" t="n"/>
+      <c r="AU104" s="2" t="n"/>
+      <c r="AV104" s="2" t="n"/>
+      <c r="AW104" s="2" t="n"/>
+      <c r="AX104" s="2" t="n"/>
+      <c r="AY104" s="2" t="n"/>
+      <c r="AZ104" s="2" t="n"/>
+      <c r="BA104" s="2" t="n"/>
+      <c r="BB104" s="2" t="n"/>
+      <c r="BC104" s="2" t="n"/>
+      <c r="BD104" s="2" t="n"/>
+      <c r="BE104" s="2" t="n"/>
+      <c r="BF104" s="2" t="n"/>
+      <c r="BG104" s="2" t="n"/>
+      <c r="BH104" s="2" t="n"/>
+      <c r="BI104" s="2" t="n"/>
+      <c r="BJ104" s="2" t="n"/>
+      <c r="BK104" s="1" t="n"/>
+      <c r="BL104" s="2" t="n"/>
+      <c r="BM104" s="2" t="n"/>
+      <c r="BN104" s="2" t="n"/>
+      <c r="BO104" s="2" t="n"/>
+      <c r="BP104" s="2" t="n"/>
+      <c r="BQ104" s="2" t="n"/>
+      <c r="BR104" s="2" t="n"/>
+      <c r="BS104" s="1" t="n"/>
+      <c r="BT104" s="2" t="n"/>
+      <c r="BU104" s="2" t="n"/>
+      <c r="BV104" s="2" t="n"/>
+      <c r="BW104" s="2" t="n"/>
+      <c r="BX104" s="2" t="n"/>
+      <c r="BY104" s="2" t="n"/>
+      <c r="BZ104" s="2" t="n"/>
+      <c r="CA104" s="2" t="n"/>
+      <c r="CB104" s="2" t="n"/>
+      <c r="CC104" s="2" t="n"/>
+      <c r="CD104" s="2" t="n"/>
+      <c r="CE104" s="2" t="n"/>
+      <c r="CF104" s="1" t="n"/>
+      <c r="CG104" s="2" t="n"/>
+      <c r="CH104" s="2" t="n"/>
+      <c r="CI104" s="2" t="n"/>
+      <c r="CJ104" s="2" t="n"/>
+      <c r="CK104" s="2" t="n"/>
+      <c r="CL104" s="2" t="n"/>
+      <c r="CM104" s="2" t="n"/>
+      <c r="CN104" s="2" t="n"/>
+      <c r="CO104" s="2" t="n"/>
+      <c r="CP104" s="2" t="n"/>
+      <c r="CQ104" s="2" t="n"/>
+      <c r="CR104" s="2" t="n"/>
+      <c r="CS104" s="2" t="n"/>
+      <c r="CT104" s="1" t="n"/>
+      <c r="CU104" s="2" t="n"/>
+      <c r="CV104" s="2" t="n"/>
+      <c r="CW104" s="2" t="n"/>
+      <c r="CX104" s="2" t="n"/>
+      <c r="CY104" s="2" t="n"/>
+      <c r="CZ104" s="2" t="n"/>
+      <c r="DA104" s="2" t="n"/>
+      <c r="DB104" s="2" t="n"/>
+      <c r="DC104" s="2" t="n"/>
+      <c r="DD104" s="2" t="n"/>
+      <c r="DE104" s="2" t="n"/>
+      <c r="DF104" s="2" t="n"/>
+      <c r="DG104" s="2" t="n"/>
+      <c r="DH104" s="2" t="n"/>
+      <c r="DI104" s="1" t="n"/>
     </row>
     <row r="105" ht="4.96" customHeight="1">
-      <c r="L105" s="6" t="n"/>
-      <c r="M105" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="P105" s="6" t="n"/>
-      <c r="BK105" s="6" t="n"/>
-      <c r="BS105" s="6" t="n"/>
-      <c r="CF105" s="6" t="n"/>
-      <c r="CT105" s="6" t="n"/>
-      <c r="DI105" s="6" t="n"/>
+      <c r="L105" s="5" t="n"/>
+      <c r="P105" s="5" t="n"/>
+      <c r="BK105" s="5" t="n"/>
+      <c r="BS105" s="5" t="n"/>
+      <c r="CF105" s="5" t="n"/>
+      <c r="CT105" s="5" t="n"/>
+      <c r="DI105" s="5" t="n"/>
     </row>
     <row r="106" ht="4.96" customHeight="1">
-      <c r="L106" s="6" t="n"/>
-      <c r="P106" s="6" t="n"/>
-      <c r="BK106" s="6" t="n"/>
-      <c r="BS106" s="6" t="n"/>
-      <c r="CF106" s="6" t="n"/>
-      <c r="CT106" s="6" t="n"/>
-      <c r="DI106" s="6" t="n"/>
+      <c r="L106" s="5" t="n"/>
+      <c r="P106" s="5" t="n"/>
+      <c r="BK106" s="5" t="n"/>
+      <c r="BS106" s="5" t="n"/>
+      <c r="CF106" s="5" t="n"/>
+      <c r="CT106" s="5" t="n"/>
+      <c r="DI106" s="5" t="n"/>
     </row>
     <row r="107" ht="4.96" customHeight="1">
-      <c r="L107" s="6" t="n"/>
-      <c r="P107" s="6" t="n"/>
-      <c r="BK107" s="6" t="n"/>
-      <c r="BS107" s="6" t="n"/>
-      <c r="CF107" s="6" t="n"/>
-      <c r="CT107" s="6" t="n"/>
-      <c r="DI107" s="6" t="n"/>
+      <c r="L107" s="1" t="n"/>
+      <c r="M107" s="2" t="n"/>
+      <c r="N107" s="2" t="n"/>
+      <c r="O107" s="2" t="n"/>
+      <c r="P107" s="1" t="n"/>
+      <c r="Q107" s="2" t="n"/>
+      <c r="R107" s="2" t="n"/>
+      <c r="S107" s="2" t="n"/>
+      <c r="T107" s="2" t="n"/>
+      <c r="U107" s="2" t="n"/>
+      <c r="V107" s="2" t="n"/>
+      <c r="W107" s="2" t="n"/>
+      <c r="X107" s="2" t="n"/>
+      <c r="Y107" s="2" t="n"/>
+      <c r="Z107" s="2" t="n"/>
+      <c r="AA107" s="2" t="n"/>
+      <c r="AB107" s="2" t="n"/>
+      <c r="AC107" s="2" t="n"/>
+      <c r="AD107" s="2" t="n"/>
+      <c r="AE107" s="2" t="n"/>
+      <c r="AF107" s="2" t="n"/>
+      <c r="AG107" s="2" t="n"/>
+      <c r="AH107" s="2" t="n"/>
+      <c r="AI107" s="2" t="n"/>
+      <c r="AJ107" s="2" t="n"/>
+      <c r="AK107" s="2" t="n"/>
+      <c r="AL107" s="2" t="n"/>
+      <c r="AM107" s="2" t="n"/>
+      <c r="AN107" s="2" t="n"/>
+      <c r="AO107" s="2" t="n"/>
+      <c r="AP107" s="2" t="n"/>
+      <c r="AQ107" s="2" t="n"/>
+      <c r="AR107" s="2" t="n"/>
+      <c r="AS107" s="2" t="n"/>
+      <c r="AT107" s="2" t="n"/>
+      <c r="AU107" s="2" t="n"/>
+      <c r="AV107" s="2" t="n"/>
+      <c r="AW107" s="2" t="n"/>
+      <c r="AX107" s="2" t="n"/>
+      <c r="AY107" s="2" t="n"/>
+      <c r="AZ107" s="2" t="n"/>
+      <c r="BA107" s="2" t="n"/>
+      <c r="BB107" s="2" t="n"/>
+      <c r="BC107" s="2" t="n"/>
+      <c r="BD107" s="2" t="n"/>
+      <c r="BE107" s="2" t="n"/>
+      <c r="BF107" s="2" t="n"/>
+      <c r="BG107" s="2" t="n"/>
+      <c r="BH107" s="2" t="n"/>
+      <c r="BI107" s="2" t="n"/>
+      <c r="BJ107" s="2" t="n"/>
+      <c r="BK107" s="1" t="n"/>
+      <c r="BL107" s="2" t="n"/>
+      <c r="BM107" s="2" t="n"/>
+      <c r="BN107" s="2" t="n"/>
+      <c r="BO107" s="2" t="n"/>
+      <c r="BP107" s="2" t="n"/>
+      <c r="BQ107" s="2" t="n"/>
+      <c r="BR107" s="2" t="n"/>
+      <c r="BS107" s="1" t="n"/>
+      <c r="BT107" s="2" t="n"/>
+      <c r="BU107" s="2" t="n"/>
+      <c r="BV107" s="2" t="n"/>
+      <c r="BW107" s="2" t="n"/>
+      <c r="BX107" s="2" t="n"/>
+      <c r="BY107" s="2" t="n"/>
+      <c r="BZ107" s="2" t="n"/>
+      <c r="CA107" s="2" t="n"/>
+      <c r="CB107" s="2" t="n"/>
+      <c r="CC107" s="2" t="n"/>
+      <c r="CD107" s="2" t="n"/>
+      <c r="CE107" s="2" t="n"/>
+      <c r="CF107" s="1" t="n"/>
+      <c r="CG107" s="2" t="n"/>
+      <c r="CH107" s="2" t="n"/>
+      <c r="CI107" s="2" t="n"/>
+      <c r="CJ107" s="2" t="n"/>
+      <c r="CK107" s="2" t="n"/>
+      <c r="CL107" s="2" t="n"/>
+      <c r="CM107" s="2" t="n"/>
+      <c r="CN107" s="2" t="n"/>
+      <c r="CO107" s="2" t="n"/>
+      <c r="CP107" s="2" t="n"/>
+      <c r="CQ107" s="2" t="n"/>
+      <c r="CR107" s="2" t="n"/>
+      <c r="CS107" s="2" t="n"/>
+      <c r="CT107" s="1" t="n"/>
+      <c r="CU107" s="2" t="n"/>
+      <c r="CV107" s="2" t="n"/>
+      <c r="CW107" s="2" t="n"/>
+      <c r="CX107" s="2" t="n"/>
+      <c r="CY107" s="2" t="n"/>
+      <c r="CZ107" s="2" t="n"/>
+      <c r="DA107" s="2" t="n"/>
+      <c r="DB107" s="2" t="n"/>
+      <c r="DC107" s="2" t="n"/>
+      <c r="DD107" s="2" t="n"/>
+      <c r="DE107" s="2" t="n"/>
+      <c r="DF107" s="2" t="n"/>
+      <c r="DG107" s="2" t="n"/>
+      <c r="DH107" s="2" t="n"/>
+      <c r="DI107" s="1" t="n"/>
     </row>
     <row r="108" ht="4.96" customHeight="1">
-      <c r="L108" s="6" t="n"/>
-      <c r="M108" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="P108" s="6" t="n"/>
-      <c r="BK108" s="6" t="n"/>
-      <c r="BS108" s="6" t="n"/>
-      <c r="CF108" s="6" t="n"/>
-      <c r="CT108" s="6" t="n"/>
-      <c r="DI108" s="6" t="n"/>
+      <c r="L108" s="5" t="n"/>
+      <c r="M108" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 9</t>
+        </is>
+      </c>
+      <c r="P108" s="5" t="n"/>
+      <c r="BK108" s="5" t="n"/>
+      <c r="BS108" s="5" t="n"/>
+      <c r="CF108" s="5" t="n"/>
+      <c r="CT108" s="5" t="n"/>
+      <c r="DI108" s="5" t="n"/>
     </row>
     <row r="109" ht="4.96" customHeight="1">
-      <c r="L109" s="6" t="n"/>
-      <c r="P109" s="6" t="n"/>
-      <c r="BK109" s="6" t="n"/>
-      <c r="BS109" s="6" t="n"/>
-      <c r="CF109" s="6" t="n"/>
-      <c r="CT109" s="6" t="n"/>
-      <c r="DI109" s="6" t="n"/>
+      <c r="L109" s="5" t="n"/>
+      <c r="P109" s="5" t="n"/>
+      <c r="BK109" s="5" t="n"/>
+      <c r="BS109" s="5" t="n"/>
+      <c r="CF109" s="5" t="n"/>
+      <c r="CT109" s="5" t="n"/>
+      <c r="DI109" s="5" t="n"/>
     </row>
     <row r="110" ht="4.96" customHeight="1">
-      <c r="L110" s="6" t="n"/>
-      <c r="P110" s="6" t="n"/>
-      <c r="BK110" s="6" t="n"/>
-      <c r="BS110" s="6" t="n"/>
-      <c r="CF110" s="6" t="n"/>
-      <c r="CT110" s="6" t="n"/>
-      <c r="DI110" s="6" t="n"/>
+      <c r="L110" s="1" t="n"/>
+      <c r="M110" s="2" t="n"/>
+      <c r="N110" s="2" t="n"/>
+      <c r="O110" s="2" t="n"/>
+      <c r="P110" s="1" t="n"/>
+      <c r="Q110" s="2" t="n"/>
+      <c r="R110" s="2" t="n"/>
+      <c r="S110" s="2" t="n"/>
+      <c r="T110" s="2" t="n"/>
+      <c r="U110" s="2" t="n"/>
+      <c r="V110" s="2" t="n"/>
+      <c r="W110" s="2" t="n"/>
+      <c r="X110" s="2" t="n"/>
+      <c r="Y110" s="2" t="n"/>
+      <c r="Z110" s="2" t="n"/>
+      <c r="AA110" s="2" t="n"/>
+      <c r="AB110" s="2" t="n"/>
+      <c r="AC110" s="2" t="n"/>
+      <c r="AD110" s="2" t="n"/>
+      <c r="AE110" s="2" t="n"/>
+      <c r="AF110" s="2" t="n"/>
+      <c r="AG110" s="2" t="n"/>
+      <c r="AH110" s="2" t="n"/>
+      <c r="AI110" s="2" t="n"/>
+      <c r="AJ110" s="2" t="n"/>
+      <c r="AK110" s="2" t="n"/>
+      <c r="AL110" s="2" t="n"/>
+      <c r="AM110" s="2" t="n"/>
+      <c r="AN110" s="2" t="n"/>
+      <c r="AO110" s="2" t="n"/>
+      <c r="AP110" s="2" t="n"/>
+      <c r="AQ110" s="2" t="n"/>
+      <c r="AR110" s="2" t="n"/>
+      <c r="AS110" s="2" t="n"/>
+      <c r="AT110" s="2" t="n"/>
+      <c r="AU110" s="2" t="n"/>
+      <c r="AV110" s="2" t="n"/>
+      <c r="AW110" s="2" t="n"/>
+      <c r="AX110" s="2" t="n"/>
+      <c r="AY110" s="2" t="n"/>
+      <c r="AZ110" s="2" t="n"/>
+      <c r="BA110" s="2" t="n"/>
+      <c r="BB110" s="2" t="n"/>
+      <c r="BC110" s="2" t="n"/>
+      <c r="BD110" s="2" t="n"/>
+      <c r="BE110" s="2" t="n"/>
+      <c r="BF110" s="2" t="n"/>
+      <c r="BG110" s="2" t="n"/>
+      <c r="BH110" s="2" t="n"/>
+      <c r="BI110" s="2" t="n"/>
+      <c r="BJ110" s="2" t="n"/>
+      <c r="BK110" s="1" t="n"/>
+      <c r="BL110" s="2" t="n"/>
+      <c r="BM110" s="2" t="n"/>
+      <c r="BN110" s="2" t="n"/>
+      <c r="BO110" s="2" t="n"/>
+      <c r="BP110" s="2" t="n"/>
+      <c r="BQ110" s="2" t="n"/>
+      <c r="BR110" s="2" t="n"/>
+      <c r="BS110" s="1" t="n"/>
+      <c r="BT110" s="2" t="n"/>
+      <c r="BU110" s="2" t="n"/>
+      <c r="BV110" s="2" t="n"/>
+      <c r="BW110" s="2" t="n"/>
+      <c r="BX110" s="2" t="n"/>
+      <c r="BY110" s="2" t="n"/>
+      <c r="BZ110" s="2" t="n"/>
+      <c r="CA110" s="2" t="n"/>
+      <c r="CB110" s="2" t="n"/>
+      <c r="CC110" s="2" t="n"/>
+      <c r="CD110" s="2" t="n"/>
+      <c r="CE110" s="2" t="n"/>
+      <c r="CF110" s="1" t="n"/>
+      <c r="CG110" s="2" t="n"/>
+      <c r="CH110" s="2" t="n"/>
+      <c r="CI110" s="2" t="n"/>
+      <c r="CJ110" s="2" t="n"/>
+      <c r="CK110" s="2" t="n"/>
+      <c r="CL110" s="2" t="n"/>
+      <c r="CM110" s="2" t="n"/>
+      <c r="CN110" s="2" t="n"/>
+      <c r="CO110" s="2" t="n"/>
+      <c r="CP110" s="2" t="n"/>
+      <c r="CQ110" s="2" t="n"/>
+      <c r="CR110" s="2" t="n"/>
+      <c r="CS110" s="2" t="n"/>
+      <c r="CT110" s="1" t="n"/>
+      <c r="CU110" s="2" t="n"/>
+      <c r="CV110" s="2" t="n"/>
+      <c r="CW110" s="2" t="n"/>
+      <c r="CX110" s="2" t="n"/>
+      <c r="CY110" s="2" t="n"/>
+      <c r="CZ110" s="2" t="n"/>
+      <c r="DA110" s="2" t="n"/>
+      <c r="DB110" s="2" t="n"/>
+      <c r="DC110" s="2" t="n"/>
+      <c r="DD110" s="2" t="n"/>
+      <c r="DE110" s="2" t="n"/>
+      <c r="DF110" s="2" t="n"/>
+      <c r="DG110" s="2" t="n"/>
+      <c r="DH110" s="2" t="n"/>
+      <c r="DI110" s="1" t="n"/>
     </row>
     <row r="111" ht="4.96" customHeight="1">
-      <c r="L111" s="6" t="n"/>
-      <c r="M111" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="P111" s="6" t="n"/>
-      <c r="BK111" s="6" t="n"/>
-      <c r="BS111" s="6" t="n"/>
-      <c r="CF111" s="6" t="n"/>
-      <c r="CT111" s="6" t="n"/>
-      <c r="DI111" s="6" t="n"/>
+      <c r="L111" s="5" t="n"/>
+      <c r="M111" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P111" s="5" t="n"/>
+      <c r="BK111" s="5" t="n"/>
+      <c r="BS111" s="5" t="n"/>
+      <c r="CF111" s="5" t="n"/>
+      <c r="CT111" s="5" t="n"/>
+      <c r="DI111" s="5" t="n"/>
     </row>
     <row r="112" ht="4.96" customHeight="1">
-      <c r="L112" s="6" t="n"/>
-      <c r="P112" s="6" t="n"/>
-      <c r="BK112" s="6" t="n"/>
-      <c r="BS112" s="6" t="n"/>
-      <c r="CF112" s="6" t="n"/>
-      <c r="CT112" s="6" t="n"/>
-      <c r="DI112" s="6" t="n"/>
+      <c r="L112" s="5" t="n"/>
+      <c r="P112" s="5" t="n"/>
+      <c r="BK112" s="5" t="n"/>
+      <c r="BS112" s="5" t="n"/>
+      <c r="CF112" s="5" t="n"/>
+      <c r="CT112" s="5" t="n"/>
+      <c r="DI112" s="5" t="n"/>
     </row>
     <row r="113" ht="4.96" customHeight="1">
-      <c r="L113" s="6" t="n"/>
-      <c r="P113" s="6" t="n"/>
-      <c r="BK113" s="6" t="n"/>
-      <c r="BS113" s="6" t="n"/>
-      <c r="CF113" s="6" t="n"/>
-      <c r="CT113" s="6" t="n"/>
-      <c r="DI113" s="6" t="n"/>
+      <c r="L113" s="5" t="n"/>
+      <c r="P113" s="5" t="n"/>
+      <c r="BK113" s="5" t="n"/>
+      <c r="BS113" s="5" t="n"/>
+      <c r="CF113" s="5" t="n"/>
+      <c r="CT113" s="5" t="n"/>
+      <c r="DI113" s="5" t="n"/>
     </row>
     <row r="114" ht="4.96" customHeight="1">
-      <c r="L114" s="6" t="n"/>
-      <c r="P114" s="6" t="n"/>
-      <c r="BK114" s="6" t="n"/>
-      <c r="BS114" s="6" t="n"/>
-      <c r="CF114" s="6" t="n"/>
-      <c r="CT114" s="6" t="n"/>
-      <c r="DI114" s="6" t="n"/>
+      <c r="K114" s="2" t="n"/>
+      <c r="L114" s="1" t="n"/>
+      <c r="M114" s="2" t="n"/>
+      <c r="N114" s="2" t="n"/>
+      <c r="O114" s="2" t="n"/>
+      <c r="P114" s="1" t="n"/>
+      <c r="Q114" s="2" t="n"/>
+      <c r="R114" s="2" t="n"/>
+      <c r="S114" s="2" t="n"/>
+      <c r="T114" s="2" t="n"/>
+      <c r="U114" s="2" t="n"/>
+      <c r="V114" s="2" t="n"/>
+      <c r="W114" s="2" t="n"/>
+      <c r="X114" s="2" t="n"/>
+      <c r="Y114" s="2" t="n"/>
+      <c r="Z114" s="2" t="n"/>
+      <c r="AA114" s="2" t="n"/>
+      <c r="AB114" s="2" t="n"/>
+      <c r="AC114" s="2" t="n"/>
+      <c r="AD114" s="2" t="n"/>
+      <c r="AE114" s="2" t="n"/>
+      <c r="AF114" s="2" t="n"/>
+      <c r="AG114" s="2" t="n"/>
+      <c r="AH114" s="2" t="n"/>
+      <c r="AI114" s="2" t="n"/>
+      <c r="AJ114" s="2" t="n"/>
+      <c r="AK114" s="2" t="n"/>
+      <c r="AL114" s="2" t="n"/>
+      <c r="AM114" s="2" t="n"/>
+      <c r="AN114" s="2" t="n"/>
+      <c r="AO114" s="2" t="n"/>
+      <c r="AP114" s="2" t="n"/>
+      <c r="AQ114" s="2" t="n"/>
+      <c r="AR114" s="2" t="n"/>
+      <c r="AS114" s="2" t="n"/>
+      <c r="AT114" s="2" t="n"/>
+      <c r="AU114" s="2" t="n"/>
+      <c r="AV114" s="2" t="n"/>
+      <c r="AW114" s="2" t="n"/>
+      <c r="AX114" s="2" t="n"/>
+      <c r="AY114" s="2" t="n"/>
+      <c r="AZ114" s="2" t="n"/>
+      <c r="BA114" s="2" t="n"/>
+      <c r="BB114" s="2" t="n"/>
+      <c r="BC114" s="2" t="n"/>
+      <c r="BD114" s="2" t="n"/>
+      <c r="BE114" s="2" t="n"/>
+      <c r="BF114" s="2" t="n"/>
+      <c r="BG114" s="2" t="n"/>
+      <c r="BH114" s="2" t="n"/>
+      <c r="BI114" s="2" t="n"/>
+      <c r="BJ114" s="2" t="n"/>
+      <c r="BK114" s="1" t="n"/>
+      <c r="BL114" s="2" t="n"/>
+      <c r="BM114" s="2" t="n"/>
+      <c r="BN114" s="2" t="n"/>
+      <c r="BO114" s="2" t="n"/>
+      <c r="BP114" s="2" t="n"/>
+      <c r="BQ114" s="2" t="n"/>
+      <c r="BR114" s="2" t="n"/>
+      <c r="BS114" s="1" t="n"/>
+      <c r="BT114" s="2" t="n"/>
+      <c r="BU114" s="2" t="n"/>
+      <c r="BV114" s="2" t="n"/>
+      <c r="BW114" s="2" t="n"/>
+      <c r="BX114" s="2" t="n"/>
+      <c r="BY114" s="2" t="n"/>
+      <c r="BZ114" s="2" t="n"/>
+      <c r="CA114" s="2" t="n"/>
+      <c r="CB114" s="2" t="n"/>
+      <c r="CC114" s="2" t="n"/>
+      <c r="CD114" s="2" t="n"/>
+      <c r="CE114" s="2" t="n"/>
+      <c r="CF114" s="1" t="n"/>
+      <c r="CG114" s="2" t="n"/>
+      <c r="CH114" s="2" t="n"/>
+      <c r="CI114" s="2" t="n"/>
+      <c r="CJ114" s="2" t="n"/>
+      <c r="CK114" s="2" t="n"/>
+      <c r="CL114" s="2" t="n"/>
+      <c r="CM114" s="2" t="n"/>
+      <c r="CN114" s="2" t="n"/>
+      <c r="CO114" s="2" t="n"/>
+      <c r="CP114" s="2" t="n"/>
+      <c r="CQ114" s="2" t="n"/>
+      <c r="CR114" s="2" t="n"/>
+      <c r="CS114" s="2" t="n"/>
+      <c r="CT114" s="1" t="n"/>
+      <c r="CU114" s="2" t="n"/>
+      <c r="CV114" s="2" t="n"/>
+      <c r="CW114" s="2" t="n"/>
+      <c r="CX114" s="2" t="n"/>
+      <c r="CY114" s="2" t="n"/>
+      <c r="CZ114" s="2" t="n"/>
+      <c r="DA114" s="2" t="n"/>
+      <c r="DB114" s="2" t="n"/>
+      <c r="DC114" s="2" t="n"/>
+      <c r="DD114" s="2" t="n"/>
+      <c r="DE114" s="2" t="n"/>
+      <c r="DF114" s="2" t="n"/>
+      <c r="DG114" s="2" t="n"/>
+      <c r="DH114" s="2" t="n"/>
+      <c r="DI114" s="1" t="n"/>
     </row>
     <row r="115" ht="4.96" customHeight="1">
-      <c r="L115" s="6" t="n"/>
-      <c r="M115" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="P115" s="6" t="n"/>
-      <c r="BK115" s="6" t="n"/>
-      <c r="BS115" s="6" t="n"/>
-      <c r="CF115" s="6" t="n"/>
-      <c r="CT115" s="6" t="n"/>
-      <c r="DI115" s="6" t="n"/>
+      <c r="L115" s="5" t="n"/>
+      <c r="M115" s="22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P115" s="5" t="n"/>
+      <c r="BK115" s="5" t="n"/>
+      <c r="BS115" s="5" t="n"/>
+      <c r="CF115" s="5" t="n"/>
+      <c r="CT115" s="5" t="n"/>
+      <c r="DI115" s="5" t="n"/>
     </row>
     <row r="116" ht="4.96" customHeight="1">
-      <c r="L116" s="6" t="n"/>
-      <c r="P116" s="6" t="n"/>
-      <c r="BK116" s="6" t="n"/>
-      <c r="BS116" s="6" t="n"/>
-      <c r="CF116" s="6" t="n"/>
-      <c r="CT116" s="6" t="n"/>
-      <c r="DI116" s="6" t="n"/>
+      <c r="L116" s="5" t="n"/>
+      <c r="P116" s="5" t="n"/>
+      <c r="BK116" s="5" t="n"/>
+      <c r="BS116" s="5" t="n"/>
+      <c r="CF116" s="5" t="n"/>
+      <c r="CT116" s="5" t="n"/>
+      <c r="DI116" s="5" t="n"/>
     </row>
     <row r="117" ht="4.96" customHeight="1">
-      <c r="L117" s="6" t="n"/>
-      <c r="P117" s="6" t="n"/>
-      <c r="BK117" s="6" t="n"/>
-      <c r="BS117" s="6" t="n"/>
-      <c r="CF117" s="6" t="n"/>
-      <c r="CT117" s="6" t="n"/>
-      <c r="DI117" s="6" t="n"/>
+      <c r="L117" s="1" t="n"/>
+      <c r="M117" s="2" t="n"/>
+      <c r="N117" s="2" t="n"/>
+      <c r="O117" s="2" t="n"/>
+      <c r="P117" s="1" t="n"/>
+      <c r="Q117" s="2" t="n"/>
+      <c r="R117" s="2" t="n"/>
+      <c r="S117" s="2" t="n"/>
+      <c r="T117" s="2" t="n"/>
+      <c r="U117" s="2" t="n"/>
+      <c r="V117" s="2" t="n"/>
+      <c r="W117" s="2" t="n"/>
+      <c r="X117" s="2" t="n"/>
+      <c r="Y117" s="2" t="n"/>
+      <c r="Z117" s="2" t="n"/>
+      <c r="AA117" s="2" t="n"/>
+      <c r="AB117" s="2" t="n"/>
+      <c r="AC117" s="2" t="n"/>
+      <c r="AD117" s="2" t="n"/>
+      <c r="AE117" s="2" t="n"/>
+      <c r="AF117" s="2" t="n"/>
+      <c r="AG117" s="2" t="n"/>
+      <c r="AH117" s="2" t="n"/>
+      <c r="AI117" s="2" t="n"/>
+      <c r="AJ117" s="2" t="n"/>
+      <c r="AK117" s="2" t="n"/>
+      <c r="AL117" s="2" t="n"/>
+      <c r="AM117" s="2" t="n"/>
+      <c r="AN117" s="2" t="n"/>
+      <c r="AO117" s="2" t="n"/>
+      <c r="AP117" s="2" t="n"/>
+      <c r="AQ117" s="2" t="n"/>
+      <c r="AR117" s="2" t="n"/>
+      <c r="AS117" s="2" t="n"/>
+      <c r="AT117" s="2" t="n"/>
+      <c r="AU117" s="2" t="n"/>
+      <c r="AV117" s="2" t="n"/>
+      <c r="AW117" s="2" t="n"/>
+      <c r="AX117" s="2" t="n"/>
+      <c r="AY117" s="2" t="n"/>
+      <c r="AZ117" s="2" t="n"/>
+      <c r="BA117" s="2" t="n"/>
+      <c r="BB117" s="2" t="n"/>
+      <c r="BC117" s="2" t="n"/>
+      <c r="BD117" s="2" t="n"/>
+      <c r="BE117" s="2" t="n"/>
+      <c r="BF117" s="2" t="n"/>
+      <c r="BG117" s="2" t="n"/>
+      <c r="BH117" s="2" t="n"/>
+      <c r="BI117" s="2" t="n"/>
+      <c r="BJ117" s="2" t="n"/>
+      <c r="BK117" s="1" t="n"/>
+      <c r="BL117" s="2" t="n"/>
+      <c r="BM117" s="2" t="n"/>
+      <c r="BN117" s="2" t="n"/>
+      <c r="BO117" s="2" t="n"/>
+      <c r="BP117" s="2" t="n"/>
+      <c r="BQ117" s="2" t="n"/>
+      <c r="BR117" s="2" t="n"/>
+      <c r="BS117" s="1" t="n"/>
+      <c r="BT117" s="2" t="n"/>
+      <c r="BU117" s="2" t="n"/>
+      <c r="BV117" s="2" t="n"/>
+      <c r="BW117" s="2" t="n"/>
+      <c r="BX117" s="2" t="n"/>
+      <c r="BY117" s="2" t="n"/>
+      <c r="BZ117" s="2" t="n"/>
+      <c r="CA117" s="2" t="n"/>
+      <c r="CB117" s="2" t="n"/>
+      <c r="CC117" s="2" t="n"/>
+      <c r="CD117" s="2" t="n"/>
+      <c r="CE117" s="2" t="n"/>
+      <c r="CF117" s="1" t="n"/>
+      <c r="CG117" s="2" t="n"/>
+      <c r="CH117" s="2" t="n"/>
+      <c r="CI117" s="2" t="n"/>
+      <c r="CJ117" s="2" t="n"/>
+      <c r="CK117" s="2" t="n"/>
+      <c r="CL117" s="2" t="n"/>
+      <c r="CM117" s="2" t="n"/>
+      <c r="CN117" s="2" t="n"/>
+      <c r="CO117" s="2" t="n"/>
+      <c r="CP117" s="2" t="n"/>
+      <c r="CQ117" s="2" t="n"/>
+      <c r="CR117" s="2" t="n"/>
+      <c r="CS117" s="2" t="n"/>
+      <c r="CT117" s="1" t="n"/>
+      <c r="CU117" s="2" t="n"/>
+      <c r="CV117" s="2" t="n"/>
+      <c r="CW117" s="2" t="n"/>
+      <c r="CX117" s="2" t="n"/>
+      <c r="CY117" s="2" t="n"/>
+      <c r="CZ117" s="2" t="n"/>
+      <c r="DA117" s="2" t="n"/>
+      <c r="DB117" s="2" t="n"/>
+      <c r="DC117" s="2" t="n"/>
+      <c r="DD117" s="2" t="n"/>
+      <c r="DE117" s="2" t="n"/>
+      <c r="DF117" s="2" t="n"/>
+      <c r="DG117" s="2" t="n"/>
+      <c r="DH117" s="2" t="n"/>
+      <c r="DI117" s="1" t="n"/>
     </row>
     <row r="118" ht="4.96" customHeight="1">
-      <c r="L118" s="6" t="n"/>
-      <c r="M118" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="P118" s="6" t="n"/>
-      <c r="BK118" s="6" t="n"/>
-      <c r="BS118" s="6" t="n"/>
-      <c r="CF118" s="6" t="n"/>
-      <c r="CT118" s="6" t="n"/>
-      <c r="DI118" s="6" t="n"/>
+      <c r="L118" s="5" t="n"/>
+      <c r="M118" s="22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P118" s="5" t="n"/>
+      <c r="BK118" s="5" t="n"/>
+      <c r="BS118" s="5" t="n"/>
+      <c r="CF118" s="5" t="n"/>
+      <c r="CT118" s="5" t="n"/>
+      <c r="DI118" s="5" t="n"/>
     </row>
     <row r="119" ht="4.96" customHeight="1">
-      <c r="L119" s="6" t="n"/>
-      <c r="P119" s="6" t="n"/>
-      <c r="BK119" s="6" t="n"/>
-      <c r="BS119" s="6" t="n"/>
-      <c r="CF119" s="6" t="n"/>
-      <c r="CT119" s="6" t="n"/>
-      <c r="DI119" s="6" t="n"/>
+      <c r="L119" s="5" t="n"/>
+      <c r="P119" s="5" t="n"/>
+      <c r="BK119" s="5" t="n"/>
+      <c r="BS119" s="5" t="n"/>
+      <c r="CF119" s="5" t="n"/>
+      <c r="CT119" s="5" t="n"/>
+      <c r="DI119" s="5" t="n"/>
     </row>
     <row r="120" ht="4.96" customHeight="1">
-      <c r="L120" s="6" t="n"/>
-      <c r="P120" s="6" t="n"/>
-      <c r="BK120" s="6" t="n"/>
-      <c r="BS120" s="6" t="n"/>
-      <c r="CF120" s="6" t="n"/>
-      <c r="CT120" s="6" t="n"/>
-      <c r="DI120" s="6" t="n"/>
+      <c r="L120" s="5" t="n"/>
+      <c r="P120" s="5" t="n"/>
+      <c r="BK120" s="5" t="n"/>
+      <c r="BS120" s="5" t="n"/>
+      <c r="CF120" s="5" t="n"/>
+      <c r="CT120" s="5" t="n"/>
+      <c r="DI120" s="5" t="n"/>
     </row>
     <row r="121" ht="4.96" customHeight="1">
-      <c r="L121" s="6" t="n"/>
-      <c r="P121" s="6" t="n"/>
-      <c r="BK121" s="6" t="n"/>
-      <c r="BS121" s="6" t="n"/>
-      <c r="CF121" s="6" t="n"/>
-      <c r="CT121" s="6" t="n"/>
-      <c r="DI121" s="6" t="n"/>
+      <c r="K121" s="2" t="n"/>
+      <c r="L121" s="1" t="n"/>
+      <c r="M121" s="2" t="n"/>
+      <c r="N121" s="2" t="n"/>
+      <c r="O121" s="2" t="n"/>
+      <c r="P121" s="1" t="n"/>
+      <c r="Q121" s="2" t="n"/>
+      <c r="R121" s="2" t="n"/>
+      <c r="S121" s="2" t="n"/>
+      <c r="T121" s="2" t="n"/>
+      <c r="U121" s="2" t="n"/>
+      <c r="V121" s="2" t="n"/>
+      <c r="W121" s="2" t="n"/>
+      <c r="X121" s="2" t="n"/>
+      <c r="Y121" s="2" t="n"/>
+      <c r="Z121" s="2" t="n"/>
+      <c r="AA121" s="2" t="n"/>
+      <c r="AB121" s="2" t="n"/>
+      <c r="AC121" s="2" t="n"/>
+      <c r="AD121" s="2" t="n"/>
+      <c r="AE121" s="2" t="n"/>
+      <c r="AF121" s="2" t="n"/>
+      <c r="AG121" s="2" t="n"/>
+      <c r="AH121" s="2" t="n"/>
+      <c r="AI121" s="2" t="n"/>
+      <c r="AJ121" s="2" t="n"/>
+      <c r="AK121" s="2" t="n"/>
+      <c r="AL121" s="2" t="n"/>
+      <c r="AM121" s="2" t="n"/>
+      <c r="AN121" s="2" t="n"/>
+      <c r="AO121" s="2" t="n"/>
+      <c r="AP121" s="2" t="n"/>
+      <c r="AQ121" s="2" t="n"/>
+      <c r="AR121" s="2" t="n"/>
+      <c r="AS121" s="2" t="n"/>
+      <c r="AT121" s="2" t="n"/>
+      <c r="AU121" s="2" t="n"/>
+      <c r="AV121" s="2" t="n"/>
+      <c r="AW121" s="2" t="n"/>
+      <c r="AX121" s="2" t="n"/>
+      <c r="AY121" s="2" t="n"/>
+      <c r="AZ121" s="2" t="n"/>
+      <c r="BA121" s="2" t="n"/>
+      <c r="BB121" s="2" t="n"/>
+      <c r="BC121" s="2" t="n"/>
+      <c r="BD121" s="2" t="n"/>
+      <c r="BE121" s="2" t="n"/>
+      <c r="BF121" s="2" t="n"/>
+      <c r="BG121" s="2" t="n"/>
+      <c r="BH121" s="2" t="n"/>
+      <c r="BI121" s="2" t="n"/>
+      <c r="BJ121" s="2" t="n"/>
+      <c r="BK121" s="1" t="n"/>
+      <c r="BL121" s="2" t="n"/>
+      <c r="BM121" s="2" t="n"/>
+      <c r="BN121" s="2" t="n"/>
+      <c r="BO121" s="2" t="n"/>
+      <c r="BP121" s="2" t="n"/>
+      <c r="BQ121" s="2" t="n"/>
+      <c r="BR121" s="2" t="n"/>
+      <c r="BS121" s="1" t="n"/>
+      <c r="BT121" s="2" t="n"/>
+      <c r="BU121" s="2" t="n"/>
+      <c r="BV121" s="2" t="n"/>
+      <c r="BW121" s="2" t="n"/>
+      <c r="BX121" s="2" t="n"/>
+      <c r="BY121" s="2" t="n"/>
+      <c r="BZ121" s="2" t="n"/>
+      <c r="CA121" s="2" t="n"/>
+      <c r="CB121" s="2" t="n"/>
+      <c r="CC121" s="2" t="n"/>
+      <c r="CD121" s="2" t="n"/>
+      <c r="CE121" s="2" t="n"/>
+      <c r="CF121" s="1" t="n"/>
+      <c r="CG121" s="2" t="n"/>
+      <c r="CH121" s="2" t="n"/>
+      <c r="CI121" s="2" t="n"/>
+      <c r="CJ121" s="2" t="n"/>
+      <c r="CK121" s="2" t="n"/>
+      <c r="CL121" s="2" t="n"/>
+      <c r="CM121" s="2" t="n"/>
+      <c r="CN121" s="2" t="n"/>
+      <c r="CO121" s="2" t="n"/>
+      <c r="CP121" s="2" t="n"/>
+      <c r="CQ121" s="2" t="n"/>
+      <c r="CR121" s="2" t="n"/>
+      <c r="CS121" s="2" t="n"/>
+      <c r="CT121" s="1" t="n"/>
+      <c r="CU121" s="2" t="n"/>
+      <c r="CV121" s="2" t="n"/>
+      <c r="CW121" s="2" t="n"/>
+      <c r="CX121" s="2" t="n"/>
+      <c r="CY121" s="2" t="n"/>
+      <c r="CZ121" s="2" t="n"/>
+      <c r="DA121" s="2" t="n"/>
+      <c r="DB121" s="2" t="n"/>
+      <c r="DC121" s="2" t="n"/>
+      <c r="DD121" s="2" t="n"/>
+      <c r="DE121" s="2" t="n"/>
+      <c r="DF121" s="2" t="n"/>
+      <c r="DG121" s="2" t="n"/>
+      <c r="DH121" s="2" t="n"/>
+      <c r="DI121" s="1" t="n"/>
     </row>
     <row r="122" ht="4.96" customHeight="1">
-      <c r="L122" s="6" t="n"/>
-      <c r="M122" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="P122" s="6" t="n"/>
-      <c r="BK122" s="6" t="n"/>
-      <c r="BS122" s="6" t="n"/>
-      <c r="CF122" s="6" t="n"/>
-      <c r="CT122" s="6" t="n"/>
-      <c r="DI122" s="6" t="n"/>
+      <c r="L122" s="5" t="n"/>
+      <c r="M122" s="22" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P122" s="5" t="n"/>
+      <c r="BK122" s="5" t="n"/>
+      <c r="BS122" s="5" t="n"/>
+      <c r="CF122" s="5" t="n"/>
+      <c r="CT122" s="5" t="n"/>
+      <c r="DI122" s="5" t="n"/>
     </row>
     <row r="123" ht="4.96" customHeight="1">
-      <c r="L123" s="6" t="n"/>
-      <c r="P123" s="6" t="n"/>
-      <c r="BK123" s="6" t="n"/>
-      <c r="BS123" s="6" t="n"/>
-      <c r="CF123" s="6" t="n"/>
-      <c r="CT123" s="6" t="n"/>
-      <c r="DI123" s="6" t="n"/>
+      <c r="L123" s="5" t="n"/>
+      <c r="P123" s="5" t="n"/>
+      <c r="BK123" s="5" t="n"/>
+      <c r="BS123" s="5" t="n"/>
+      <c r="CF123" s="5" t="n"/>
+      <c r="CT123" s="5" t="n"/>
+      <c r="DI123" s="5" t="n"/>
     </row>
     <row r="124" ht="4.96" customHeight="1">
-      <c r="L124" s="6" t="n"/>
-      <c r="P124" s="6" t="n"/>
-      <c r="BK124" s="6" t="n"/>
-      <c r="BS124" s="6" t="n"/>
-      <c r="CF124" s="6" t="n"/>
-      <c r="CT124" s="6" t="n"/>
-      <c r="DI124" s="6" t="n"/>
+      <c r="K124" s="2" t="n"/>
+      <c r="L124" s="1" t="n"/>
+      <c r="M124" s="2" t="n"/>
+      <c r="N124" s="2" t="n"/>
+      <c r="O124" s="2" t="n"/>
+      <c r="P124" s="1" t="n"/>
+      <c r="Q124" s="2" t="n"/>
+      <c r="R124" s="2" t="n"/>
+      <c r="S124" s="2" t="n"/>
+      <c r="T124" s="2" t="n"/>
+      <c r="U124" s="2" t="n"/>
+      <c r="V124" s="2" t="n"/>
+      <c r="W124" s="2" t="n"/>
+      <c r="X124" s="2" t="n"/>
+      <c r="Y124" s="2" t="n"/>
+      <c r="Z124" s="2" t="n"/>
+      <c r="AA124" s="2" t="n"/>
+      <c r="AB124" s="2" t="n"/>
+      <c r="AC124" s="2" t="n"/>
+      <c r="AD124" s="2" t="n"/>
+      <c r="AE124" s="2" t="n"/>
+      <c r="AF124" s="2" t="n"/>
+      <c r="AG124" s="2" t="n"/>
+      <c r="AH124" s="2" t="n"/>
+      <c r="AI124" s="2" t="n"/>
+      <c r="AJ124" s="2" t="n"/>
+      <c r="AK124" s="2" t="n"/>
+      <c r="AL124" s="2" t="n"/>
+      <c r="AM124" s="2" t="n"/>
+      <c r="AN124" s="2" t="n"/>
+      <c r="AO124" s="2" t="n"/>
+      <c r="AP124" s="2" t="n"/>
+      <c r="AQ124" s="2" t="n"/>
+      <c r="AR124" s="2" t="n"/>
+      <c r="AS124" s="2" t="n"/>
+      <c r="AT124" s="2" t="n"/>
+      <c r="AU124" s="2" t="n"/>
+      <c r="AV124" s="2" t="n"/>
+      <c r="AW124" s="2" t="n"/>
+      <c r="AX124" s="2" t="n"/>
+      <c r="AY124" s="2" t="n"/>
+      <c r="AZ124" s="2" t="n"/>
+      <c r="BA124" s="2" t="n"/>
+      <c r="BB124" s="2" t="n"/>
+      <c r="BC124" s="2" t="n"/>
+      <c r="BD124" s="2" t="n"/>
+      <c r="BE124" s="2" t="n"/>
+      <c r="BF124" s="2" t="n"/>
+      <c r="BG124" s="2" t="n"/>
+      <c r="BH124" s="2" t="n"/>
+      <c r="BI124" s="2" t="n"/>
+      <c r="BJ124" s="2" t="n"/>
+      <c r="BK124" s="1" t="n"/>
+      <c r="BL124" s="2" t="n"/>
+      <c r="BM124" s="2" t="n"/>
+      <c r="BN124" s="2" t="n"/>
+      <c r="BO124" s="2" t="n"/>
+      <c r="BP124" s="2" t="n"/>
+      <c r="BQ124" s="2" t="n"/>
+      <c r="BR124" s="2" t="n"/>
+      <c r="BS124" s="1" t="n"/>
+      <c r="BT124" s="2" t="n"/>
+      <c r="BU124" s="2" t="n"/>
+      <c r="BV124" s="2" t="n"/>
+      <c r="BW124" s="2" t="n"/>
+      <c r="BX124" s="2" t="n"/>
+      <c r="BY124" s="2" t="n"/>
+      <c r="BZ124" s="2" t="n"/>
+      <c r="CA124" s="2" t="n"/>
+      <c r="CB124" s="2" t="n"/>
+      <c r="CC124" s="2" t="n"/>
+      <c r="CD124" s="2" t="n"/>
+      <c r="CE124" s="2" t="n"/>
+      <c r="CF124" s="1" t="n"/>
+      <c r="CG124" s="2" t="n"/>
+      <c r="CH124" s="2" t="n"/>
+      <c r="CI124" s="2" t="n"/>
+      <c r="CJ124" s="2" t="n"/>
+      <c r="CK124" s="2" t="n"/>
+      <c r="CL124" s="2" t="n"/>
+      <c r="CM124" s="2" t="n"/>
+      <c r="CN124" s="2" t="n"/>
+      <c r="CO124" s="2" t="n"/>
+      <c r="CP124" s="2" t="n"/>
+      <c r="CQ124" s="2" t="n"/>
+      <c r="CR124" s="2" t="n"/>
+      <c r="CS124" s="2" t="n"/>
+      <c r="CT124" s="1" t="n"/>
+      <c r="CU124" s="2" t="n"/>
+      <c r="CV124" s="2" t="n"/>
+      <c r="CW124" s="2" t="n"/>
+      <c r="CX124" s="2" t="n"/>
+      <c r="CY124" s="2" t="n"/>
+      <c r="CZ124" s="2" t="n"/>
+      <c r="DA124" s="2" t="n"/>
+      <c r="DB124" s="2" t="n"/>
+      <c r="DC124" s="2" t="n"/>
+      <c r="DD124" s="2" t="n"/>
+      <c r="DE124" s="2" t="n"/>
+      <c r="DF124" s="2" t="n"/>
+      <c r="DG124" s="2" t="n"/>
+      <c r="DH124" s="2" t="n"/>
+      <c r="DI124" s="1" t="n"/>
     </row>
     <row r="125" ht="4.96" customHeight="1">
-      <c r="L125" s="6" t="n"/>
-      <c r="M125" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="P125" s="6" t="n"/>
-      <c r="BK125" s="6" t="n"/>
-      <c r="BS125" s="6" t="n"/>
-      <c r="CF125" s="6" t="n"/>
-      <c r="CT125" s="6" t="n"/>
-      <c r="DI125" s="6" t="n"/>
+      <c r="L125" s="5" t="n"/>
+      <c r="M125" s="22" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P125" s="5" t="n"/>
+      <c r="BK125" s="5" t="n"/>
+      <c r="BS125" s="5" t="n"/>
+      <c r="CF125" s="5" t="n"/>
+      <c r="CT125" s="5" t="n"/>
+      <c r="DI125" s="5" t="n"/>
     </row>
     <row r="126" ht="4.96" customHeight="1">
-      <c r="L126" s="6" t="n"/>
-      <c r="P126" s="6" t="n"/>
-      <c r="BK126" s="6" t="n"/>
-      <c r="BS126" s="6" t="n"/>
-      <c r="CF126" s="6" t="n"/>
-      <c r="CT126" s="6" t="n"/>
-      <c r="DI126" s="6" t="n"/>
+      <c r="L126" s="5" t="n"/>
+      <c r="P126" s="5" t="n"/>
+      <c r="BK126" s="5" t="n"/>
+      <c r="BS126" s="5" t="n"/>
+      <c r="CF126" s="5" t="n"/>
+      <c r="CT126" s="5" t="n"/>
+      <c r="DI126" s="5" t="n"/>
     </row>
     <row r="127" ht="4.96" customHeight="1">
-      <c r="L127" s="6" t="n"/>
-      <c r="P127" s="6" t="n"/>
-      <c r="BK127" s="6" t="n"/>
-      <c r="BS127" s="6" t="n"/>
-      <c r="CF127" s="6" t="n"/>
-      <c r="CT127" s="6" t="n"/>
-      <c r="DI127" s="6" t="n"/>
+      <c r="L127" s="5" t="n"/>
+      <c r="P127" s="5" t="n"/>
+      <c r="BK127" s="5" t="n"/>
+      <c r="BS127" s="5" t="n"/>
+      <c r="CF127" s="5" t="n"/>
+      <c r="CT127" s="5" t="n"/>
+      <c r="DI127" s="5" t="n"/>
     </row>
     <row r="128" ht="4.96" customHeight="1">
-      <c r="L128" s="6" t="n"/>
-      <c r="P128" s="6" t="n"/>
-      <c r="BK128" s="6" t="n"/>
-      <c r="BS128" s="6" t="n"/>
-      <c r="CF128" s="6" t="n"/>
-      <c r="CT128" s="6" t="n"/>
-      <c r="DI128" s="6" t="n"/>
+      <c r="L128" s="1" t="n"/>
+      <c r="M128" s="24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="n"/>
+      <c r="O128" s="2" t="n"/>
+      <c r="P128" s="1" t="n"/>
+      <c r="Q128" s="2" t="n"/>
+      <c r="R128" s="2" t="n"/>
+      <c r="S128" s="2" t="n"/>
+      <c r="T128" s="2" t="n"/>
+      <c r="U128" s="2" t="n"/>
+      <c r="V128" s="2" t="n"/>
+      <c r="W128" s="2" t="n"/>
+      <c r="X128" s="2" t="n"/>
+      <c r="Y128" s="2" t="n"/>
+      <c r="Z128" s="2" t="n"/>
+      <c r="AA128" s="2" t="n"/>
+      <c r="AB128" s="2" t="n"/>
+      <c r="AC128" s="2" t="n"/>
+      <c r="AD128" s="2" t="n"/>
+      <c r="AE128" s="2" t="n"/>
+      <c r="AF128" s="2" t="n"/>
+      <c r="AG128" s="2" t="n"/>
+      <c r="AH128" s="2" t="n"/>
+      <c r="AI128" s="2" t="n"/>
+      <c r="AJ128" s="2" t="n"/>
+      <c r="AK128" s="2" t="n"/>
+      <c r="AL128" s="2" t="n"/>
+      <c r="AM128" s="2" t="n"/>
+      <c r="AN128" s="2" t="n"/>
+      <c r="AO128" s="2" t="n"/>
+      <c r="AP128" s="2" t="n"/>
+      <c r="AQ128" s="2" t="n"/>
+      <c r="AR128" s="2" t="n"/>
+      <c r="AS128" s="2" t="n"/>
+      <c r="AT128" s="2" t="n"/>
+      <c r="AU128" s="2" t="n"/>
+      <c r="AV128" s="2" t="n"/>
+      <c r="AW128" s="2" t="n"/>
+      <c r="AX128" s="2" t="n"/>
+      <c r="AY128" s="2" t="n"/>
+      <c r="AZ128" s="2" t="n"/>
+      <c r="BA128" s="2" t="n"/>
+      <c r="BB128" s="2" t="n"/>
+      <c r="BC128" s="2" t="n"/>
+      <c r="BD128" s="2" t="n"/>
+      <c r="BE128" s="2" t="n"/>
+      <c r="BF128" s="2" t="n"/>
+      <c r="BG128" s="2" t="n"/>
+      <c r="BH128" s="2" t="n"/>
+      <c r="BI128" s="2" t="n"/>
+      <c r="BJ128" s="2" t="n"/>
+      <c r="BK128" s="1" t="n"/>
+      <c r="BL128" s="2" t="n"/>
+      <c r="BM128" s="2" t="n"/>
+      <c r="BN128" s="2" t="n"/>
+      <c r="BO128" s="2" t="n"/>
+      <c r="BP128" s="2" t="n"/>
+      <c r="BQ128" s="2" t="n"/>
+      <c r="BR128" s="2" t="n"/>
+      <c r="BS128" s="1" t="n"/>
+      <c r="BT128" s="2" t="n"/>
+      <c r="BU128" s="2" t="n"/>
+      <c r="BV128" s="2" t="n"/>
+      <c r="BW128" s="2" t="n"/>
+      <c r="BX128" s="2" t="n"/>
+      <c r="BY128" s="2" t="n"/>
+      <c r="BZ128" s="2" t="n"/>
+      <c r="CA128" s="2" t="n"/>
+      <c r="CB128" s="2" t="n"/>
+      <c r="CC128" s="2" t="n"/>
+      <c r="CD128" s="2" t="n"/>
+      <c r="CE128" s="2" t="n"/>
+      <c r="CF128" s="1" t="n"/>
+      <c r="CG128" s="2" t="n"/>
+      <c r="CH128" s="2" t="n"/>
+      <c r="CI128" s="2" t="n"/>
+      <c r="CJ128" s="2" t="n"/>
+      <c r="CK128" s="2" t="n"/>
+      <c r="CL128" s="2" t="n"/>
+      <c r="CM128" s="2" t="n"/>
+      <c r="CN128" s="2" t="n"/>
+      <c r="CO128" s="2" t="n"/>
+      <c r="CP128" s="2" t="n"/>
+      <c r="CQ128" s="2" t="n"/>
+      <c r="CR128" s="2" t="n"/>
+      <c r="CS128" s="2" t="n"/>
+      <c r="CT128" s="1" t="n"/>
+      <c r="CU128" s="2" t="n"/>
+      <c r="CV128" s="2" t="n"/>
+      <c r="CW128" s="2" t="n"/>
+      <c r="CX128" s="2" t="n"/>
+      <c r="CY128" s="2" t="n"/>
+      <c r="CZ128" s="2" t="n"/>
+      <c r="DA128" s="2" t="n"/>
+      <c r="DB128" s="2" t="n"/>
+      <c r="DC128" s="2" t="n"/>
+      <c r="DD128" s="2" t="n"/>
+      <c r="DE128" s="2" t="n"/>
+      <c r="DF128" s="2" t="n"/>
+      <c r="DG128" s="2" t="n"/>
+      <c r="DH128" s="2" t="n"/>
+      <c r="DI128" s="1" t="n"/>
     </row>
     <row r="129" ht="4.96" customHeight="1">
-      <c r="L129" s="6" t="n"/>
-      <c r="M129" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="P129" s="6" t="n"/>
-      <c r="BK129" s="6" t="n"/>
-      <c r="BS129" s="6" t="n"/>
-      <c r="CF129" s="6" t="n"/>
-      <c r="CT129" s="6" t="n"/>
-      <c r="DI129" s="6" t="n"/>
+      <c r="L129" s="5" t="n"/>
+      <c r="P129" s="5" t="n"/>
+      <c r="BK129" s="5" t="n"/>
+      <c r="BS129" s="5" t="n"/>
+      <c r="CF129" s="5" t="n"/>
+      <c r="CT129" s="5" t="n"/>
+      <c r="DI129" s="5" t="n"/>
     </row>
     <row r="130" ht="4.96" customHeight="1">
-      <c r="L130" s="6" t="n"/>
-      <c r="P130" s="6" t="n"/>
-      <c r="BK130" s="6" t="n"/>
-      <c r="BS130" s="6" t="n"/>
-      <c r="CF130" s="6" t="n"/>
-      <c r="CT130" s="6" t="n"/>
-      <c r="DI130" s="6" t="n"/>
+      <c r="L130" s="5" t="n"/>
+      <c r="P130" s="5" t="n"/>
+      <c r="BK130" s="5" t="n"/>
+      <c r="BS130" s="5" t="n"/>
+      <c r="CF130" s="5" t="n"/>
+      <c r="CT130" s="5" t="n"/>
+      <c r="DI130" s="5" t="n"/>
     </row>
     <row r="131" ht="4.96" customHeight="1">
-      <c r="L131" s="6" t="n"/>
-      <c r="P131" s="6" t="n"/>
-      <c r="BK131" s="6" t="n"/>
-      <c r="BS131" s="6" t="n"/>
-      <c r="CF131" s="6" t="n"/>
-      <c r="CT131" s="6" t="n"/>
-      <c r="DI131" s="6" t="n"/>
+      <c r="L131" s="1" t="n"/>
+      <c r="M131" s="2" t="n"/>
+      <c r="N131" s="2" t="n"/>
+      <c r="O131" s="2" t="n"/>
+      <c r="P131" s="1" t="n"/>
+      <c r="Q131" s="2" t="n"/>
+      <c r="R131" s="2" t="n"/>
+      <c r="S131" s="2" t="n"/>
+      <c r="T131" s="2" t="n"/>
+      <c r="U131" s="2" t="n"/>
+      <c r="V131" s="2" t="n"/>
+      <c r="W131" s="2" t="n"/>
+      <c r="X131" s="2" t="n"/>
+      <c r="Y131" s="2" t="n"/>
+      <c r="Z131" s="2" t="n"/>
+      <c r="AA131" s="2" t="n"/>
+      <c r="AB131" s="2" t="n"/>
+      <c r="AC131" s="2" t="n"/>
+      <c r="AD131" s="2" t="n"/>
+      <c r="AE131" s="2" t="n"/>
+      <c r="AF131" s="2" t="n"/>
+      <c r="AG131" s="2" t="n"/>
+      <c r="AH131" s="2" t="n"/>
+      <c r="AI131" s="2" t="n"/>
+      <c r="AJ131" s="2" t="n"/>
+      <c r="AK131" s="2" t="n"/>
+      <c r="AL131" s="2" t="n"/>
+      <c r="AM131" s="2" t="n"/>
+      <c r="AN131" s="2" t="n"/>
+      <c r="AO131" s="2" t="n"/>
+      <c r="AP131" s="2" t="n"/>
+      <c r="AQ131" s="2" t="n"/>
+      <c r="AR131" s="2" t="n"/>
+      <c r="AS131" s="2" t="n"/>
+      <c r="AT131" s="2" t="n"/>
+      <c r="AU131" s="2" t="n"/>
+      <c r="AV131" s="2" t="n"/>
+      <c r="AW131" s="2" t="n"/>
+      <c r="AX131" s="2" t="n"/>
+      <c r="AY131" s="2" t="n"/>
+      <c r="AZ131" s="2" t="n"/>
+      <c r="BA131" s="2" t="n"/>
+      <c r="BB131" s="2" t="n"/>
+      <c r="BC131" s="2" t="n"/>
+      <c r="BD131" s="2" t="n"/>
+      <c r="BE131" s="2" t="n"/>
+      <c r="BF131" s="2" t="n"/>
+      <c r="BG131" s="2" t="n"/>
+      <c r="BH131" s="2" t="n"/>
+      <c r="BI131" s="2" t="n"/>
+      <c r="BJ131" s="2" t="n"/>
+      <c r="BK131" s="1" t="n"/>
+      <c r="BL131" s="2" t="n"/>
+      <c r="BM131" s="2" t="n"/>
+      <c r="BN131" s="2" t="n"/>
+      <c r="BO131" s="2" t="n"/>
+      <c r="BP131" s="2" t="n"/>
+      <c r="BQ131" s="2" t="n"/>
+      <c r="BR131" s="2" t="n"/>
+      <c r="BS131" s="1" t="n"/>
+      <c r="BT131" s="2" t="n"/>
+      <c r="BU131" s="2" t="n"/>
+      <c r="BV131" s="2" t="n"/>
+      <c r="BW131" s="2" t="n"/>
+      <c r="BX131" s="2" t="n"/>
+      <c r="BY131" s="2" t="n"/>
+      <c r="BZ131" s="2" t="n"/>
+      <c r="CA131" s="2" t="n"/>
+      <c r="CB131" s="2" t="n"/>
+      <c r="CC131" s="2" t="n"/>
+      <c r="CD131" s="2" t="n"/>
+      <c r="CE131" s="2" t="n"/>
+      <c r="CF131" s="1" t="n"/>
+      <c r="CG131" s="2" t="n"/>
+      <c r="CH131" s="2" t="n"/>
+      <c r="CI131" s="2" t="n"/>
+      <c r="CJ131" s="2" t="n"/>
+      <c r="CK131" s="2" t="n"/>
+      <c r="CL131" s="2" t="n"/>
+      <c r="CM131" s="2" t="n"/>
+      <c r="CN131" s="2" t="n"/>
+      <c r="CO131" s="2" t="n"/>
+      <c r="CP131" s="2" t="n"/>
+      <c r="CQ131" s="2" t="n"/>
+      <c r="CR131" s="2" t="n"/>
+      <c r="CS131" s="2" t="n"/>
+      <c r="CT131" s="1" t="n"/>
+      <c r="CU131" s="2" t="n"/>
+      <c r="CV131" s="2" t="n"/>
+      <c r="CW131" s="2" t="n"/>
+      <c r="CX131" s="2" t="n"/>
+      <c r="CY131" s="2" t="n"/>
+      <c r="CZ131" s="2" t="n"/>
+      <c r="DA131" s="2" t="n"/>
+      <c r="DB131" s="2" t="n"/>
+      <c r="DC131" s="2" t="n"/>
+      <c r="DD131" s="2" t="n"/>
+      <c r="DE131" s="2" t="n"/>
+      <c r="DF131" s="2" t="n"/>
+      <c r="DG131" s="2" t="n"/>
+      <c r="DH131" s="2" t="n"/>
+      <c r="DI131" s="1" t="n"/>
     </row>
     <row r="132" ht="4.96" customHeight="1">
-      <c r="L132" s="6" t="n"/>
-      <c r="M132" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="P132" s="6" t="n"/>
-      <c r="BK132" s="6" t="n"/>
-      <c r="BS132" s="6" t="n"/>
-      <c r="CF132" s="6" t="n"/>
-      <c r="CT132" s="6" t="n"/>
-      <c r="DI132" s="6" t="n"/>
+      <c r="L132" s="5" t="n"/>
+      <c r="M132" s="22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P132" s="5" t="n"/>
+      <c r="BK132" s="5" t="n"/>
+      <c r="BS132" s="5" t="n"/>
+      <c r="CF132" s="5" t="n"/>
+      <c r="CT132" s="5" t="n"/>
+      <c r="DI132" s="5" t="n"/>
     </row>
     <row r="133" ht="4.96" customHeight="1">
-      <c r="L133" s="6" t="n"/>
-      <c r="P133" s="6" t="n"/>
-      <c r="BK133" s="6" t="n"/>
-      <c r="BS133" s="6" t="n"/>
-      <c r="CF133" s="6" t="n"/>
-      <c r="CT133" s="6" t="n"/>
-      <c r="DI133" s="6" t="n"/>
+      <c r="L133" s="5" t="n"/>
+      <c r="P133" s="5" t="n"/>
+      <c r="BK133" s="5" t="n"/>
+      <c r="BS133" s="5" t="n"/>
+      <c r="CF133" s="5" t="n"/>
+      <c r="CT133" s="5" t="n"/>
+      <c r="DI133" s="5" t="n"/>
     </row>
     <row r="134" ht="4.96" customHeight="1">
-      <c r="L134" s="6" t="n"/>
-      <c r="P134" s="6" t="n"/>
-      <c r="BK134" s="6" t="n"/>
-      <c r="BS134" s="6" t="n"/>
-      <c r="CF134" s="6" t="n"/>
-      <c r="CT134" s="6" t="n"/>
-      <c r="DI134" s="6" t="n"/>
+      <c r="K134" s="2" t="n"/>
+      <c r="L134" s="1" t="n"/>
+      <c r="M134" s="2" t="n"/>
+      <c r="N134" s="2" t="n"/>
+      <c r="O134" s="2" t="n"/>
+      <c r="P134" s="1" t="n"/>
+      <c r="Q134" s="2" t="n"/>
+      <c r="R134" s="2" t="n"/>
+      <c r="S134" s="2" t="n"/>
+      <c r="T134" s="2" t="n"/>
+      <c r="U134" s="2" t="n"/>
+      <c r="V134" s="2" t="n"/>
+      <c r="W134" s="2" t="n"/>
+      <c r="X134" s="2" t="n"/>
+      <c r="Y134" s="2" t="n"/>
+      <c r="Z134" s="2" t="n"/>
+      <c r="AA134" s="2" t="n"/>
+      <c r="AB134" s="2" t="n"/>
+      <c r="AC134" s="2" t="n"/>
+      <c r="AD134" s="2" t="n"/>
+      <c r="AE134" s="2" t="n"/>
+      <c r="AF134" s="2" t="n"/>
+      <c r="AG134" s="2" t="n"/>
+      <c r="AH134" s="2" t="n"/>
+      <c r="AI134" s="2" t="n"/>
+      <c r="AJ134" s="2" t="n"/>
+      <c r="AK134" s="2" t="n"/>
+      <c r="AL134" s="2" t="n"/>
+      <c r="AM134" s="2" t="n"/>
+      <c r="AN134" s="2" t="n"/>
+      <c r="AO134" s="2" t="n"/>
+      <c r="AP134" s="2" t="n"/>
+      <c r="AQ134" s="2" t="n"/>
+      <c r="AR134" s="2" t="n"/>
+      <c r="AS134" s="2" t="n"/>
+      <c r="AT134" s="2" t="n"/>
+      <c r="AU134" s="2" t="n"/>
+      <c r="AV134" s="2" t="n"/>
+      <c r="AW134" s="2" t="n"/>
+      <c r="AX134" s="2" t="n"/>
+      <c r="AY134" s="2" t="n"/>
+      <c r="AZ134" s="2" t="n"/>
+      <c r="BA134" s="2" t="n"/>
+      <c r="BB134" s="2" t="n"/>
+      <c r="BC134" s="2" t="n"/>
+      <c r="BD134" s="2" t="n"/>
+      <c r="BE134" s="2" t="n"/>
+      <c r="BF134" s="2" t="n"/>
+      <c r="BG134" s="2" t="n"/>
+      <c r="BH134" s="2" t="n"/>
+      <c r="BI134" s="2" t="n"/>
+      <c r="BJ134" s="2" t="n"/>
+      <c r="BK134" s="1" t="n"/>
+      <c r="BL134" s="2" t="n"/>
+      <c r="BM134" s="2" t="n"/>
+      <c r="BN134" s="2" t="n"/>
+      <c r="BO134" s="2" t="n"/>
+      <c r="BP134" s="2" t="n"/>
+      <c r="BQ134" s="2" t="n"/>
+      <c r="BR134" s="2" t="n"/>
+      <c r="BS134" s="1" t="n"/>
+      <c r="BT134" s="2" t="n"/>
+      <c r="BU134" s="2" t="n"/>
+      <c r="BV134" s="2" t="n"/>
+      <c r="BW134" s="2" t="n"/>
+      <c r="BX134" s="2" t="n"/>
+      <c r="BY134" s="2" t="n"/>
+      <c r="BZ134" s="2" t="n"/>
+      <c r="CA134" s="2" t="n"/>
+      <c r="CB134" s="2" t="n"/>
+      <c r="CC134" s="2" t="n"/>
+      <c r="CD134" s="2" t="n"/>
+      <c r="CE134" s="2" t="n"/>
+      <c r="CF134" s="1" t="n"/>
+      <c r="CG134" s="2" t="n"/>
+      <c r="CH134" s="2" t="n"/>
+      <c r="CI134" s="2" t="n"/>
+      <c r="CJ134" s="2" t="n"/>
+      <c r="CK134" s="2" t="n"/>
+      <c r="CL134" s="2" t="n"/>
+      <c r="CM134" s="2" t="n"/>
+      <c r="CN134" s="2" t="n"/>
+      <c r="CO134" s="2" t="n"/>
+      <c r="CP134" s="2" t="n"/>
+      <c r="CQ134" s="2" t="n"/>
+      <c r="CR134" s="2" t="n"/>
+      <c r="CS134" s="2" t="n"/>
+      <c r="CT134" s="1" t="n"/>
+      <c r="CU134" s="2" t="n"/>
+      <c r="CV134" s="2" t="n"/>
+      <c r="CW134" s="2" t="n"/>
+      <c r="CX134" s="2" t="n"/>
+      <c r="CY134" s="2" t="n"/>
+      <c r="CZ134" s="2" t="n"/>
+      <c r="DA134" s="2" t="n"/>
+      <c r="DB134" s="2" t="n"/>
+      <c r="DC134" s="2" t="n"/>
+      <c r="DD134" s="2" t="n"/>
+      <c r="DE134" s="2" t="n"/>
+      <c r="DF134" s="2" t="n"/>
+      <c r="DG134" s="2" t="n"/>
+      <c r="DH134" s="2" t="n"/>
+      <c r="DI134" s="1" t="n"/>
     </row>
     <row r="135" ht="4.96" customHeight="1">
-      <c r="L135" s="6" t="n"/>
-      <c r="M135" s="19" t="n">
-        <v>17</v>
-      </c>
-      <c r="P135" s="6" t="n"/>
-      <c r="BK135" s="6" t="n"/>
-      <c r="BS135" s="6" t="n"/>
-      <c r="CF135" s="6" t="n"/>
-      <c r="CT135" s="6" t="n"/>
-      <c r="DI135" s="6" t="n"/>
+      <c r="L135" s="5" t="n"/>
+      <c r="M135" s="22" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P135" s="5" t="n"/>
+      <c r="BK135" s="5" t="n"/>
+      <c r="BS135" s="5" t="n"/>
+      <c r="CF135" s="5" t="n"/>
+      <c r="CT135" s="5" t="n"/>
+      <c r="DI135" s="5" t="n"/>
     </row>
     <row r="136" ht="4.96" customHeight="1">
-      <c r="L136" s="6" t="n"/>
-      <c r="P136" s="6" t="n"/>
-      <c r="BK136" s="6" t="n"/>
-      <c r="BS136" s="6" t="n"/>
-      <c r="CF136" s="6" t="n"/>
-      <c r="CT136" s="6" t="n"/>
-      <c r="DI136" s="6" t="n"/>
+      <c r="L136" s="5" t="n"/>
+      <c r="P136" s="5" t="n"/>
+      <c r="BK136" s="5" t="n"/>
+      <c r="BS136" s="5" t="n"/>
+      <c r="CF136" s="5" t="n"/>
+      <c r="CT136" s="5" t="n"/>
+      <c r="DI136" s="5" t="n"/>
     </row>
     <row r="137" ht="4.96" customHeight="1">
-      <c r="L137" s="6" t="n"/>
-      <c r="P137" s="6" t="n"/>
-      <c r="BK137" s="6" t="n"/>
-      <c r="BS137" s="6" t="n"/>
-      <c r="CF137" s="6" t="n"/>
-      <c r="CT137" s="6" t="n"/>
-      <c r="DI137" s="6" t="n"/>
+      <c r="L137" s="5" t="n"/>
+      <c r="P137" s="5" t="n"/>
+      <c r="BK137" s="5" t="n"/>
+      <c r="BS137" s="5" t="n"/>
+      <c r="CF137" s="5" t="n"/>
+      <c r="CT137" s="5" t="n"/>
+      <c r="DI137" s="5" t="n"/>
     </row>
     <row r="138" ht="4.96" customHeight="1">
-      <c r="L138" s="6" t="n"/>
-      <c r="P138" s="6" t="n"/>
-      <c r="BK138" s="6" t="n"/>
-      <c r="BS138" s="6" t="n"/>
-      <c r="CF138" s="6" t="n"/>
-      <c r="CT138" s="6" t="n"/>
-      <c r="DI138" s="6" t="n"/>
+      <c r="K138" s="2" t="n"/>
+      <c r="L138" s="1" t="n"/>
+      <c r="M138" s="2" t="n"/>
+      <c r="N138" s="2" t="n"/>
+      <c r="O138" s="2" t="n"/>
+      <c r="P138" s="1" t="n"/>
+      <c r="Q138" s="2" t="n"/>
+      <c r="R138" s="2" t="n"/>
+      <c r="S138" s="2" t="n"/>
+      <c r="T138" s="2" t="n"/>
+      <c r="U138" s="2" t="n"/>
+      <c r="V138" s="2" t="n"/>
+      <c r="W138" s="2" t="n"/>
+      <c r="X138" s="2" t="n"/>
+      <c r="Y138" s="2" t="n"/>
+      <c r="Z138" s="2" t="n"/>
+      <c r="AA138" s="2" t="n"/>
+      <c r="AB138" s="2" t="n"/>
+      <c r="AC138" s="2" t="n"/>
+      <c r="AD138" s="2" t="n"/>
+      <c r="AE138" s="2" t="n"/>
+      <c r="AF138" s="2" t="n"/>
+      <c r="AG138" s="2" t="n"/>
+      <c r="AH138" s="2" t="n"/>
+      <c r="AI138" s="2" t="n"/>
+      <c r="AJ138" s="2" t="n"/>
+      <c r="AK138" s="2" t="n"/>
+      <c r="AL138" s="2" t="n"/>
+      <c r="AM138" s="2" t="n"/>
+      <c r="AN138" s="2" t="n"/>
+      <c r="AO138" s="2" t="n"/>
+      <c r="AP138" s="2" t="n"/>
+      <c r="AQ138" s="2" t="n"/>
+      <c r="AR138" s="2" t="n"/>
+      <c r="AS138" s="2" t="n"/>
+      <c r="AT138" s="2" t="n"/>
+      <c r="AU138" s="2" t="n"/>
+      <c r="AV138" s="2" t="n"/>
+      <c r="AW138" s="2" t="n"/>
+      <c r="AX138" s="2" t="n"/>
+      <c r="AY138" s="2" t="n"/>
+      <c r="AZ138" s="2" t="n"/>
+      <c r="BA138" s="2" t="n"/>
+      <c r="BB138" s="2" t="n"/>
+      <c r="BC138" s="2" t="n"/>
+      <c r="BD138" s="2" t="n"/>
+      <c r="BE138" s="2" t="n"/>
+      <c r="BF138" s="2" t="n"/>
+      <c r="BG138" s="2" t="n"/>
+      <c r="BH138" s="2" t="n"/>
+      <c r="BI138" s="2" t="n"/>
+      <c r="BJ138" s="2" t="n"/>
+      <c r="BK138" s="1" t="n"/>
+      <c r="BL138" s="2" t="n"/>
+      <c r="BM138" s="2" t="n"/>
+      <c r="BN138" s="2" t="n"/>
+      <c r="BO138" s="2" t="n"/>
+      <c r="BP138" s="2" t="n"/>
+      <c r="BQ138" s="2" t="n"/>
+      <c r="BR138" s="2" t="n"/>
+      <c r="BS138" s="1" t="n"/>
+      <c r="BT138" s="2" t="n"/>
+      <c r="BU138" s="2" t="n"/>
+      <c r="BV138" s="2" t="n"/>
+      <c r="BW138" s="2" t="n"/>
+      <c r="BX138" s="2" t="n"/>
+      <c r="BY138" s="2" t="n"/>
+      <c r="BZ138" s="2" t="n"/>
+      <c r="CA138" s="2" t="n"/>
+      <c r="CB138" s="2" t="n"/>
+      <c r="CC138" s="2" t="n"/>
+      <c r="CD138" s="2" t="n"/>
+      <c r="CE138" s="2" t="n"/>
+      <c r="CF138" s="1" t="n"/>
+      <c r="CG138" s="2" t="n"/>
+      <c r="CH138" s="2" t="n"/>
+      <c r="CI138" s="2" t="n"/>
+      <c r="CJ138" s="2" t="n"/>
+      <c r="CK138" s="2" t="n"/>
+      <c r="CL138" s="2" t="n"/>
+      <c r="CM138" s="2" t="n"/>
+      <c r="CN138" s="2" t="n"/>
+      <c r="CO138" s="2" t="n"/>
+      <c r="CP138" s="2" t="n"/>
+      <c r="CQ138" s="2" t="n"/>
+      <c r="CR138" s="2" t="n"/>
+      <c r="CS138" s="2" t="n"/>
+      <c r="CT138" s="1" t="n"/>
+      <c r="CU138" s="2" t="n"/>
+      <c r="CV138" s="2" t="n"/>
+      <c r="CW138" s="2" t="n"/>
+      <c r="CX138" s="2" t="n"/>
+      <c r="CY138" s="2" t="n"/>
+      <c r="CZ138" s="2" t="n"/>
+      <c r="DA138" s="2" t="n"/>
+      <c r="DB138" s="2" t="n"/>
+      <c r="DC138" s="2" t="n"/>
+      <c r="DD138" s="2" t="n"/>
+      <c r="DE138" s="2" t="n"/>
+      <c r="DF138" s="2" t="n"/>
+      <c r="DG138" s="2" t="n"/>
+      <c r="DH138" s="2" t="n"/>
+      <c r="DI138" s="1" t="n"/>
     </row>
     <row r="139" ht="4.96" customHeight="1">
-      <c r="L139" s="6" t="n"/>
-      <c r="M139" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="P139" s="6" t="n"/>
-      <c r="BK139" s="6" t="n"/>
-      <c r="BS139" s="6" t="n"/>
-      <c r="CF139" s="6" t="n"/>
-      <c r="CT139" s="6" t="n"/>
-      <c r="DI139" s="6" t="n"/>
+      <c r="L139" s="5" t="n"/>
+      <c r="M139" s="22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P139" s="5" t="n"/>
+      <c r="BK139" s="5" t="n"/>
+      <c r="BS139" s="5" t="n"/>
+      <c r="CF139" s="5" t="n"/>
+      <c r="CT139" s="5" t="n"/>
+      <c r="DI139" s="5" t="n"/>
     </row>
     <row r="140" ht="4.96" customHeight="1">
-      <c r="L140" s="6" t="n"/>
-      <c r="P140" s="6" t="n"/>
-      <c r="BK140" s="6" t="n"/>
-      <c r="BS140" s="6" t="n"/>
-      <c r="CF140" s="6" t="n"/>
-      <c r="CT140" s="6" t="n"/>
-      <c r="DI140" s="6" t="n"/>
+      <c r="L140" s="5" t="n"/>
+      <c r="P140" s="5" t="n"/>
+      <c r="BK140" s="5" t="n"/>
+      <c r="BS140" s="5" t="n"/>
+      <c r="CF140" s="5" t="n"/>
+      <c r="CT140" s="5" t="n"/>
+      <c r="DI140" s="5" t="n"/>
     </row>
     <row r="141" ht="4.96" customHeight="1">
-      <c r="L141" s="6" t="n"/>
-      <c r="P141" s="6" t="n"/>
-      <c r="BK141" s="6" t="n"/>
-      <c r="BS141" s="6" t="n"/>
-      <c r="CF141" s="6" t="n"/>
-      <c r="CT141" s="6" t="n"/>
-      <c r="DI141" s="6" t="n"/>
+      <c r="L141" s="1" t="n"/>
+      <c r="M141" s="2" t="n"/>
+      <c r="N141" s="2" t="n"/>
+      <c r="O141" s="2" t="n"/>
+      <c r="P141" s="1" t="n"/>
+      <c r="Q141" s="2" t="n"/>
+      <c r="R141" s="2" t="n"/>
+      <c r="S141" s="2" t="n"/>
+      <c r="T141" s="2" t="n"/>
+      <c r="U141" s="2" t="n"/>
+      <c r="V141" s="2" t="n"/>
+      <c r="W141" s="2" t="n"/>
+      <c r="X141" s="2" t="n"/>
+      <c r="Y141" s="2" t="n"/>
+      <c r="Z141" s="2" t="n"/>
+      <c r="AA141" s="2" t="n"/>
+      <c r="AB141" s="2" t="n"/>
+      <c r="AC141" s="2" t="n"/>
+      <c r="AD141" s="2" t="n"/>
+      <c r="AE141" s="2" t="n"/>
+      <c r="AF141" s="2" t="n"/>
+      <c r="AG141" s="2" t="n"/>
+      <c r="AH141" s="2" t="n"/>
+      <c r="AI141" s="2" t="n"/>
+      <c r="AJ141" s="2" t="n"/>
+      <c r="AK141" s="2" t="n"/>
+      <c r="AL141" s="2" t="n"/>
+      <c r="AM141" s="2" t="n"/>
+      <c r="AN141" s="2" t="n"/>
+      <c r="AO141" s="2" t="n"/>
+      <c r="AP141" s="2" t="n"/>
+      <c r="AQ141" s="2" t="n"/>
+      <c r="AR141" s="2" t="n"/>
+      <c r="AS141" s="2" t="n"/>
+      <c r="AT141" s="2" t="n"/>
+      <c r="AU141" s="2" t="n"/>
+      <c r="AV141" s="2" t="n"/>
+      <c r="AW141" s="2" t="n"/>
+      <c r="AX141" s="2" t="n"/>
+      <c r="AY141" s="2" t="n"/>
+      <c r="AZ141" s="2" t="n"/>
+      <c r="BA141" s="2" t="n"/>
+      <c r="BB141" s="2" t="n"/>
+      <c r="BC141" s="2" t="n"/>
+      <c r="BD141" s="2" t="n"/>
+      <c r="BE141" s="2" t="n"/>
+      <c r="BF141" s="2" t="n"/>
+      <c r="BG141" s="2" t="n"/>
+      <c r="BH141" s="2" t="n"/>
+      <c r="BI141" s="2" t="n"/>
+      <c r="BJ141" s="2" t="n"/>
+      <c r="BK141" s="1" t="n"/>
+      <c r="BL141" s="2" t="n"/>
+      <c r="BM141" s="2" t="n"/>
+      <c r="BN141" s="2" t="n"/>
+      <c r="BO141" s="2" t="n"/>
+      <c r="BP141" s="2" t="n"/>
+      <c r="BQ141" s="2" t="n"/>
+      <c r="BR141" s="2" t="n"/>
+      <c r="BS141" s="1" t="n"/>
+      <c r="BT141" s="2" t="n"/>
+      <c r="BU141" s="2" t="n"/>
+      <c r="BV141" s="2" t="n"/>
+      <c r="BW141" s="2" t="n"/>
+      <c r="BX141" s="2" t="n"/>
+      <c r="BY141" s="2" t="n"/>
+      <c r="BZ141" s="2" t="n"/>
+      <c r="CA141" s="2" t="n"/>
+      <c r="CB141" s="2" t="n"/>
+      <c r="CC141" s="2" t="n"/>
+      <c r="CD141" s="2" t="n"/>
+      <c r="CE141" s="2" t="n"/>
+      <c r="CF141" s="1" t="n"/>
+      <c r="CG141" s="2" t="n"/>
+      <c r="CH141" s="2" t="n"/>
+      <c r="CI141" s="2" t="n"/>
+      <c r="CJ141" s="2" t="n"/>
+      <c r="CK141" s="2" t="n"/>
+      <c r="CL141" s="2" t="n"/>
+      <c r="CM141" s="2" t="n"/>
+      <c r="CN141" s="2" t="n"/>
+      <c r="CO141" s="2" t="n"/>
+      <c r="CP141" s="2" t="n"/>
+      <c r="CQ141" s="2" t="n"/>
+      <c r="CR141" s="2" t="n"/>
+      <c r="CS141" s="2" t="n"/>
+      <c r="CT141" s="1" t="n"/>
+      <c r="CU141" s="2" t="n"/>
+      <c r="CV141" s="2" t="n"/>
+      <c r="CW141" s="2" t="n"/>
+      <c r="CX141" s="2" t="n"/>
+      <c r="CY141" s="2" t="n"/>
+      <c r="CZ141" s="2" t="n"/>
+      <c r="DA141" s="2" t="n"/>
+      <c r="DB141" s="2" t="n"/>
+      <c r="DC141" s="2" t="n"/>
+      <c r="DD141" s="2" t="n"/>
+      <c r="DE141" s="2" t="n"/>
+      <c r="DF141" s="2" t="n"/>
+      <c r="DG141" s="2" t="n"/>
+      <c r="DH141" s="2" t="n"/>
+      <c r="DI141" s="1" t="n"/>
     </row>
     <row r="142" ht="4.96" customHeight="1">
-      <c r="L142" s="6" t="n"/>
-      <c r="M142" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="P142" s="6" t="n"/>
-      <c r="BK142" s="6" t="n"/>
-      <c r="BS142" s="6" t="n"/>
-      <c r="CF142" s="6" t="n"/>
-      <c r="CT142" s="6" t="n"/>
-      <c r="DI142" s="6" t="n"/>
+      <c r="L142" s="5" t="n"/>
+      <c r="M142" s="22" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P142" s="5" t="n"/>
+      <c r="BK142" s="5" t="n"/>
+      <c r="BS142" s="5" t="n"/>
+      <c r="CF142" s="5" t="n"/>
+      <c r="CT142" s="5" t="n"/>
+      <c r="DI142" s="5" t="n"/>
     </row>
     <row r="143" ht="4.96" customHeight="1">
-      <c r="L143" s="6" t="n"/>
-      <c r="P143" s="6" t="n"/>
-      <c r="BK143" s="6" t="n"/>
-      <c r="BS143" s="6" t="n"/>
-      <c r="CF143" s="6" t="n"/>
-      <c r="CT143" s="6" t="n"/>
-      <c r="DI143" s="6" t="n"/>
+      <c r="L143" s="5" t="n"/>
+      <c r="P143" s="5" t="n"/>
+      <c r="BK143" s="5" t="n"/>
+      <c r="BS143" s="5" t="n"/>
+      <c r="CF143" s="5" t="n"/>
+      <c r="CT143" s="5" t="n"/>
+      <c r="DI143" s="5" t="n"/>
     </row>
     <row r="144" ht="4.96" customHeight="1">
-      <c r="L144" s="6" t="n"/>
-      <c r="P144" s="6" t="n"/>
-      <c r="BK144" s="6" t="n"/>
-      <c r="BS144" s="6" t="n"/>
-      <c r="CF144" s="6" t="n"/>
-      <c r="CT144" s="6" t="n"/>
-      <c r="DI144" s="6" t="n"/>
+      <c r="L144" s="5" t="n"/>
+      <c r="P144" s="5" t="n"/>
+      <c r="BK144" s="5" t="n"/>
+      <c r="BS144" s="5" t="n"/>
+      <c r="CF144" s="5" t="n"/>
+      <c r="CT144" s="5" t="n"/>
+      <c r="DI144" s="5" t="n"/>
     </row>
     <row r="145" ht="4.96" customHeight="1">
-      <c r="L145" s="6" t="n"/>
-      <c r="P145" s="6" t="n"/>
-      <c r="BK145" s="6" t="n"/>
-      <c r="BS145" s="6" t="n"/>
-      <c r="CF145" s="6" t="n"/>
-      <c r="CT145" s="6" t="n"/>
-      <c r="DI145" s="6" t="n"/>
+      <c r="L145" s="1" t="n"/>
+      <c r="M145" s="24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="n"/>
+      <c r="O145" s="2" t="n"/>
+      <c r="P145" s="1" t="n"/>
+      <c r="Q145" s="2" t="n"/>
+      <c r="R145" s="2" t="n"/>
+      <c r="S145" s="2" t="n"/>
+      <c r="T145" s="2" t="n"/>
+      <c r="U145" s="2" t="n"/>
+      <c r="V145" s="2" t="n"/>
+      <c r="W145" s="2" t="n"/>
+      <c r="X145" s="2" t="n"/>
+      <c r="Y145" s="2" t="n"/>
+      <c r="Z145" s="2" t="n"/>
+      <c r="AA145" s="2" t="n"/>
+      <c r="AB145" s="2" t="n"/>
+      <c r="AC145" s="2" t="n"/>
+      <c r="AD145" s="2" t="n"/>
+      <c r="AE145" s="2" t="n"/>
+      <c r="AF145" s="2" t="n"/>
+      <c r="AG145" s="2" t="n"/>
+      <c r="AH145" s="2" t="n"/>
+      <c r="AI145" s="2" t="n"/>
+      <c r="AJ145" s="2" t="n"/>
+      <c r="AK145" s="2" t="n"/>
+      <c r="AL145" s="2" t="n"/>
+      <c r="AM145" s="2" t="n"/>
+      <c r="AN145" s="2" t="n"/>
+      <c r="AO145" s="2" t="n"/>
+      <c r="AP145" s="2" t="n"/>
+      <c r="AQ145" s="2" t="n"/>
+      <c r="AR145" s="2" t="n"/>
+      <c r="AS145" s="2" t="n"/>
+      <c r="AT145" s="2" t="n"/>
+      <c r="AU145" s="2" t="n"/>
+      <c r="AV145" s="2" t="n"/>
+      <c r="AW145" s="2" t="n"/>
+      <c r="AX145" s="2" t="n"/>
+      <c r="AY145" s="2" t="n"/>
+      <c r="AZ145" s="2" t="n"/>
+      <c r="BA145" s="2" t="n"/>
+      <c r="BB145" s="2" t="n"/>
+      <c r="BC145" s="2" t="n"/>
+      <c r="BD145" s="2" t="n"/>
+      <c r="BE145" s="2" t="n"/>
+      <c r="BF145" s="2" t="n"/>
+      <c r="BG145" s="2" t="n"/>
+      <c r="BH145" s="2" t="n"/>
+      <c r="BI145" s="2" t="n"/>
+      <c r="BJ145" s="2" t="n"/>
+      <c r="BK145" s="1" t="n"/>
+      <c r="BL145" s="2" t="n"/>
+      <c r="BM145" s="2" t="n"/>
+      <c r="BN145" s="2" t="n"/>
+      <c r="BO145" s="2" t="n"/>
+      <c r="BP145" s="2" t="n"/>
+      <c r="BQ145" s="2" t="n"/>
+      <c r="BR145" s="2" t="n"/>
+      <c r="BS145" s="1" t="n"/>
+      <c r="BT145" s="2" t="n"/>
+      <c r="BU145" s="2" t="n"/>
+      <c r="BV145" s="2" t="n"/>
+      <c r="BW145" s="2" t="n"/>
+      <c r="BX145" s="2" t="n"/>
+      <c r="BY145" s="2" t="n"/>
+      <c r="BZ145" s="2" t="n"/>
+      <c r="CA145" s="2" t="n"/>
+      <c r="CB145" s="2" t="n"/>
+      <c r="CC145" s="2" t="n"/>
+      <c r="CD145" s="2" t="n"/>
+      <c r="CE145" s="2" t="n"/>
+      <c r="CF145" s="1" t="n"/>
+      <c r="CG145" s="2" t="n"/>
+      <c r="CH145" s="2" t="n"/>
+      <c r="CI145" s="2" t="n"/>
+      <c r="CJ145" s="2" t="n"/>
+      <c r="CK145" s="2" t="n"/>
+      <c r="CL145" s="2" t="n"/>
+      <c r="CM145" s="2" t="n"/>
+      <c r="CN145" s="2" t="n"/>
+      <c r="CO145" s="2" t="n"/>
+      <c r="CP145" s="2" t="n"/>
+      <c r="CQ145" s="2" t="n"/>
+      <c r="CR145" s="2" t="n"/>
+      <c r="CS145" s="2" t="n"/>
+      <c r="CT145" s="1" t="n"/>
+      <c r="CU145" s="2" t="n"/>
+      <c r="CV145" s="2" t="n"/>
+      <c r="CW145" s="2" t="n"/>
+      <c r="CX145" s="2" t="n"/>
+      <c r="CY145" s="2" t="n"/>
+      <c r="CZ145" s="2" t="n"/>
+      <c r="DA145" s="2" t="n"/>
+      <c r="DB145" s="2" t="n"/>
+      <c r="DC145" s="2" t="n"/>
+      <c r="DD145" s="2" t="n"/>
+      <c r="DE145" s="2" t="n"/>
+      <c r="DF145" s="2" t="n"/>
+      <c r="DG145" s="2" t="n"/>
+      <c r="DH145" s="2" t="n"/>
+      <c r="DI145" s="1" t="n"/>
     </row>
     <row r="146" ht="4.96" customHeight="1">
-      <c r="L146" s="6" t="n"/>
-      <c r="M146" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="P146" s="6" t="n"/>
-      <c r="BK146" s="6" t="n"/>
-      <c r="BS146" s="6" t="n"/>
-      <c r="CF146" s="6" t="n"/>
-      <c r="CT146" s="6" t="n"/>
-      <c r="DI146" s="6" t="n"/>
+      <c r="L146" s="5" t="n"/>
+      <c r="P146" s="5" t="n"/>
+      <c r="BK146" s="5" t="n"/>
+      <c r="BS146" s="5" t="n"/>
+      <c r="CF146" s="5" t="n"/>
+      <c r="CT146" s="5" t="n"/>
+      <c r="DI146" s="5" t="n"/>
     </row>
     <row r="147" ht="4.96" customHeight="1">
-      <c r="L147" s="6" t="n"/>
-      <c r="P147" s="6" t="n"/>
-      <c r="BK147" s="6" t="n"/>
-      <c r="BS147" s="6" t="n"/>
-      <c r="CF147" s="6" t="n"/>
-      <c r="CT147" s="6" t="n"/>
-      <c r="DI147" s="6" t="n"/>
+      <c r="L147" s="5" t="n"/>
+      <c r="P147" s="5" t="n"/>
+      <c r="BK147" s="5" t="n"/>
+      <c r="BS147" s="5" t="n"/>
+      <c r="CF147" s="5" t="n"/>
+      <c r="CT147" s="5" t="n"/>
+      <c r="DI147" s="5" t="n"/>
     </row>
     <row r="148" ht="4.96" customHeight="1">
-      <c r="L148" s="1" t="n"/>
-      <c r="M148" s="2" t="n"/>
-      <c r="N148" s="2" t="n"/>
-      <c r="O148" s="2" t="n"/>
-      <c r="P148" s="1" t="n"/>
-      <c r="Q148" s="2" t="n"/>
-      <c r="R148" s="2" t="n"/>
-      <c r="S148" s="2" t="n"/>
-      <c r="T148" s="2" t="n"/>
-      <c r="U148" s="2" t="n"/>
-      <c r="V148" s="2" t="n"/>
-      <c r="W148" s="2" t="n"/>
-      <c r="X148" s="2" t="n"/>
-      <c r="Y148" s="2" t="n"/>
-      <c r="Z148" s="2" t="n"/>
-      <c r="AA148" s="2" t="n"/>
-      <c r="AB148" s="18" t="inlineStr">
+      <c r="L148" s="27" t="n"/>
+      <c r="M148" s="19" t="n"/>
+      <c r="N148" s="19" t="n"/>
+      <c r="O148" s="19" t="n"/>
+      <c r="P148" s="27" t="n"/>
+      <c r="Q148" s="19" t="n"/>
+      <c r="R148" s="19" t="n"/>
+      <c r="S148" s="19" t="n"/>
+      <c r="T148" s="19" t="n"/>
+      <c r="U148" s="19" t="n"/>
+      <c r="V148" s="19" t="n"/>
+      <c r="W148" s="19" t="n"/>
+      <c r="X148" s="19" t="n"/>
+      <c r="Y148" s="19" t="n"/>
+      <c r="Z148" s="19" t="n"/>
+      <c r="AA148" s="19" t="n"/>
+      <c r="AB148" s="28" t="inlineStr">
         <is>
           <t>合　　計</t>
         </is>
       </c>
-      <c r="AC148" s="4" t="n"/>
-      <c r="AD148" s="4" t="n"/>
-      <c r="AE148" s="4" t="n"/>
-      <c r="AF148" s="4" t="n"/>
-      <c r="AG148" s="4" t="n"/>
-      <c r="AH148" s="4" t="n"/>
-      <c r="AI148" s="4" t="n"/>
-      <c r="AJ148" s="4" t="n"/>
-      <c r="AK148" s="4" t="n"/>
-      <c r="AL148" s="2" t="n"/>
-      <c r="AM148" s="2" t="n"/>
-      <c r="AN148" s="2" t="n"/>
-      <c r="AO148" s="2" t="n"/>
-      <c r="AP148" s="2" t="n"/>
-      <c r="AQ148" s="2" t="n"/>
-      <c r="AR148" s="2" t="n"/>
-      <c r="AS148" s="2" t="n"/>
-      <c r="AT148" s="2" t="n"/>
-      <c r="AU148" s="2" t="n"/>
-      <c r="AV148" s="2" t="n"/>
-      <c r="AW148" s="2" t="n"/>
-      <c r="AX148" s="2" t="n"/>
-      <c r="AY148" s="2" t="n"/>
-      <c r="AZ148" s="2" t="n"/>
-      <c r="BA148" s="2" t="n"/>
-      <c r="BB148" s="2" t="n"/>
-      <c r="BC148" s="2" t="n"/>
-      <c r="BD148" s="2" t="n"/>
-      <c r="BE148" s="2" t="n"/>
-      <c r="BF148" s="2" t="n"/>
-      <c r="BG148" s="2" t="n"/>
-      <c r="BH148" s="2" t="n"/>
-      <c r="BI148" s="2" t="n"/>
-      <c r="BJ148" s="2" t="n"/>
-      <c r="BK148" s="1" t="n"/>
-      <c r="BL148" s="2" t="n"/>
-      <c r="BM148" s="2" t="n"/>
-      <c r="BN148" s="2" t="n"/>
-      <c r="BO148" s="2" t="n"/>
-      <c r="BP148" s="2" t="n"/>
-      <c r="BQ148" s="2" t="n"/>
-      <c r="BR148" s="2" t="n"/>
-      <c r="BS148" s="1" t="n"/>
-      <c r="BT148" s="2" t="n"/>
-      <c r="BU148" s="2" t="n"/>
-      <c r="BV148" s="2" t="n"/>
-      <c r="BW148" s="2" t="n"/>
-      <c r="BX148" s="2" t="n"/>
-      <c r="BY148" s="2" t="n"/>
-      <c r="BZ148" s="2" t="n"/>
-      <c r="CA148" s="2" t="n"/>
-      <c r="CB148" s="2" t="n"/>
-      <c r="CC148" s="2" t="n"/>
-      <c r="CD148" s="2" t="n"/>
-      <c r="CE148" s="2" t="n"/>
-      <c r="CF148" s="1" t="n"/>
-      <c r="CG148" s="2" t="n"/>
-      <c r="CH148" s="2" t="n"/>
-      <c r="CI148" s="2" t="n"/>
-      <c r="CJ148" s="2" t="n"/>
-      <c r="CK148" s="2" t="n"/>
-      <c r="CL148" s="2" t="n"/>
-      <c r="CM148" s="2" t="n"/>
-      <c r="CN148" s="2" t="n"/>
-      <c r="CO148" s="2" t="n"/>
-      <c r="CP148" s="2" t="n"/>
-      <c r="CQ148" s="2" t="n"/>
-      <c r="CR148" s="2" t="n"/>
-      <c r="CS148" s="2" t="n"/>
-      <c r="CT148" s="1" t="n"/>
-      <c r="CU148" s="2" t="n"/>
-      <c r="CV148" s="2" t="n"/>
-      <c r="CW148" s="2" t="n"/>
-      <c r="CX148" s="2" t="n"/>
-      <c r="CY148" s="2" t="n"/>
-      <c r="CZ148" s="20" t="inlineStr">
+      <c r="AC148" s="19" t="n"/>
+      <c r="AD148" s="19" t="n"/>
+      <c r="AE148" s="19" t="n"/>
+      <c r="AF148" s="19" t="n"/>
+      <c r="AG148" s="19" t="n"/>
+      <c r="AH148" s="19" t="n"/>
+      <c r="AI148" s="19" t="n"/>
+      <c r="AJ148" s="19" t="n"/>
+      <c r="AK148" s="19" t="n"/>
+      <c r="AL148" s="19" t="n"/>
+      <c r="AM148" s="19" t="n"/>
+      <c r="AN148" s="19" t="n"/>
+      <c r="AO148" s="19" t="n"/>
+      <c r="AP148" s="19" t="n"/>
+      <c r="AQ148" s="19" t="n"/>
+      <c r="AR148" s="19" t="n"/>
+      <c r="AS148" s="19" t="n"/>
+      <c r="AT148" s="19" t="n"/>
+      <c r="AU148" s="19" t="n"/>
+      <c r="AV148" s="19" t="n"/>
+      <c r="AW148" s="19" t="n"/>
+      <c r="AX148" s="19" t="n"/>
+      <c r="AY148" s="19" t="n"/>
+      <c r="AZ148" s="19" t="n"/>
+      <c r="BA148" s="19" t="n"/>
+      <c r="BB148" s="19" t="n"/>
+      <c r="BC148" s="19" t="n"/>
+      <c r="BD148" s="19" t="n"/>
+      <c r="BE148" s="19" t="n"/>
+      <c r="BF148" s="19" t="n"/>
+      <c r="BG148" s="19" t="n"/>
+      <c r="BH148" s="19" t="n"/>
+      <c r="BI148" s="19" t="n"/>
+      <c r="BJ148" s="19" t="n"/>
+      <c r="BK148" s="27" t="n"/>
+      <c r="BL148" s="19" t="n"/>
+      <c r="BM148" s="19" t="n"/>
+      <c r="BN148" s="19" t="n"/>
+      <c r="BO148" s="19" t="n"/>
+      <c r="BP148" s="19" t="n"/>
+      <c r="BQ148" s="19" t="n"/>
+      <c r="BR148" s="19" t="n"/>
+      <c r="BS148" s="27" t="n"/>
+      <c r="BT148" s="19" t="n"/>
+      <c r="BU148" s="19" t="n"/>
+      <c r="BV148" s="19" t="n"/>
+      <c r="BW148" s="19" t="n"/>
+      <c r="BX148" s="19" t="n"/>
+      <c r="BY148" s="19" t="n"/>
+      <c r="BZ148" s="19" t="n"/>
+      <c r="CA148" s="19" t="n"/>
+      <c r="CB148" s="19" t="n"/>
+      <c r="CC148" s="19" t="n"/>
+      <c r="CD148" s="19" t="n"/>
+      <c r="CE148" s="19" t="n"/>
+      <c r="CF148" s="27" t="n"/>
+      <c r="CG148" s="19" t="n"/>
+      <c r="CH148" s="19" t="n"/>
+      <c r="CI148" s="19" t="n"/>
+      <c r="CJ148" s="19" t="n"/>
+      <c r="CK148" s="19" t="n"/>
+      <c r="CL148" s="19" t="n"/>
+      <c r="CM148" s="19" t="n"/>
+      <c r="CN148" s="19" t="n"/>
+      <c r="CO148" s="19" t="n"/>
+      <c r="CP148" s="19" t="n"/>
+      <c r="CQ148" s="19" t="n"/>
+      <c r="CR148" s="19" t="n"/>
+      <c r="CS148" s="19" t="n"/>
+      <c r="CT148" s="27" t="n"/>
+      <c r="CU148" s="19" t="n"/>
+      <c r="CV148" s="19" t="n"/>
+      <c r="CW148" s="19" t="n"/>
+      <c r="CX148" s="19" t="n"/>
+      <c r="CY148" s="19" t="n"/>
+      <c r="CZ148" s="29" t="inlineStr">
         <is>
           <t>3,700,000</t>
         </is>
       </c>
-      <c r="DA148" s="4" t="n"/>
-      <c r="DB148" s="4" t="n"/>
-      <c r="DC148" s="4" t="n"/>
-      <c r="DD148" s="4" t="n"/>
-      <c r="DE148" s="4" t="n"/>
-      <c r="DF148" s="4" t="n"/>
-      <c r="DG148" s="4" t="n"/>
-      <c r="DH148" s="4" t="n"/>
-      <c r="DI148" s="1" t="n"/>
+      <c r="DA148" s="19" t="n"/>
+      <c r="DB148" s="19" t="n"/>
+      <c r="DC148" s="19" t="n"/>
+      <c r="DD148" s="19" t="n"/>
+      <c r="DE148" s="19" t="n"/>
+      <c r="DF148" s="19" t="n"/>
+      <c r="DG148" s="19" t="n"/>
+      <c r="DH148" s="19" t="n"/>
+      <c r="DI148" s="27" t="n"/>
     </row>
     <row r="149" ht="4.96" customHeight="1">
-      <c r="L149" s="6" t="n"/>
-      <c r="DI149" s="6" t="n"/>
+      <c r="L149" s="5" t="n"/>
+      <c r="DI149" s="5" t="n"/>
     </row>
     <row r="150" ht="4.96" customHeight="1">
-      <c r="L150" s="6" t="n"/>
-      <c r="DI150" s="6" t="n"/>
+      <c r="L150" s="5" t="n"/>
+      <c r="DI150" s="5" t="n"/>
     </row>
     <row r="151" ht="4.96" customHeight="1">
-      <c r="L151" s="6" t="n"/>
-      <c r="DI151" s="6" t="n"/>
+      <c r="L151" s="1" t="n"/>
+      <c r="M151" s="2" t="n"/>
+      <c r="N151" s="2" t="n"/>
+      <c r="O151" s="2" t="n"/>
+      <c r="P151" s="2" t="n"/>
+      <c r="Q151" s="2" t="n"/>
+      <c r="R151" s="2" t="n"/>
+      <c r="S151" s="2" t="n"/>
+      <c r="T151" s="2" t="n"/>
+      <c r="U151" s="2" t="n"/>
+      <c r="V151" s="2" t="n"/>
+      <c r="W151" s="2" t="n"/>
+      <c r="X151" s="2" t="n"/>
+      <c r="Y151" s="2" t="n"/>
+      <c r="Z151" s="2" t="n"/>
+      <c r="AA151" s="2" t="n"/>
+      <c r="AB151" s="2" t="n"/>
+      <c r="AC151" s="2" t="n"/>
+      <c r="AD151" s="2" t="n"/>
+      <c r="AE151" s="2" t="n"/>
+      <c r="AF151" s="2" t="n"/>
+      <c r="AG151" s="2" t="n"/>
+      <c r="AH151" s="2" t="n"/>
+      <c r="AI151" s="2" t="n"/>
+      <c r="AJ151" s="2" t="n"/>
+      <c r="AK151" s="2" t="n"/>
+      <c r="AL151" s="2" t="n"/>
+      <c r="AM151" s="2" t="n"/>
+      <c r="AN151" s="2" t="n"/>
+      <c r="AO151" s="2" t="n"/>
+      <c r="AP151" s="2" t="n"/>
+      <c r="AQ151" s="2" t="n"/>
+      <c r="AR151" s="2" t="n"/>
+      <c r="AS151" s="2" t="n"/>
+      <c r="AT151" s="2" t="n"/>
+      <c r="AU151" s="2" t="n"/>
+      <c r="AV151" s="2" t="n"/>
+      <c r="AW151" s="2" t="n"/>
+      <c r="AX151" s="2" t="n"/>
+      <c r="AY151" s="2" t="n"/>
+      <c r="AZ151" s="2" t="n"/>
+      <c r="BA151" s="2" t="n"/>
+      <c r="BB151" s="2" t="n"/>
+      <c r="BC151" s="2" t="n"/>
+      <c r="BD151" s="2" t="n"/>
+      <c r="BE151" s="2" t="n"/>
+      <c r="BF151" s="2" t="n"/>
+      <c r="BG151" s="2" t="n"/>
+      <c r="BH151" s="2" t="n"/>
+      <c r="BI151" s="2" t="n"/>
+      <c r="BJ151" s="2" t="n"/>
+      <c r="BK151" s="2" t="n"/>
+      <c r="BL151" s="2" t="n"/>
+      <c r="BM151" s="2" t="n"/>
+      <c r="BN151" s="2" t="n"/>
+      <c r="BO151" s="2" t="n"/>
+      <c r="BP151" s="2" t="n"/>
+      <c r="BQ151" s="2" t="n"/>
+      <c r="BR151" s="2" t="n"/>
+      <c r="BS151" s="2" t="n"/>
+      <c r="BT151" s="2" t="n"/>
+      <c r="BU151" s="2" t="n"/>
+      <c r="BV151" s="2" t="n"/>
+      <c r="BW151" s="2" t="n"/>
+      <c r="BX151" s="2" t="n"/>
+      <c r="BY151" s="2" t="n"/>
+      <c r="BZ151" s="2" t="n"/>
+      <c r="CA151" s="2" t="n"/>
+      <c r="CB151" s="2" t="n"/>
+      <c r="CC151" s="2" t="n"/>
+      <c r="CD151" s="2" t="n"/>
+      <c r="CE151" s="2" t="n"/>
+      <c r="CF151" s="2" t="n"/>
+      <c r="CG151" s="2" t="n"/>
+      <c r="CH151" s="2" t="n"/>
+      <c r="CI151" s="2" t="n"/>
+      <c r="CJ151" s="2" t="n"/>
+      <c r="CK151" s="2" t="n"/>
+      <c r="CL151" s="2" t="n"/>
+      <c r="CM151" s="2" t="n"/>
+      <c r="CN151" s="2" t="n"/>
+      <c r="CO151" s="2" t="n"/>
+      <c r="CP151" s="2" t="n"/>
+      <c r="CQ151" s="2" t="n"/>
+      <c r="CR151" s="2" t="n"/>
+      <c r="CS151" s="2" t="n"/>
+      <c r="CT151" s="2" t="n"/>
+      <c r="CU151" s="2" t="n"/>
+      <c r="CV151" s="2" t="n"/>
+      <c r="CW151" s="2" t="n"/>
+      <c r="CX151" s="2" t="n"/>
+      <c r="CY151" s="2" t="n"/>
+      <c r="CZ151" s="2" t="n"/>
+      <c r="DA151" s="2" t="n"/>
+      <c r="DB151" s="2" t="n"/>
+      <c r="DC151" s="2" t="n"/>
+      <c r="DD151" s="2" t="n"/>
+      <c r="DE151" s="2" t="n"/>
+      <c r="DF151" s="2" t="n"/>
+      <c r="DG151" s="2" t="n"/>
+      <c r="DH151" s="2" t="n"/>
+      <c r="DI151" s="1" t="n"/>
     </row>
     <row r="152" ht="4.96" customHeight="1">
-      <c r="M152" s="12" t="inlineStr">
+      <c r="L152" s="1" t="n"/>
+      <c r="M152" s="30" t="inlineStr">
         <is>
           <t>備　　考</t>
         </is>
       </c>
-    </row>
-    <row r="153" ht="4.96" customHeight="1"/>
-    <row r="154" ht="4.96" customHeight="1"/>
-    <row r="155" ht="4.96" customHeight="1"/>
-    <row r="156" ht="4.96" customHeight="1"/>
-    <row r="157" ht="4.96" customHeight="1"/>
-    <row r="158" ht="4.96" customHeight="1"/>
-    <row r="159" ht="4.96" customHeight="1"/>
-    <row r="160" ht="4.96" customHeight="1"/>
-    <row r="161" ht="4.96" customHeight="1"/>
-    <row r="162" ht="4.96" customHeight="1"/>
-    <row r="163" ht="4.96" customHeight="1"/>
-    <row r="164" ht="4.96" customHeight="1"/>
-    <row r="165" ht="4.96" customHeight="1"/>
+      <c r="N152" s="2" t="n"/>
+      <c r="O152" s="2" t="n"/>
+      <c r="P152" s="2" t="n"/>
+      <c r="Q152" s="2" t="n"/>
+      <c r="R152" s="2" t="n"/>
+      <c r="S152" s="2" t="n"/>
+      <c r="T152" s="2" t="n"/>
+      <c r="U152" s="2" t="n"/>
+      <c r="V152" s="2" t="n"/>
+      <c r="W152" s="2" t="n"/>
+      <c r="X152" s="2" t="n"/>
+      <c r="Y152" s="2" t="n"/>
+      <c r="Z152" s="2" t="n"/>
+      <c r="AA152" s="2" t="n"/>
+      <c r="AB152" s="2" t="n"/>
+      <c r="AC152" s="2" t="n"/>
+      <c r="AD152" s="2" t="n"/>
+      <c r="AE152" s="2" t="n"/>
+      <c r="AF152" s="2" t="n"/>
+      <c r="AG152" s="2" t="n"/>
+      <c r="AH152" s="2" t="n"/>
+      <c r="AI152" s="2" t="n"/>
+      <c r="AJ152" s="2" t="n"/>
+      <c r="AK152" s="2" t="n"/>
+      <c r="AL152" s="2" t="n"/>
+      <c r="AM152" s="2" t="n"/>
+      <c r="AN152" s="2" t="n"/>
+      <c r="AO152" s="2" t="n"/>
+      <c r="AP152" s="2" t="n"/>
+      <c r="AQ152" s="2" t="n"/>
+      <c r="AR152" s="2" t="n"/>
+      <c r="AS152" s="2" t="n"/>
+      <c r="AT152" s="2" t="n"/>
+      <c r="AU152" s="2" t="n"/>
+      <c r="AV152" s="2" t="n"/>
+      <c r="AW152" s="2" t="n"/>
+      <c r="AX152" s="2" t="n"/>
+      <c r="AY152" s="2" t="n"/>
+      <c r="AZ152" s="2" t="n"/>
+      <c r="BA152" s="2" t="n"/>
+      <c r="BB152" s="2" t="n"/>
+      <c r="BC152" s="2" t="n"/>
+      <c r="BD152" s="2" t="n"/>
+      <c r="BE152" s="2" t="n"/>
+      <c r="BF152" s="2" t="n"/>
+      <c r="BG152" s="2" t="n"/>
+      <c r="BH152" s="2" t="n"/>
+      <c r="BI152" s="2" t="n"/>
+      <c r="BJ152" s="2" t="n"/>
+      <c r="BK152" s="2" t="n"/>
+      <c r="BL152" s="2" t="n"/>
+      <c r="BM152" s="2" t="n"/>
+      <c r="BN152" s="2" t="n"/>
+      <c r="BO152" s="2" t="n"/>
+      <c r="BP152" s="2" t="n"/>
+      <c r="BQ152" s="2" t="n"/>
+      <c r="BR152" s="2" t="n"/>
+      <c r="BS152" s="2" t="n"/>
+      <c r="BT152" s="2" t="n"/>
+      <c r="BU152" s="2" t="n"/>
+      <c r="BV152" s="2" t="n"/>
+      <c r="BW152" s="2" t="n"/>
+      <c r="BX152" s="2" t="n"/>
+      <c r="BY152" s="2" t="n"/>
+      <c r="BZ152" s="2" t="n"/>
+      <c r="CA152" s="2" t="n"/>
+      <c r="CB152" s="2" t="n"/>
+      <c r="CC152" s="2" t="n"/>
+      <c r="CD152" s="2" t="n"/>
+      <c r="CE152" s="2" t="n"/>
+      <c r="CF152" s="2" t="n"/>
+      <c r="CG152" s="2" t="n"/>
+      <c r="CH152" s="2" t="n"/>
+      <c r="CI152" s="2" t="n"/>
+      <c r="CJ152" s="2" t="n"/>
+      <c r="CK152" s="2" t="n"/>
+      <c r="CL152" s="2" t="n"/>
+      <c r="CM152" s="2" t="n"/>
+      <c r="CN152" s="2" t="n"/>
+      <c r="CO152" s="2" t="n"/>
+      <c r="CP152" s="2" t="n"/>
+      <c r="CQ152" s="2" t="n"/>
+      <c r="CR152" s="2" t="n"/>
+      <c r="CS152" s="2" t="n"/>
+      <c r="CT152" s="2" t="n"/>
+      <c r="CU152" s="2" t="n"/>
+      <c r="CV152" s="2" t="n"/>
+      <c r="CW152" s="2" t="n"/>
+      <c r="CX152" s="2" t="n"/>
+      <c r="CY152" s="2" t="n"/>
+      <c r="CZ152" s="2" t="n"/>
+      <c r="DA152" s="2" t="n"/>
+      <c r="DB152" s="2" t="n"/>
+      <c r="DC152" s="2" t="n"/>
+      <c r="DD152" s="2" t="n"/>
+      <c r="DE152" s="2" t="n"/>
+      <c r="DF152" s="2" t="n"/>
+      <c r="DG152" s="2" t="n"/>
+      <c r="DH152" s="2" t="n"/>
+      <c r="DI152" s="1" t="n"/>
+    </row>
+    <row r="153" ht="4.96" customHeight="1">
+      <c r="L153" s="5" t="n"/>
+      <c r="DI153" s="5" t="n"/>
+    </row>
+    <row r="154" ht="4.96" customHeight="1">
+      <c r="L154" s="5" t="n"/>
+      <c r="DI154" s="5" t="n"/>
+    </row>
+    <row r="155" ht="4.96" customHeight="1">
+      <c r="L155" s="31" t="inlineStr">
+        <is>
+          <t>・消費税は別途計上させていただきます。</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="n"/>
+      <c r="N155" s="2" t="n"/>
+      <c r="O155" s="2" t="n"/>
+      <c r="P155" s="2" t="n"/>
+      <c r="Q155" s="2" t="n"/>
+      <c r="R155" s="2" t="n"/>
+      <c r="S155" s="2" t="n"/>
+      <c r="T155" s="2" t="n"/>
+      <c r="U155" s="2" t="n"/>
+      <c r="V155" s="2" t="n"/>
+      <c r="W155" s="2" t="n"/>
+      <c r="X155" s="2" t="n"/>
+      <c r="Y155" s="2" t="n"/>
+      <c r="Z155" s="2" t="n"/>
+      <c r="AA155" s="2" t="n"/>
+      <c r="AB155" s="2" t="n"/>
+      <c r="AC155" s="2" t="n"/>
+      <c r="AD155" s="2" t="n"/>
+      <c r="AE155" s="2" t="n"/>
+      <c r="AF155" s="2" t="n"/>
+      <c r="AG155" s="2" t="n"/>
+      <c r="AH155" s="2" t="n"/>
+      <c r="AI155" s="2" t="n"/>
+      <c r="AJ155" s="2" t="n"/>
+      <c r="AK155" s="2" t="n"/>
+      <c r="AL155" s="2" t="n"/>
+      <c r="AM155" s="2" t="n"/>
+      <c r="AN155" s="2" t="n"/>
+      <c r="AO155" s="2" t="n"/>
+      <c r="AP155" s="2" t="n"/>
+      <c r="AQ155" s="2" t="n"/>
+      <c r="AR155" s="2" t="n"/>
+      <c r="AS155" s="2" t="n"/>
+      <c r="AT155" s="2" t="n"/>
+      <c r="AU155" s="2" t="n"/>
+      <c r="AV155" s="2" t="n"/>
+      <c r="AW155" s="2" t="n"/>
+      <c r="AX155" s="2" t="n"/>
+      <c r="AY155" s="2" t="n"/>
+      <c r="AZ155" s="2" t="n"/>
+      <c r="BA155" s="2" t="n"/>
+      <c r="BB155" s="2" t="n"/>
+      <c r="BC155" s="2" t="n"/>
+      <c r="BD155" s="2" t="n"/>
+      <c r="BE155" s="2" t="n"/>
+      <c r="BF155" s="2" t="n"/>
+      <c r="BG155" s="2" t="n"/>
+      <c r="BH155" s="2" t="n"/>
+      <c r="BI155" s="2" t="n"/>
+      <c r="BJ155" s="2" t="n"/>
+      <c r="BK155" s="2" t="n"/>
+      <c r="BL155" s="2" t="n"/>
+      <c r="BM155" s="2" t="n"/>
+      <c r="BN155" s="2" t="n"/>
+      <c r="BO155" s="2" t="n"/>
+      <c r="BP155" s="2" t="n"/>
+      <c r="BQ155" s="2" t="n"/>
+      <c r="BR155" s="2" t="n"/>
+      <c r="BS155" s="2" t="n"/>
+      <c r="BT155" s="2" t="n"/>
+      <c r="BU155" s="2" t="n"/>
+      <c r="BV155" s="2" t="n"/>
+      <c r="BW155" s="2" t="n"/>
+      <c r="BX155" s="2" t="n"/>
+      <c r="BY155" s="2" t="n"/>
+      <c r="BZ155" s="2" t="n"/>
+      <c r="CA155" s="2" t="n"/>
+      <c r="CB155" s="2" t="n"/>
+      <c r="CC155" s="2" t="n"/>
+      <c r="CD155" s="2" t="n"/>
+      <c r="CE155" s="2" t="n"/>
+      <c r="CF155" s="2" t="n"/>
+      <c r="CG155" s="2" t="n"/>
+      <c r="CH155" s="2" t="n"/>
+      <c r="CI155" s="2" t="n"/>
+      <c r="CJ155" s="2" t="n"/>
+      <c r="CK155" s="2" t="n"/>
+      <c r="CL155" s="2" t="n"/>
+      <c r="CM155" s="2" t="n"/>
+      <c r="CN155" s="2" t="n"/>
+      <c r="CO155" s="2" t="n"/>
+      <c r="CP155" s="2" t="n"/>
+      <c r="CQ155" s="2" t="n"/>
+      <c r="CR155" s="2" t="n"/>
+      <c r="CS155" s="2" t="n"/>
+      <c r="CT155" s="2" t="n"/>
+      <c r="CU155" s="2" t="n"/>
+      <c r="CV155" s="2" t="n"/>
+      <c r="CW155" s="2" t="n"/>
+      <c r="CX155" s="2" t="n"/>
+      <c r="CY155" s="2" t="n"/>
+      <c r="CZ155" s="2" t="n"/>
+      <c r="DA155" s="2" t="n"/>
+      <c r="DB155" s="2" t="n"/>
+      <c r="DC155" s="2" t="n"/>
+      <c r="DD155" s="2" t="n"/>
+      <c r="DE155" s="2" t="n"/>
+      <c r="DF155" s="2" t="n"/>
+      <c r="DG155" s="2" t="n"/>
+      <c r="DH155" s="2" t="n"/>
+      <c r="DI155" s="1" t="n"/>
+    </row>
+    <row r="156" ht="4.96" customHeight="1">
+      <c r="L156" s="5" t="n"/>
+      <c r="DI156" s="5" t="n"/>
+    </row>
+    <row r="157" ht="4.96" customHeight="1">
+      <c r="L157" s="5" t="n"/>
+      <c r="DI157" s="5" t="n"/>
+    </row>
+    <row r="158" ht="4.96" customHeight="1">
+      <c r="L158" s="32" t="inlineStr">
+        <is>
+          <t>・製品の瑕疵、無償保証期間は御購入後3ヶ月間です。</t>
+        </is>
+      </c>
+      <c r="DI158" s="5" t="n"/>
+    </row>
+    <row r="159" ht="4.96" customHeight="1">
+      <c r="L159" s="5" t="n"/>
+      <c r="DI159" s="5" t="n"/>
+    </row>
+    <row r="160" ht="4.96" customHeight="1">
+      <c r="L160" s="5" t="n"/>
+      <c r="DI160" s="5" t="n"/>
+    </row>
+    <row r="161" ht="4.96" customHeight="1">
+      <c r="L161" s="5" t="n"/>
+      <c r="DI161" s="5" t="n"/>
+    </row>
+    <row r="162" ht="4.96" customHeight="1">
+      <c r="L162" s="5" t="n"/>
+      <c r="DI162" s="5" t="n"/>
+    </row>
+    <row r="163" ht="4.96" customHeight="1">
+      <c r="L163" s="5" t="n"/>
+      <c r="DI163" s="5" t="n"/>
+    </row>
+    <row r="164" ht="4.96" customHeight="1">
+      <c r="L164" s="5" t="n"/>
+      <c r="DI164" s="5" t="n"/>
+    </row>
+    <row r="165" ht="4.96" customHeight="1">
+      <c r="L165" s="1" t="n"/>
+      <c r="M165" s="2" t="n"/>
+      <c r="N165" s="2" t="n"/>
+      <c r="O165" s="2" t="n"/>
+      <c r="P165" s="2" t="n"/>
+      <c r="Q165" s="2" t="n"/>
+      <c r="R165" s="2" t="n"/>
+      <c r="S165" s="2" t="n"/>
+      <c r="T165" s="2" t="n"/>
+      <c r="U165" s="2" t="n"/>
+      <c r="V165" s="2" t="n"/>
+      <c r="W165" s="2" t="n"/>
+      <c r="X165" s="2" t="n"/>
+      <c r="Y165" s="2" t="n"/>
+      <c r="Z165" s="2" t="n"/>
+      <c r="AA165" s="2" t="n"/>
+      <c r="AB165" s="2" t="n"/>
+      <c r="AC165" s="2" t="n"/>
+      <c r="AD165" s="2" t="n"/>
+      <c r="AE165" s="2" t="n"/>
+      <c r="AF165" s="2" t="n"/>
+      <c r="AG165" s="2" t="n"/>
+      <c r="AH165" s="2" t="n"/>
+      <c r="AI165" s="2" t="n"/>
+      <c r="AJ165" s="2" t="n"/>
+      <c r="AK165" s="2" t="n"/>
+      <c r="AL165" s="2" t="n"/>
+      <c r="AM165" s="2" t="n"/>
+      <c r="AN165" s="2" t="n"/>
+      <c r="AO165" s="2" t="n"/>
+      <c r="AP165" s="2" t="n"/>
+      <c r="AQ165" s="2" t="n"/>
+      <c r="AR165" s="2" t="n"/>
+      <c r="AS165" s="2" t="n"/>
+      <c r="AT165" s="2" t="n"/>
+      <c r="AU165" s="2" t="n"/>
+      <c r="AV165" s="2" t="n"/>
+      <c r="AW165" s="2" t="n"/>
+      <c r="AX165" s="2" t="n"/>
+      <c r="AY165" s="2" t="n"/>
+      <c r="AZ165" s="2" t="n"/>
+      <c r="BA165" s="2" t="n"/>
+      <c r="BB165" s="2" t="n"/>
+      <c r="BC165" s="2" t="n"/>
+      <c r="BD165" s="2" t="n"/>
+      <c r="BE165" s="2" t="n"/>
+      <c r="BF165" s="2" t="n"/>
+      <c r="BG165" s="2" t="n"/>
+      <c r="BH165" s="2" t="n"/>
+      <c r="BI165" s="2" t="n"/>
+      <c r="BJ165" s="2" t="n"/>
+      <c r="BK165" s="2" t="n"/>
+      <c r="BL165" s="2" t="n"/>
+      <c r="BM165" s="2" t="n"/>
+      <c r="BN165" s="2" t="n"/>
+      <c r="BO165" s="2" t="n"/>
+      <c r="BP165" s="2" t="n"/>
+      <c r="BQ165" s="2" t="n"/>
+      <c r="BR165" s="2" t="n"/>
+      <c r="BS165" s="2" t="n"/>
+      <c r="BT165" s="2" t="n"/>
+      <c r="BU165" s="2" t="n"/>
+      <c r="BV165" s="2" t="n"/>
+      <c r="BW165" s="2" t="n"/>
+      <c r="BX165" s="2" t="n"/>
+      <c r="BY165" s="2" t="n"/>
+      <c r="BZ165" s="2" t="n"/>
+      <c r="CA165" s="2" t="n"/>
+      <c r="CB165" s="2" t="n"/>
+      <c r="CC165" s="2" t="n"/>
+      <c r="CD165" s="2" t="n"/>
+      <c r="CE165" s="2" t="n"/>
+      <c r="CF165" s="2" t="n"/>
+      <c r="CG165" s="2" t="n"/>
+      <c r="CH165" s="2" t="n"/>
+      <c r="CI165" s="2" t="n"/>
+      <c r="CJ165" s="2" t="n"/>
+      <c r="CK165" s="2" t="n"/>
+      <c r="CL165" s="2" t="n"/>
+      <c r="CM165" s="2" t="n"/>
+      <c r="CN165" s="2" t="n"/>
+      <c r="CO165" s="2" t="n"/>
+      <c r="CP165" s="2" t="n"/>
+      <c r="CQ165" s="2" t="n"/>
+      <c r="CR165" s="2" t="n"/>
+      <c r="CS165" s="2" t="n"/>
+      <c r="CT165" s="2" t="n"/>
+      <c r="CU165" s="2" t="n"/>
+      <c r="CV165" s="2" t="n"/>
+      <c r="CW165" s="2" t="n"/>
+      <c r="CX165" s="2" t="n"/>
+      <c r="CY165" s="2" t="n"/>
+      <c r="CZ165" s="2" t="n"/>
+      <c r="DA165" s="2" t="n"/>
+      <c r="DB165" s="2" t="n"/>
+      <c r="DC165" s="2" t="n"/>
+      <c r="DD165" s="2" t="n"/>
+      <c r="DE165" s="2" t="n"/>
+      <c r="DF165" s="2" t="n"/>
+      <c r="DG165" s="2" t="n"/>
+      <c r="DH165" s="2" t="n"/>
+      <c r="DI165" s="1" t="n"/>
+    </row>
     <row r="166" ht="4.96" customHeight="1"/>
     <row r="167" ht="4.96" customHeight="1"/>
     <row r="168" ht="4.96" customHeight="1"/>
@@ -2010,27 +5362,6 @@
     <row r="175" ht="4.96" customHeight="1"/>
     <row r="176" ht="4.96" customHeight="1"/>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="CC20:CO22"/>
-    <mergeCell ref="CW77:DF79"/>
-    <mergeCell ref="G22:W24"/>
-    <mergeCell ref="CO20:DC22"/>
-    <mergeCell ref="W70:AN73"/>
-    <mergeCell ref="AY69:BO73"/>
-    <mergeCell ref="CC42:DE44"/>
-    <mergeCell ref="AB148:AK151"/>
-    <mergeCell ref="BP70:CD73"/>
-    <mergeCell ref="Q81:BG83"/>
-    <mergeCell ref="BD22:BI25"/>
-    <mergeCell ref="AC77:AL79"/>
-    <mergeCell ref="BU77:CD79"/>
-    <mergeCell ref="CZ148:DH150"/>
-    <mergeCell ref="BL77:BQ79"/>
-    <mergeCell ref="M152:U154"/>
-    <mergeCell ref="AY10:BT15"/>
-    <mergeCell ref="CZ81:DH83"/>
-    <mergeCell ref="CI77:CR79"/>
-  </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -2051,243 +5382,243 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>■ フォント一覧</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>フォント名</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="34" t="inlineStr">
         <is>
           <t>サイズ (pt)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="n">
+      <c r="A4" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>MS-Mincho</t>
         </is>
       </c>
-      <c r="C4" s="23" t="n">
+      <c r="C4" s="35" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="n">
+      <c r="A5" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>MS-Mincho</t>
         </is>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="35" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="n">
+      <c r="A6" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>MS-Gothic</t>
         </is>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="35" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="n">
+      <c r="A7" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>MS-Mincho</t>
         </is>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="35" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="n">
+      <c r="A8" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>MS-Mincho</t>
         </is>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="35" t="n">
         <v>12.5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="n">
+      <c r="A9" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>MS-Mincho</t>
         </is>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="35" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="n">
+      <c r="A10" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>MS-Mincho</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="35" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="n">
+      <c r="A11" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>MS-Gothic</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="35" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="n">
+      <c r="A12" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>MS-Mincho</t>
         </is>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="35" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="n">
+      <c r="A13" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>MS-Gothic</t>
         </is>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="35" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="n">
+      <c r="A14" s="35" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Helvetica</t>
         </is>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="35" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="n">
+      <c r="A15" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>AAAAAA+MS-PGothic</t>
         </is>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="35" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="35" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>AAAAAA+MS-PGothic</t>
         </is>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="35" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>■ カラーコード一覧</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>カラーコード</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="n">
+      <c r="A22" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>#000000</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr"/>
+      <c r="C22" s="36" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="n">
+      <c r="A23" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>#4F4F4F</t>
         </is>
       </c>
-      <c r="C23" s="25" t="inlineStr"/>
+      <c r="C23" s="37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2304,7 +5635,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>Page 1</t>
         </is>

--- a/data/out/mitsumori/mitsumori.xlsx
+++ b/data/out/mitsumori/mitsumori.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="変換結果" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="フォント・カラー情報" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PDF画像" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,10 +98,6 @@
     <font>
       <b val="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -242,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,7 +318,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -398,36 +392,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5715000" cy="8086725"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5623,26 +5587,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="38" t="inlineStr">
-        <is>
-          <t>Page 1</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/data/out/mitsumori/mitsumori.xlsx
+++ b/data/out/mitsumori/mitsumori.xlsx
@@ -10,7 +10,9 @@
     <sheet name="変換結果" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="フォント・カラー情報" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'変換結果'!$A$1:$DP$182</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,13 +20,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="MS-Mincho"/>
@@ -235,13 +241,13 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -251,70 +257,70 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -686,138 +692,138 @@
   <dimension ref="F10:DI165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="0.9399999999999999" customWidth="1" min="1" max="1"/>
-    <col width="0.9399999999999999" customWidth="1" min="2" max="2"/>
-    <col width="0.9399999999999999" customWidth="1" min="3" max="3"/>
-    <col width="0.9399999999999999" customWidth="1" min="4" max="4"/>
-    <col width="0.9399999999999999" customWidth="1" min="5" max="5"/>
-    <col width="0.9399999999999999" customWidth="1" min="6" max="6"/>
-    <col width="0.9399999999999999" customWidth="1" min="7" max="7"/>
-    <col width="0.9399999999999999" customWidth="1" min="8" max="8"/>
-    <col width="0.9399999999999999" customWidth="1" min="9" max="9"/>
-    <col width="0.9399999999999999" customWidth="1" min="10" max="10"/>
-    <col width="0.9399999999999999" customWidth="1" min="11" max="11"/>
-    <col width="0.9399999999999999" customWidth="1" min="12" max="12"/>
-    <col width="0.9399999999999999" customWidth="1" min="13" max="13"/>
-    <col width="0.9399999999999999" customWidth="1" min="14" max="14"/>
-    <col width="0.9399999999999999" customWidth="1" min="15" max="15"/>
-    <col width="0.9399999999999999" customWidth="1" min="16" max="16"/>
-    <col width="0.9399999999999999" customWidth="1" min="17" max="17"/>
-    <col width="0.9399999999999999" customWidth="1" min="18" max="18"/>
-    <col width="0.9399999999999999" customWidth="1" min="19" max="19"/>
-    <col width="0.9399999999999999" customWidth="1" min="20" max="20"/>
-    <col width="0.9399999999999999" customWidth="1" min="21" max="21"/>
-    <col width="0.9399999999999999" customWidth="1" min="22" max="22"/>
-    <col width="0.9399999999999999" customWidth="1" min="23" max="23"/>
-    <col width="0.9399999999999999" customWidth="1" min="24" max="24"/>
-    <col width="0.9399999999999999" customWidth="1" min="25" max="25"/>
-    <col width="0.9399999999999999" customWidth="1" min="26" max="26"/>
-    <col width="0.9399999999999999" customWidth="1" min="27" max="27"/>
-    <col width="0.9399999999999999" customWidth="1" min="28" max="28"/>
-    <col width="0.9399999999999999" customWidth="1" min="29" max="29"/>
-    <col width="0.9399999999999999" customWidth="1" min="30" max="30"/>
-    <col width="0.9399999999999999" customWidth="1" min="31" max="31"/>
-    <col width="0.9399999999999999" customWidth="1" min="32" max="32"/>
-    <col width="0.9399999999999999" customWidth="1" min="33" max="33"/>
-    <col width="0.9399999999999999" customWidth="1" min="34" max="34"/>
-    <col width="0.9399999999999999" customWidth="1" min="35" max="35"/>
-    <col width="0.9399999999999999" customWidth="1" min="36" max="36"/>
-    <col width="0.9399999999999999" customWidth="1" min="37" max="37"/>
-    <col width="0.9399999999999999" customWidth="1" min="38" max="38"/>
-    <col width="0.9399999999999999" customWidth="1" min="39" max="39"/>
-    <col width="0.9399999999999999" customWidth="1" min="40" max="40"/>
-    <col width="0.9399999999999999" customWidth="1" min="41" max="41"/>
-    <col width="0.9399999999999999" customWidth="1" min="42" max="42"/>
-    <col width="0.9399999999999999" customWidth="1" min="43" max="43"/>
-    <col width="0.9399999999999999" customWidth="1" min="44" max="44"/>
-    <col width="0.9399999999999999" customWidth="1" min="45" max="45"/>
-    <col width="0.9399999999999999" customWidth="1" min="46" max="46"/>
-    <col width="0.9399999999999999" customWidth="1" min="47" max="47"/>
-    <col width="0.9399999999999999" customWidth="1" min="48" max="48"/>
-    <col width="0.9399999999999999" customWidth="1" min="49" max="49"/>
-    <col width="0.9399999999999999" customWidth="1" min="50" max="50"/>
-    <col width="0.9399999999999999" customWidth="1" min="51" max="51"/>
-    <col width="0.9399999999999999" customWidth="1" min="52" max="52"/>
-    <col width="0.9399999999999999" customWidth="1" min="53" max="53"/>
-    <col width="0.9399999999999999" customWidth="1" min="54" max="54"/>
-    <col width="0.9399999999999999" customWidth="1" min="55" max="55"/>
-    <col width="0.9399999999999999" customWidth="1" min="56" max="56"/>
-    <col width="0.9399999999999999" customWidth="1" min="57" max="57"/>
-    <col width="0.9399999999999999" customWidth="1" min="58" max="58"/>
-    <col width="0.9399999999999999" customWidth="1" min="59" max="59"/>
-    <col width="0.9399999999999999" customWidth="1" min="60" max="60"/>
-    <col width="0.9399999999999999" customWidth="1" min="61" max="61"/>
-    <col width="0.9399999999999999" customWidth="1" min="62" max="62"/>
-    <col width="0.9399999999999999" customWidth="1" min="63" max="63"/>
-    <col width="0.9399999999999999" customWidth="1" min="64" max="64"/>
-    <col width="0.9399999999999999" customWidth="1" min="65" max="65"/>
-    <col width="0.9399999999999999" customWidth="1" min="66" max="66"/>
-    <col width="0.9399999999999999" customWidth="1" min="67" max="67"/>
-    <col width="0.9399999999999999" customWidth="1" min="68" max="68"/>
-    <col width="0.9399999999999999" customWidth="1" min="69" max="69"/>
-    <col width="0.9399999999999999" customWidth="1" min="70" max="70"/>
-    <col width="0.9399999999999999" customWidth="1" min="71" max="71"/>
-    <col width="0.9399999999999999" customWidth="1" min="72" max="72"/>
-    <col width="0.9399999999999999" customWidth="1" min="73" max="73"/>
-    <col width="0.9399999999999999" customWidth="1" min="74" max="74"/>
-    <col width="0.9399999999999999" customWidth="1" min="75" max="75"/>
-    <col width="0.9399999999999999" customWidth="1" min="76" max="76"/>
-    <col width="0.9399999999999999" customWidth="1" min="77" max="77"/>
-    <col width="0.9399999999999999" customWidth="1" min="78" max="78"/>
-    <col width="0.9399999999999999" customWidth="1" min="79" max="79"/>
-    <col width="0.9399999999999999" customWidth="1" min="80" max="80"/>
-    <col width="0.9399999999999999" customWidth="1" min="81" max="81"/>
-    <col width="0.9399999999999999" customWidth="1" min="82" max="82"/>
-    <col width="0.9399999999999999" customWidth="1" min="83" max="83"/>
-    <col width="0.9399999999999999" customWidth="1" min="84" max="84"/>
-    <col width="0.9399999999999999" customWidth="1" min="85" max="85"/>
-    <col width="0.9399999999999999" customWidth="1" min="86" max="86"/>
-    <col width="0.9399999999999999" customWidth="1" min="87" max="87"/>
-    <col width="0.9399999999999999" customWidth="1" min="88" max="88"/>
-    <col width="0.9399999999999999" customWidth="1" min="89" max="89"/>
-    <col width="0.9399999999999999" customWidth="1" min="90" max="90"/>
-    <col width="0.9399999999999999" customWidth="1" min="91" max="91"/>
-    <col width="0.9399999999999999" customWidth="1" min="92" max="92"/>
-    <col width="0.9399999999999999" customWidth="1" min="93" max="93"/>
-    <col width="0.9399999999999999" customWidth="1" min="94" max="94"/>
-    <col width="0.9399999999999999" customWidth="1" min="95" max="95"/>
-    <col width="0.9399999999999999" customWidth="1" min="96" max="96"/>
-    <col width="0.9399999999999999" customWidth="1" min="97" max="97"/>
-    <col width="0.9399999999999999" customWidth="1" min="98" max="98"/>
-    <col width="0.9399999999999999" customWidth="1" min="99" max="99"/>
-    <col width="0.9399999999999999" customWidth="1" min="100" max="100"/>
-    <col width="0.9399999999999999" customWidth="1" min="101" max="101"/>
-    <col width="0.9399999999999999" customWidth="1" min="102" max="102"/>
-    <col width="0.9399999999999999" customWidth="1" min="103" max="103"/>
-    <col width="0.9399999999999999" customWidth="1" min="104" max="104"/>
-    <col width="0.9399999999999999" customWidth="1" min="105" max="105"/>
-    <col width="0.9399999999999999" customWidth="1" min="106" max="106"/>
-    <col width="0.9399999999999999" customWidth="1" min="107" max="107"/>
-    <col width="0.9399999999999999" customWidth="1" min="108" max="108"/>
-    <col width="0.9399999999999999" customWidth="1" min="109" max="109"/>
-    <col width="0.9399999999999999" customWidth="1" min="110" max="110"/>
-    <col width="0.9399999999999999" customWidth="1" min="111" max="111"/>
-    <col width="0.9399999999999999" customWidth="1" min="112" max="112"/>
-    <col width="0.9399999999999999" customWidth="1" min="113" max="113"/>
-    <col width="0.9399999999999999" customWidth="1" min="114" max="114"/>
-    <col width="0.9399999999999999" customWidth="1" min="115" max="115"/>
-    <col width="0.9399999999999999" customWidth="1" min="116" max="116"/>
-    <col width="0.9399999999999999" customWidth="1" min="117" max="117"/>
-    <col width="0.9399999999999999" customWidth="1" min="118" max="118"/>
-    <col width="0.9399999999999999" customWidth="1" min="119" max="119"/>
-    <col width="0.9399999999999999" customWidth="1" min="120" max="120"/>
+    <col width="0.75" customWidth="1" min="1" max="1"/>
+    <col width="0.75" customWidth="1" min="2" max="2"/>
+    <col width="0.75" customWidth="1" min="3" max="3"/>
+    <col width="0.75" customWidth="1" min="4" max="4"/>
+    <col width="0.75" customWidth="1" min="5" max="5"/>
+    <col width="0.75" customWidth="1" min="6" max="6"/>
+    <col width="0.75" customWidth="1" min="7" max="7"/>
+    <col width="0.75" customWidth="1" min="8" max="8"/>
+    <col width="0.75" customWidth="1" min="9" max="9"/>
+    <col width="0.75" customWidth="1" min="10" max="10"/>
+    <col width="0.75" customWidth="1" min="11" max="11"/>
+    <col width="0.75" customWidth="1" min="12" max="12"/>
+    <col width="0.75" customWidth="1" min="13" max="13"/>
+    <col width="0.75" customWidth="1" min="14" max="14"/>
+    <col width="0.75" customWidth="1" min="15" max="15"/>
+    <col width="0.75" customWidth="1" min="16" max="16"/>
+    <col width="0.75" customWidth="1" min="17" max="17"/>
+    <col width="0.75" customWidth="1" min="18" max="18"/>
+    <col width="0.75" customWidth="1" min="19" max="19"/>
+    <col width="0.75" customWidth="1" min="20" max="20"/>
+    <col width="0.75" customWidth="1" min="21" max="21"/>
+    <col width="0.75" customWidth="1" min="22" max="22"/>
+    <col width="0.75" customWidth="1" min="23" max="23"/>
+    <col width="0.75" customWidth="1" min="24" max="24"/>
+    <col width="0.75" customWidth="1" min="25" max="25"/>
+    <col width="0.75" customWidth="1" min="26" max="26"/>
+    <col width="0.75" customWidth="1" min="27" max="27"/>
+    <col width="0.75" customWidth="1" min="28" max="28"/>
+    <col width="0.75" customWidth="1" min="29" max="29"/>
+    <col width="0.75" customWidth="1" min="30" max="30"/>
+    <col width="0.75" customWidth="1" min="31" max="31"/>
+    <col width="0.75" customWidth="1" min="32" max="32"/>
+    <col width="0.75" customWidth="1" min="33" max="33"/>
+    <col width="0.75" customWidth="1" min="34" max="34"/>
+    <col width="0.75" customWidth="1" min="35" max="35"/>
+    <col width="0.75" customWidth="1" min="36" max="36"/>
+    <col width="0.75" customWidth="1" min="37" max="37"/>
+    <col width="0.75" customWidth="1" min="38" max="38"/>
+    <col width="0.75" customWidth="1" min="39" max="39"/>
+    <col width="0.75" customWidth="1" min="40" max="40"/>
+    <col width="0.75" customWidth="1" min="41" max="41"/>
+    <col width="0.75" customWidth="1" min="42" max="42"/>
+    <col width="0.75" customWidth="1" min="43" max="43"/>
+    <col width="0.75" customWidth="1" min="44" max="44"/>
+    <col width="0.75" customWidth="1" min="45" max="45"/>
+    <col width="0.75" customWidth="1" min="46" max="46"/>
+    <col width="0.75" customWidth="1" min="47" max="47"/>
+    <col width="0.75" customWidth="1" min="48" max="48"/>
+    <col width="0.75" customWidth="1" min="49" max="49"/>
+    <col width="0.75" customWidth="1" min="50" max="50"/>
+    <col width="0.75" customWidth="1" min="51" max="51"/>
+    <col width="0.75" customWidth="1" min="52" max="52"/>
+    <col width="0.75" customWidth="1" min="53" max="53"/>
+    <col width="0.75" customWidth="1" min="54" max="54"/>
+    <col width="0.75" customWidth="1" min="55" max="55"/>
+    <col width="0.75" customWidth="1" min="56" max="56"/>
+    <col width="0.75" customWidth="1" min="57" max="57"/>
+    <col width="0.75" customWidth="1" min="58" max="58"/>
+    <col width="0.75" customWidth="1" min="59" max="59"/>
+    <col width="0.75" customWidth="1" min="60" max="60"/>
+    <col width="0.75" customWidth="1" min="61" max="61"/>
+    <col width="0.75" customWidth="1" min="62" max="62"/>
+    <col width="0.75" customWidth="1" min="63" max="63"/>
+    <col width="0.75" customWidth="1" min="64" max="64"/>
+    <col width="0.75" customWidth="1" min="65" max="65"/>
+    <col width="0.75" customWidth="1" min="66" max="66"/>
+    <col width="0.75" customWidth="1" min="67" max="67"/>
+    <col width="0.75" customWidth="1" min="68" max="68"/>
+    <col width="0.75" customWidth="1" min="69" max="69"/>
+    <col width="0.75" customWidth="1" min="70" max="70"/>
+    <col width="0.75" customWidth="1" min="71" max="71"/>
+    <col width="0.75" customWidth="1" min="72" max="72"/>
+    <col width="0.75" customWidth="1" min="73" max="73"/>
+    <col width="0.75" customWidth="1" min="74" max="74"/>
+    <col width="0.75" customWidth="1" min="75" max="75"/>
+    <col width="0.75" customWidth="1" min="76" max="76"/>
+    <col width="0.75" customWidth="1" min="77" max="77"/>
+    <col width="0.75" customWidth="1" min="78" max="78"/>
+    <col width="0.75" customWidth="1" min="79" max="79"/>
+    <col width="0.75" customWidth="1" min="80" max="80"/>
+    <col width="0.75" customWidth="1" min="81" max="81"/>
+    <col width="0.75" customWidth="1" min="82" max="82"/>
+    <col width="0.75" customWidth="1" min="83" max="83"/>
+    <col width="0.75" customWidth="1" min="84" max="84"/>
+    <col width="0.75" customWidth="1" min="85" max="85"/>
+    <col width="0.75" customWidth="1" min="86" max="86"/>
+    <col width="0.75" customWidth="1" min="87" max="87"/>
+    <col width="0.75" customWidth="1" min="88" max="88"/>
+    <col width="0.75" customWidth="1" min="89" max="89"/>
+    <col width="0.75" customWidth="1" min="90" max="90"/>
+    <col width="0.75" customWidth="1" min="91" max="91"/>
+    <col width="0.75" customWidth="1" min="92" max="92"/>
+    <col width="0.75" customWidth="1" min="93" max="93"/>
+    <col width="0.75" customWidth="1" min="94" max="94"/>
+    <col width="0.75" customWidth="1" min="95" max="95"/>
+    <col width="0.75" customWidth="1" min="96" max="96"/>
+    <col width="0.75" customWidth="1" min="97" max="97"/>
+    <col width="0.75" customWidth="1" min="98" max="98"/>
+    <col width="0.75" customWidth="1" min="99" max="99"/>
+    <col width="0.75" customWidth="1" min="100" max="100"/>
+    <col width="0.75" customWidth="1" min="101" max="101"/>
+    <col width="0.75" customWidth="1" min="102" max="102"/>
+    <col width="0.75" customWidth="1" min="103" max="103"/>
+    <col width="0.75" customWidth="1" min="104" max="104"/>
+    <col width="0.75" customWidth="1" min="105" max="105"/>
+    <col width="0.75" customWidth="1" min="106" max="106"/>
+    <col width="0.75" customWidth="1" min="107" max="107"/>
+    <col width="0.75" customWidth="1" min="108" max="108"/>
+    <col width="0.75" customWidth="1" min="109" max="109"/>
+    <col width="0.75" customWidth="1" min="110" max="110"/>
+    <col width="0.75" customWidth="1" min="111" max="111"/>
+    <col width="0.75" customWidth="1" min="112" max="112"/>
+    <col width="0.75" customWidth="1" min="113" max="113"/>
+    <col width="0.75" customWidth="1" min="114" max="114"/>
+    <col width="0.75" customWidth="1" min="115" max="115"/>
+    <col width="0.75" customWidth="1" min="116" max="116"/>
+    <col width="0.75" customWidth="1" min="117" max="117"/>
+    <col width="0.75" customWidth="1" min="118" max="118"/>
+    <col width="0.75" customWidth="1" min="119" max="119"/>
+    <col width="0.75" customWidth="1" min="120" max="120"/>
   </cols>
   <sheetData>
-    <row r="1" ht="4.96" customHeight="1"/>
-    <row r="2" ht="4.96" customHeight="1"/>
-    <row r="3" ht="4.96" customHeight="1"/>
-    <row r="4" ht="4.96" customHeight="1"/>
-    <row r="5" ht="4.96" customHeight="1"/>
-    <row r="6" ht="4.96" customHeight="1"/>
-    <row r="7" ht="4.96" customHeight="1"/>
-    <row r="8" ht="4.96" customHeight="1"/>
-    <row r="9" ht="4.96" customHeight="1"/>
-    <row r="10" ht="4.96" customHeight="1">
+    <row r="1" ht="4.65" customHeight="1"/>
+    <row r="2" ht="4.65" customHeight="1"/>
+    <row r="3" ht="4.65" customHeight="1"/>
+    <row r="4" ht="4.65" customHeight="1"/>
+    <row r="5" ht="4.65" customHeight="1"/>
+    <row r="6" ht="4.65" customHeight="1"/>
+    <row r="7" ht="4.65" customHeight="1"/>
+    <row r="8" ht="4.65" customHeight="1"/>
+    <row r="9" ht="4.65" customHeight="1"/>
+    <row r="10" ht="4.65" customHeight="1">
       <c r="AT10" s="1" t="n"/>
       <c r="AU10" s="2" t="n"/>
       <c r="AV10" s="2" t="n"/>
@@ -855,7 +861,7 @@
       <c r="BX10" s="2" t="n"/>
       <c r="BY10" s="4" t="n"/>
     </row>
-    <row r="11" ht="4.96" customHeight="1">
+    <row r="11" ht="4.65" customHeight="1">
       <c r="AT11" s="5" t="n"/>
       <c r="AU11" s="6" t="n"/>
       <c r="AV11" s="6" t="n"/>
@@ -889,7 +895,7 @@
       <c r="BX11" s="6" t="n"/>
       <c r="BY11" s="7" t="n"/>
     </row>
-    <row r="12" ht="4.96" customHeight="1">
+    <row r="12" ht="4.65" customHeight="1">
       <c r="AT12" s="5" t="n"/>
       <c r="AU12" s="6" t="n"/>
       <c r="AV12" s="6" t="n"/>
@@ -923,7 +929,7 @@
       <c r="BX12" s="6" t="n"/>
       <c r="BY12" s="7" t="n"/>
     </row>
-    <row r="13" ht="4.96" customHeight="1">
+    <row r="13" ht="4.65" customHeight="1">
       <c r="AT13" s="5" t="n"/>
       <c r="AU13" s="6" t="n"/>
       <c r="AV13" s="6" t="n"/>
@@ -957,7 +963,7 @@
       <c r="BX13" s="6" t="n"/>
       <c r="BY13" s="7" t="n"/>
     </row>
-    <row r="14" ht="4.96" customHeight="1">
+    <row r="14" ht="4.65" customHeight="1">
       <c r="AT14" s="5" t="n"/>
       <c r="AU14" s="6" t="n"/>
       <c r="AV14" s="6" t="n"/>
@@ -991,7 +997,7 @@
       <c r="BX14" s="6" t="n"/>
       <c r="BY14" s="7" t="n"/>
     </row>
-    <row r="15" ht="4.96" customHeight="1">
+    <row r="15" ht="4.65" customHeight="1">
       <c r="AT15" s="5" t="n"/>
       <c r="AU15" s="6" t="n"/>
       <c r="AV15" s="6" t="n"/>
@@ -1025,7 +1031,7 @@
       <c r="BX15" s="6" t="n"/>
       <c r="BY15" s="7" t="n"/>
     </row>
-    <row r="16" ht="4.96" customHeight="1">
+    <row r="16" ht="4.65" customHeight="1">
       <c r="AT16" s="8" t="n"/>
       <c r="AU16" s="9" t="n"/>
       <c r="AV16" s="9" t="n"/>
@@ -1059,10 +1065,10 @@
       <c r="BX16" s="9" t="n"/>
       <c r="BY16" s="10" t="n"/>
     </row>
-    <row r="17" ht="4.96" customHeight="1"/>
-    <row r="18" ht="4.96" customHeight="1"/>
-    <row r="19" ht="4.96" customHeight="1"/>
-    <row r="20" ht="4.96" customHeight="1">
+    <row r="17" ht="4.65" customHeight="1"/>
+    <row r="18" ht="4.65" customHeight="1"/>
+    <row r="19" ht="4.65" customHeight="1"/>
+    <row r="20" ht="4.65" customHeight="1">
       <c r="CC20" s="11" t="inlineStr">
         <is>
           <t>見積書Ｎｏ．</t>
@@ -1074,8 +1080,8 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="4.96" customHeight="1"/>
-    <row r="22" ht="4.96" customHeight="1">
+    <row r="21" ht="4.65" customHeight="1"/>
+    <row r="22" ht="4.65" customHeight="1">
       <c r="G22" s="12" t="inlineStr">
         <is>
           <t>△△株式会社</t>
@@ -1117,9 +1123,9 @@
       <c r="DD22" s="2" t="n"/>
       <c r="DE22" s="2" t="n"/>
     </row>
-    <row r="23" ht="4.96" customHeight="1"/>
-    <row r="24" ht="4.96" customHeight="1"/>
-    <row r="25" ht="4.96" customHeight="1">
+    <row r="23" ht="4.65" customHeight="1"/>
+    <row r="24" ht="4.65" customHeight="1"/>
+    <row r="25" ht="4.65" customHeight="1">
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
@@ -1178,7 +1184,7 @@
       <c r="BI25" s="2" t="n"/>
       <c r="BJ25" s="2" t="n"/>
     </row>
-    <row r="26" ht="4.96" customHeight="1">
+    <row r="26" ht="4.65" customHeight="1">
       <c r="CC26" s="11" t="inlineStr">
         <is>
           <t>作成日:</t>
@@ -1190,9 +1196,9 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="4.96" customHeight="1"/>
-    <row r="28" ht="4.96" customHeight="1"/>
-    <row r="29" ht="4.96" customHeight="1">
+    <row r="27" ht="4.65" customHeight="1"/>
+    <row r="28" ht="4.65" customHeight="1"/>
+    <row r="29" ht="4.65" customHeight="1">
       <c r="CB29" s="2" t="n"/>
       <c r="CC29" s="2" t="n"/>
       <c r="CD29" s="2" t="n"/>
@@ -1223,30 +1229,30 @@
       <c r="DC29" s="2" t="n"/>
       <c r="DD29" s="2" t="n"/>
     </row>
-    <row r="30" ht="4.96" customHeight="1"/>
-    <row r="31" ht="4.96" customHeight="1">
+    <row r="30" ht="4.65" customHeight="1"/>
+    <row r="31" ht="4.65" customHeight="1">
       <c r="O31" s="13" t="inlineStr">
         <is>
           <t>下記のとおり御見積申し上げます。</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="4.96" customHeight="1"/>
-    <row r="33" ht="4.96" customHeight="1"/>
-    <row r="34" ht="4.96" customHeight="1">
+    <row r="32" ht="4.65" customHeight="1"/>
+    <row r="33" ht="4.65" customHeight="1"/>
+    <row r="34" ht="4.65" customHeight="1">
       <c r="O34" s="13" t="inlineStr">
         <is>
           <t>何卒ご用命の程、お願い申し上げます。</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="4.96" customHeight="1"/>
-    <row r="36" ht="4.96" customHeight="1"/>
-    <row r="37" ht="4.96" customHeight="1"/>
-    <row r="38" ht="4.96" customHeight="1"/>
-    <row r="39" ht="4.96" customHeight="1"/>
-    <row r="40" ht="4.96" customHeight="1"/>
-    <row r="41" ht="4.96" customHeight="1">
+    <row r="35" ht="4.65" customHeight="1"/>
+    <row r="36" ht="4.65" customHeight="1"/>
+    <row r="37" ht="4.65" customHeight="1"/>
+    <row r="38" ht="4.65" customHeight="1"/>
+    <row r="39" ht="4.65" customHeight="1"/>
+    <row r="40" ht="4.65" customHeight="1"/>
+    <row r="41" ht="4.65" customHeight="1">
       <c r="F41" s="13" t="inlineStr">
         <is>
           <t>受渡期日:</t>
@@ -1258,15 +1264,15 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="4.96" customHeight="1">
+    <row r="42" ht="4.65" customHeight="1">
       <c r="CC42" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">ワークフロー商事株式会社 </t>
         </is>
       </c>
     </row>
-    <row r="43" ht="4.96" customHeight="1"/>
-    <row r="44" ht="4.96" customHeight="1">
+    <row r="43" ht="4.65" customHeight="1"/>
+    <row r="44" ht="4.65" customHeight="1">
       <c r="F44" s="2" t="n"/>
       <c r="G44" s="2" t="n"/>
       <c r="H44" s="2" t="n"/>
@@ -1325,8 +1331,8 @@
       <c r="BI44" s="2" t="n"/>
       <c r="BJ44" s="2" t="n"/>
     </row>
-    <row r="45" ht="4.96" customHeight="1"/>
-    <row r="46" ht="4.96" customHeight="1">
+    <row r="45" ht="4.65" customHeight="1"/>
+    <row r="46" ht="4.65" customHeight="1">
       <c r="F46" s="13" t="inlineStr">
         <is>
           <t>取引方法:</t>
@@ -1343,9 +1349,9 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="4.96" customHeight="1"/>
-    <row r="48" ht="4.96" customHeight="1"/>
-    <row r="49" ht="4.96" customHeight="1">
+    <row r="47" ht="4.65" customHeight="1"/>
+    <row r="48" ht="4.65" customHeight="1"/>
+    <row r="49" ht="4.65" customHeight="1">
       <c r="F49" s="2" t="n"/>
       <c r="G49" s="2" t="n"/>
       <c r="H49" s="2" t="n"/>
@@ -1409,8 +1415,8 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="4.96" customHeight="1"/>
-    <row r="51" ht="4.96" customHeight="1">
+    <row r="50" ht="4.65" customHeight="1"/>
+    <row r="51" ht="4.65" customHeight="1">
       <c r="F51" s="13" t="inlineStr">
         <is>
           <t>有効期限:</t>
@@ -1427,9 +1433,9 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="4.96" customHeight="1"/>
-    <row r="53" ht="4.96" customHeight="1"/>
-    <row r="54" ht="4.96" customHeight="1">
+    <row r="52" ht="4.65" customHeight="1"/>
+    <row r="53" ht="4.65" customHeight="1"/>
+    <row r="54" ht="4.65" customHeight="1">
       <c r="F54" s="2" t="n"/>
       <c r="G54" s="2" t="n"/>
       <c r="H54" s="2" t="n"/>
@@ -1493,22 +1499,22 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="4.96" customHeight="1"/>
-    <row r="56" ht="4.96" customHeight="1">
+    <row r="55" ht="4.65" customHeight="1"/>
+    <row r="56" ht="4.65" customHeight="1">
       <c r="CD56" s="11" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
     </row>
-    <row r="57" ht="4.96" customHeight="1">
+    <row r="57" ht="4.65" customHeight="1">
       <c r="F57" s="13" t="inlineStr">
         <is>
           <t>貴社管理番号：</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="4.96" customHeight="1">
+    <row r="58" ht="4.65" customHeight="1">
       <c r="CM58" s="1" t="n"/>
       <c r="CN58" s="2" t="n"/>
       <c r="CO58" s="2" t="n"/>
@@ -1531,7 +1537,7 @@
       <c r="DF58" s="2" t="n"/>
       <c r="DG58" s="1" t="n"/>
     </row>
-    <row r="59" ht="4.96" customHeight="1">
+    <row r="59" ht="4.65" customHeight="1">
       <c r="CM59" s="5" t="n"/>
       <c r="CP59" s="15" t="inlineStr">
         <is>
@@ -1546,7 +1552,7 @@
       </c>
       <c r="DG59" s="5" t="n"/>
     </row>
-    <row r="60" ht="4.96" customHeight="1">
+    <row r="60" ht="4.65" customHeight="1">
       <c r="F60" s="2" t="n"/>
       <c r="G60" s="2" t="n"/>
       <c r="H60" s="2" t="n"/>
@@ -1612,42 +1618,42 @@
       <c r="DF60" s="2" t="n"/>
       <c r="DG60" s="1" t="n"/>
     </row>
-    <row r="61" ht="4.96" customHeight="1">
+    <row r="61" ht="4.65" customHeight="1">
       <c r="CM61" s="5" t="n"/>
       <c r="CW61" s="5" t="n"/>
       <c r="DG61" s="5" t="n"/>
     </row>
-    <row r="62" ht="4.96" customHeight="1">
+    <row r="62" ht="4.65" customHeight="1">
       <c r="CM62" s="5" t="n"/>
       <c r="CW62" s="5" t="n"/>
       <c r="DG62" s="5" t="n"/>
     </row>
-    <row r="63" ht="4.96" customHeight="1">
+    <row r="63" ht="4.65" customHeight="1">
       <c r="CM63" s="5" t="n"/>
       <c r="CW63" s="5" t="n"/>
       <c r="DG63" s="5" t="n"/>
     </row>
-    <row r="64" ht="4.96" customHeight="1">
+    <row r="64" ht="4.65" customHeight="1">
       <c r="CM64" s="5" t="n"/>
       <c r="CW64" s="5" t="n"/>
       <c r="DG64" s="5" t="n"/>
     </row>
-    <row r="65" ht="4.96" customHeight="1">
+    <row r="65" ht="4.65" customHeight="1">
       <c r="CM65" s="5" t="n"/>
       <c r="CW65" s="5" t="n"/>
       <c r="DG65" s="5" t="n"/>
     </row>
-    <row r="66" ht="4.96" customHeight="1">
+    <row r="66" ht="4.65" customHeight="1">
       <c r="CM66" s="5" t="n"/>
       <c r="CW66" s="5" t="n"/>
       <c r="DG66" s="5" t="n"/>
     </row>
-    <row r="67" ht="4.96" customHeight="1">
+    <row r="67" ht="4.65" customHeight="1">
       <c r="CM67" s="5" t="n"/>
       <c r="CW67" s="5" t="n"/>
       <c r="DG67" s="5" t="n"/>
     </row>
-    <row r="68" ht="4.96" customHeight="1">
+    <row r="68" ht="4.65" customHeight="1">
       <c r="CM68" s="1" t="n"/>
       <c r="CN68" s="2" t="n"/>
       <c r="CO68" s="2" t="n"/>
@@ -1670,14 +1676,14 @@
       <c r="DF68" s="2" t="n"/>
       <c r="DG68" s="1" t="n"/>
     </row>
-    <row r="69" ht="4.96" customHeight="1">
+    <row r="69" ht="4.65" customHeight="1">
       <c r="AY69" s="16" t="inlineStr">
         <is>
           <t>\3,700,000</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="4.96" customHeight="1">
+    <row r="70" ht="4.65" customHeight="1">
       <c r="W70" s="17" t="inlineStr">
         <is>
           <t>合計金額：</t>
@@ -1689,10 +1695,10 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="4.96" customHeight="1"/>
-    <row r="72" ht="4.96" customHeight="1"/>
-    <row r="73" ht="4.96" customHeight="1"/>
-    <row r="74" ht="4.96" customHeight="1">
+    <row r="71" ht="4.65" customHeight="1"/>
+    <row r="72" ht="4.65" customHeight="1"/>
+    <row r="73" ht="4.65" customHeight="1"/>
+    <row r="74" ht="4.65" customHeight="1">
       <c r="L74" s="19" t="n"/>
       <c r="M74" s="19" t="n"/>
       <c r="N74" s="19" t="n"/>
@@ -1796,9 +1802,9 @@
       <c r="DH74" s="19" t="n"/>
       <c r="DI74" s="19" t="n"/>
     </row>
-    <row r="75" ht="4.96" customHeight="1"/>
-    <row r="76" ht="4.96" customHeight="1"/>
-    <row r="77" ht="4.96" customHeight="1">
+    <row r="75" ht="4.65" customHeight="1"/>
+    <row r="76" ht="4.65" customHeight="1"/>
+    <row r="77" ht="4.65" customHeight="1">
       <c r="L77" s="20" t="inlineStr">
         <is>
           <t>No.</t>
@@ -1926,7 +1932,7 @@
       <c r="DH77" s="2" t="n"/>
       <c r="DI77" s="1" t="n"/>
     </row>
-    <row r="78" ht="4.96" customHeight="1">
+    <row r="78" ht="4.65" customHeight="1">
       <c r="L78" s="5" t="n"/>
       <c r="P78" s="5" t="n"/>
       <c r="BK78" s="5" t="n"/>
@@ -1935,7 +1941,7 @@
       <c r="CT78" s="5" t="n"/>
       <c r="DI78" s="5" t="n"/>
     </row>
-    <row r="79" ht="4.96" customHeight="1">
+    <row r="79" ht="4.65" customHeight="1">
       <c r="L79" s="1" t="n"/>
       <c r="M79" s="2" t="n"/>
       <c r="N79" s="2" t="n"/>
@@ -2039,7 +2045,7 @@
       <c r="DH79" s="2" t="n"/>
       <c r="DI79" s="1" t="n"/>
     </row>
-    <row r="80" ht="4.96" customHeight="1">
+    <row r="80" ht="4.65" customHeight="1">
       <c r="L80" s="1" t="n"/>
       <c r="M80" s="2" t="n"/>
       <c r="N80" s="2" t="n"/>
@@ -2143,7 +2149,7 @@
       <c r="DH80" s="2" t="n"/>
       <c r="DI80" s="1" t="n"/>
     </row>
-    <row r="81" ht="4.96" customHeight="1">
+    <row r="81" ht="4.65" customHeight="1">
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="22" t="inlineStr">
         <is>
@@ -2182,7 +2188,7 @@
       </c>
       <c r="DI81" s="5" t="n"/>
     </row>
-    <row r="82" ht="4.96" customHeight="1">
+    <row r="82" ht="4.65" customHeight="1">
       <c r="L82" s="5" t="n"/>
       <c r="P82" s="5" t="n"/>
       <c r="BK82" s="5" t="n"/>
@@ -2191,7 +2197,7 @@
       <c r="CT82" s="5" t="n"/>
       <c r="DI82" s="5" t="n"/>
     </row>
-    <row r="83" ht="4.96" customHeight="1">
+    <row r="83" ht="4.65" customHeight="1">
       <c r="L83" s="1" t="n"/>
       <c r="M83" s="2" t="n"/>
       <c r="N83" s="2" t="n"/>
@@ -2295,7 +2301,7 @@
       <c r="DH83" s="2" t="n"/>
       <c r="DI83" s="1" t="n"/>
     </row>
-    <row r="84" ht="4.96" customHeight="1">
+    <row r="84" ht="4.65" customHeight="1">
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="22" t="inlineStr">
         <is>
@@ -2334,7 +2340,7 @@
       </c>
       <c r="DI84" s="5" t="n"/>
     </row>
-    <row r="85" ht="4.96" customHeight="1">
+    <row r="85" ht="4.65" customHeight="1">
       <c r="L85" s="5" t="n"/>
       <c r="P85" s="5" t="n"/>
       <c r="BK85" s="5" t="n"/>
@@ -2343,7 +2349,7 @@
       <c r="CT85" s="5" t="n"/>
       <c r="DI85" s="5" t="n"/>
     </row>
-    <row r="86" ht="4.96" customHeight="1">
+    <row r="86" ht="4.65" customHeight="1">
       <c r="L86" s="5" t="n"/>
       <c r="P86" s="5" t="n"/>
       <c r="BK86" s="5" t="n"/>
@@ -2352,7 +2358,7 @@
       <c r="CT86" s="5" t="n"/>
       <c r="DI86" s="5" t="n"/>
     </row>
-    <row r="87" ht="4.96" customHeight="1">
+    <row r="87" ht="4.65" customHeight="1">
       <c r="L87" s="1" t="n"/>
       <c r="M87" s="24" t="inlineStr">
         <is>
@@ -2480,7 +2486,7 @@
       <c r="DH87" s="2" t="n"/>
       <c r="DI87" s="1" t="n"/>
     </row>
-    <row r="88" ht="4.96" customHeight="1">
+    <row r="88" ht="4.65" customHeight="1">
       <c r="L88" s="5" t="n"/>
       <c r="P88" s="5" t="n"/>
       <c r="BK88" s="5" t="n"/>
@@ -2489,7 +2495,7 @@
       <c r="CT88" s="5" t="n"/>
       <c r="DI88" s="5" t="n"/>
     </row>
-    <row r="89" ht="4.96" customHeight="1">
+    <row r="89" ht="4.65" customHeight="1">
       <c r="L89" s="5" t="n"/>
       <c r="P89" s="5" t="n"/>
       <c r="BK89" s="5" t="n"/>
@@ -2498,7 +2504,7 @@
       <c r="CT89" s="5" t="n"/>
       <c r="DI89" s="5" t="n"/>
     </row>
-    <row r="90" ht="4.96" customHeight="1">
+    <row r="90" ht="4.65" customHeight="1">
       <c r="L90" s="1" t="n"/>
       <c r="M90" s="2" t="n"/>
       <c r="N90" s="2" t="n"/>
@@ -2602,7 +2608,7 @@
       <c r="DH90" s="2" t="n"/>
       <c r="DI90" s="1" t="n"/>
     </row>
-    <row r="91" ht="4.96" customHeight="1">
+    <row r="91" ht="4.65" customHeight="1">
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="22" t="inlineStr">
         <is>
@@ -2616,7 +2622,7 @@
       <c r="CT91" s="5" t="n"/>
       <c r="DI91" s="5" t="n"/>
     </row>
-    <row r="92" ht="4.96" customHeight="1">
+    <row r="92" ht="4.65" customHeight="1">
       <c r="L92" s="5" t="n"/>
       <c r="P92" s="5" t="n"/>
       <c r="BK92" s="5" t="n"/>
@@ -2625,7 +2631,7 @@
       <c r="CT92" s="5" t="n"/>
       <c r="DI92" s="5" t="n"/>
     </row>
-    <row r="93" ht="4.96" customHeight="1">
+    <row r="93" ht="4.65" customHeight="1">
       <c r="L93" s="1" t="n"/>
       <c r="M93" s="2" t="n"/>
       <c r="N93" s="2" t="n"/>
@@ -2729,7 +2735,7 @@
       <c r="DH93" s="2" t="n"/>
       <c r="DI93" s="1" t="n"/>
     </row>
-    <row r="94" ht="4.96" customHeight="1">
+    <row r="94" ht="4.65" customHeight="1">
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="22" t="inlineStr">
         <is>
@@ -2743,7 +2749,7 @@
       <c r="CT94" s="5" t="n"/>
       <c r="DI94" s="5" t="n"/>
     </row>
-    <row r="95" ht="4.96" customHeight="1">
+    <row r="95" ht="4.65" customHeight="1">
       <c r="L95" s="5" t="n"/>
       <c r="P95" s="5" t="n"/>
       <c r="BK95" s="5" t="n"/>
@@ -2752,7 +2758,7 @@
       <c r="CT95" s="5" t="n"/>
       <c r="DI95" s="5" t="n"/>
     </row>
-    <row r="96" ht="4.96" customHeight="1">
+    <row r="96" ht="4.65" customHeight="1">
       <c r="L96" s="5" t="n"/>
       <c r="P96" s="5" t="n"/>
       <c r="BK96" s="5" t="n"/>
@@ -2761,7 +2767,7 @@
       <c r="CT96" s="5" t="n"/>
       <c r="DI96" s="5" t="n"/>
     </row>
-    <row r="97" ht="4.96" customHeight="1">
+    <row r="97" ht="4.65" customHeight="1">
       <c r="L97" s="1" t="n"/>
       <c r="M97" s="2" t="n"/>
       <c r="N97" s="2" t="n"/>
@@ -2865,7 +2871,7 @@
       <c r="DH97" s="2" t="n"/>
       <c r="DI97" s="1" t="n"/>
     </row>
-    <row r="98" ht="4.96" customHeight="1">
+    <row r="98" ht="4.65" customHeight="1">
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="22" t="inlineStr">
         <is>
@@ -2879,7 +2885,7 @@
       <c r="CT98" s="5" t="n"/>
       <c r="DI98" s="5" t="n"/>
     </row>
-    <row r="99" ht="4.96" customHeight="1">
+    <row r="99" ht="4.65" customHeight="1">
       <c r="L99" s="5" t="n"/>
       <c r="P99" s="5" t="n"/>
       <c r="BK99" s="5" t="n"/>
@@ -2888,7 +2894,7 @@
       <c r="CT99" s="5" t="n"/>
       <c r="DI99" s="5" t="n"/>
     </row>
-    <row r="100" ht="4.96" customHeight="1">
+    <row r="100" ht="4.65" customHeight="1">
       <c r="L100" s="1" t="n"/>
       <c r="M100" s="2" t="n"/>
       <c r="N100" s="2" t="n"/>
@@ -2992,7 +2998,7 @@
       <c r="DH100" s="2" t="n"/>
       <c r="DI100" s="1" t="n"/>
     </row>
-    <row r="101" ht="4.96" customHeight="1">
+    <row r="101" ht="4.65" customHeight="1">
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="22" t="inlineStr">
         <is>
@@ -3006,7 +3012,7 @@
       <c r="CT101" s="5" t="n"/>
       <c r="DI101" s="5" t="n"/>
     </row>
-    <row r="102" ht="4.96" customHeight="1">
+    <row r="102" ht="4.65" customHeight="1">
       <c r="L102" s="5" t="n"/>
       <c r="P102" s="5" t="n"/>
       <c r="BK102" s="5" t="n"/>
@@ -3015,7 +3021,7 @@
       <c r="CT102" s="5" t="n"/>
       <c r="DI102" s="5" t="n"/>
     </row>
-    <row r="103" ht="4.96" customHeight="1">
+    <row r="103" ht="4.65" customHeight="1">
       <c r="L103" s="5" t="n"/>
       <c r="P103" s="5" t="n"/>
       <c r="BK103" s="5" t="n"/>
@@ -3024,7 +3030,7 @@
       <c r="CT103" s="5" t="n"/>
       <c r="DI103" s="5" t="n"/>
     </row>
-    <row r="104" ht="4.96" customHeight="1">
+    <row r="104" ht="4.65" customHeight="1">
       <c r="L104" s="1" t="n"/>
       <c r="M104" s="24" t="inlineStr">
         <is>
@@ -3132,7 +3138,7 @@
       <c r="DH104" s="2" t="n"/>
       <c r="DI104" s="1" t="n"/>
     </row>
-    <row r="105" ht="4.96" customHeight="1">
+    <row r="105" ht="4.65" customHeight="1">
       <c r="L105" s="5" t="n"/>
       <c r="P105" s="5" t="n"/>
       <c r="BK105" s="5" t="n"/>
@@ -3141,7 +3147,7 @@
       <c r="CT105" s="5" t="n"/>
       <c r="DI105" s="5" t="n"/>
     </row>
-    <row r="106" ht="4.96" customHeight="1">
+    <row r="106" ht="4.65" customHeight="1">
       <c r="L106" s="5" t="n"/>
       <c r="P106" s="5" t="n"/>
       <c r="BK106" s="5" t="n"/>
@@ -3150,7 +3156,7 @@
       <c r="CT106" s="5" t="n"/>
       <c r="DI106" s="5" t="n"/>
     </row>
-    <row r="107" ht="4.96" customHeight="1">
+    <row r="107" ht="4.65" customHeight="1">
       <c r="L107" s="1" t="n"/>
       <c r="M107" s="2" t="n"/>
       <c r="N107" s="2" t="n"/>
@@ -3254,7 +3260,7 @@
       <c r="DH107" s="2" t="n"/>
       <c r="DI107" s="1" t="n"/>
     </row>
-    <row r="108" ht="4.96" customHeight="1">
+    <row r="108" ht="4.65" customHeight="1">
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="22" t="inlineStr">
         <is>
@@ -3268,7 +3274,7 @@
       <c r="CT108" s="5" t="n"/>
       <c r="DI108" s="5" t="n"/>
     </row>
-    <row r="109" ht="4.96" customHeight="1">
+    <row r="109" ht="4.65" customHeight="1">
       <c r="L109" s="5" t="n"/>
       <c r="P109" s="5" t="n"/>
       <c r="BK109" s="5" t="n"/>
@@ -3277,7 +3283,7 @@
       <c r="CT109" s="5" t="n"/>
       <c r="DI109" s="5" t="n"/>
     </row>
-    <row r="110" ht="4.96" customHeight="1">
+    <row r="110" ht="4.65" customHeight="1">
       <c r="L110" s="1" t="n"/>
       <c r="M110" s="2" t="n"/>
       <c r="N110" s="2" t="n"/>
@@ -3381,7 +3387,7 @@
       <c r="DH110" s="2" t="n"/>
       <c r="DI110" s="1" t="n"/>
     </row>
-    <row r="111" ht="4.96" customHeight="1">
+    <row r="111" ht="4.65" customHeight="1">
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="22" t="inlineStr">
         <is>
@@ -3395,7 +3401,7 @@
       <c r="CT111" s="5" t="n"/>
       <c r="DI111" s="5" t="n"/>
     </row>
-    <row r="112" ht="4.96" customHeight="1">
+    <row r="112" ht="4.65" customHeight="1">
       <c r="L112" s="5" t="n"/>
       <c r="P112" s="5" t="n"/>
       <c r="BK112" s="5" t="n"/>
@@ -3404,7 +3410,7 @@
       <c r="CT112" s="5" t="n"/>
       <c r="DI112" s="5" t="n"/>
     </row>
-    <row r="113" ht="4.96" customHeight="1">
+    <row r="113" ht="4.65" customHeight="1">
       <c r="L113" s="5" t="n"/>
       <c r="P113" s="5" t="n"/>
       <c r="BK113" s="5" t="n"/>
@@ -3413,7 +3419,7 @@
       <c r="CT113" s="5" t="n"/>
       <c r="DI113" s="5" t="n"/>
     </row>
-    <row r="114" ht="4.96" customHeight="1">
+    <row r="114" ht="4.65" customHeight="1">
       <c r="K114" s="2" t="n"/>
       <c r="L114" s="1" t="n"/>
       <c r="M114" s="2" t="n"/>
@@ -3518,7 +3524,7 @@
       <c r="DH114" s="2" t="n"/>
       <c r="DI114" s="1" t="n"/>
     </row>
-    <row r="115" ht="4.96" customHeight="1">
+    <row r="115" ht="4.65" customHeight="1">
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="22" t="inlineStr">
         <is>
@@ -3532,7 +3538,7 @@
       <c r="CT115" s="5" t="n"/>
       <c r="DI115" s="5" t="n"/>
     </row>
-    <row r="116" ht="4.96" customHeight="1">
+    <row r="116" ht="4.65" customHeight="1">
       <c r="L116" s="5" t="n"/>
       <c r="P116" s="5" t="n"/>
       <c r="BK116" s="5" t="n"/>
@@ -3541,7 +3547,7 @@
       <c r="CT116" s="5" t="n"/>
       <c r="DI116" s="5" t="n"/>
     </row>
-    <row r="117" ht="4.96" customHeight="1">
+    <row r="117" ht="4.65" customHeight="1">
       <c r="L117" s="1" t="n"/>
       <c r="M117" s="2" t="n"/>
       <c r="N117" s="2" t="n"/>
@@ -3645,7 +3651,7 @@
       <c r="DH117" s="2" t="n"/>
       <c r="DI117" s="1" t="n"/>
     </row>
-    <row r="118" ht="4.96" customHeight="1">
+    <row r="118" ht="4.65" customHeight="1">
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="22" t="inlineStr">
         <is>
@@ -3659,7 +3665,7 @@
       <c r="CT118" s="5" t="n"/>
       <c r="DI118" s="5" t="n"/>
     </row>
-    <row r="119" ht="4.96" customHeight="1">
+    <row r="119" ht="4.65" customHeight="1">
       <c r="L119" s="5" t="n"/>
       <c r="P119" s="5" t="n"/>
       <c r="BK119" s="5" t="n"/>
@@ -3668,7 +3674,7 @@
       <c r="CT119" s="5" t="n"/>
       <c r="DI119" s="5" t="n"/>
     </row>
-    <row r="120" ht="4.96" customHeight="1">
+    <row r="120" ht="4.65" customHeight="1">
       <c r="L120" s="5" t="n"/>
       <c r="P120" s="5" t="n"/>
       <c r="BK120" s="5" t="n"/>
@@ -3677,7 +3683,7 @@
       <c r="CT120" s="5" t="n"/>
       <c r="DI120" s="5" t="n"/>
     </row>
-    <row r="121" ht="4.96" customHeight="1">
+    <row r="121" ht="4.65" customHeight="1">
       <c r="K121" s="2" t="n"/>
       <c r="L121" s="1" t="n"/>
       <c r="M121" s="2" t="n"/>
@@ -3782,7 +3788,7 @@
       <c r="DH121" s="2" t="n"/>
       <c r="DI121" s="1" t="n"/>
     </row>
-    <row r="122" ht="4.96" customHeight="1">
+    <row r="122" ht="4.65" customHeight="1">
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="22" t="inlineStr">
         <is>
@@ -3796,7 +3802,7 @@
       <c r="CT122" s="5" t="n"/>
       <c r="DI122" s="5" t="n"/>
     </row>
-    <row r="123" ht="4.96" customHeight="1">
+    <row r="123" ht="4.65" customHeight="1">
       <c r="L123" s="5" t="n"/>
       <c r="P123" s="5" t="n"/>
       <c r="BK123" s="5" t="n"/>
@@ -3805,7 +3811,7 @@
       <c r="CT123" s="5" t="n"/>
       <c r="DI123" s="5" t="n"/>
     </row>
-    <row r="124" ht="4.96" customHeight="1">
+    <row r="124" ht="4.65" customHeight="1">
       <c r="K124" s="2" t="n"/>
       <c r="L124" s="1" t="n"/>
       <c r="M124" s="2" t="n"/>
@@ -3910,7 +3916,7 @@
       <c r="DH124" s="2" t="n"/>
       <c r="DI124" s="1" t="n"/>
     </row>
-    <row r="125" ht="4.96" customHeight="1">
+    <row r="125" ht="4.65" customHeight="1">
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="22" t="inlineStr">
         <is>
@@ -3924,7 +3930,7 @@
       <c r="CT125" s="5" t="n"/>
       <c r="DI125" s="5" t="n"/>
     </row>
-    <row r="126" ht="4.96" customHeight="1">
+    <row r="126" ht="4.65" customHeight="1">
       <c r="L126" s="5" t="n"/>
       <c r="P126" s="5" t="n"/>
       <c r="BK126" s="5" t="n"/>
@@ -3933,7 +3939,7 @@
       <c r="CT126" s="5" t="n"/>
       <c r="DI126" s="5" t="n"/>
     </row>
-    <row r="127" ht="4.96" customHeight="1">
+    <row r="127" ht="4.65" customHeight="1">
       <c r="L127" s="5" t="n"/>
       <c r="P127" s="5" t="n"/>
       <c r="BK127" s="5" t="n"/>
@@ -3942,7 +3948,7 @@
       <c r="CT127" s="5" t="n"/>
       <c r="DI127" s="5" t="n"/>
     </row>
-    <row r="128" ht="4.96" customHeight="1">
+    <row r="128" ht="4.65" customHeight="1">
       <c r="L128" s="1" t="n"/>
       <c r="M128" s="24" t="inlineStr">
         <is>
@@ -4050,7 +4056,7 @@
       <c r="DH128" s="2" t="n"/>
       <c r="DI128" s="1" t="n"/>
     </row>
-    <row r="129" ht="4.96" customHeight="1">
+    <row r="129" ht="4.65" customHeight="1">
       <c r="L129" s="5" t="n"/>
       <c r="P129" s="5" t="n"/>
       <c r="BK129" s="5" t="n"/>
@@ -4059,7 +4065,7 @@
       <c r="CT129" s="5" t="n"/>
       <c r="DI129" s="5" t="n"/>
     </row>
-    <row r="130" ht="4.96" customHeight="1">
+    <row r="130" ht="4.65" customHeight="1">
       <c r="L130" s="5" t="n"/>
       <c r="P130" s="5" t="n"/>
       <c r="BK130" s="5" t="n"/>
@@ -4068,7 +4074,7 @@
       <c r="CT130" s="5" t="n"/>
       <c r="DI130" s="5" t="n"/>
     </row>
-    <row r="131" ht="4.96" customHeight="1">
+    <row r="131" ht="4.65" customHeight="1">
       <c r="L131" s="1" t="n"/>
       <c r="M131" s="2" t="n"/>
       <c r="N131" s="2" t="n"/>
@@ -4172,7 +4178,7 @@
       <c r="DH131" s="2" t="n"/>
       <c r="DI131" s="1" t="n"/>
     </row>
-    <row r="132" ht="4.96" customHeight="1">
+    <row r="132" ht="4.65" customHeight="1">
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="22" t="inlineStr">
         <is>
@@ -4186,7 +4192,7 @@
       <c r="CT132" s="5" t="n"/>
       <c r="DI132" s="5" t="n"/>
     </row>
-    <row r="133" ht="4.96" customHeight="1">
+    <row r="133" ht="4.65" customHeight="1">
       <c r="L133" s="5" t="n"/>
       <c r="P133" s="5" t="n"/>
       <c r="BK133" s="5" t="n"/>
@@ -4195,7 +4201,7 @@
       <c r="CT133" s="5" t="n"/>
       <c r="DI133" s="5" t="n"/>
     </row>
-    <row r="134" ht="4.96" customHeight="1">
+    <row r="134" ht="4.65" customHeight="1">
       <c r="K134" s="2" t="n"/>
       <c r="L134" s="1" t="n"/>
       <c r="M134" s="2" t="n"/>
@@ -4300,7 +4306,7 @@
       <c r="DH134" s="2" t="n"/>
       <c r="DI134" s="1" t="n"/>
     </row>
-    <row r="135" ht="4.96" customHeight="1">
+    <row r="135" ht="4.65" customHeight="1">
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="22" t="inlineStr">
         <is>
@@ -4314,7 +4320,7 @@
       <c r="CT135" s="5" t="n"/>
       <c r="DI135" s="5" t="n"/>
     </row>
-    <row r="136" ht="4.96" customHeight="1">
+    <row r="136" ht="4.65" customHeight="1">
       <c r="L136" s="5" t="n"/>
       <c r="P136" s="5" t="n"/>
       <c r="BK136" s="5" t="n"/>
@@ -4323,7 +4329,7 @@
       <c r="CT136" s="5" t="n"/>
       <c r="DI136" s="5" t="n"/>
     </row>
-    <row r="137" ht="4.96" customHeight="1">
+    <row r="137" ht="4.65" customHeight="1">
       <c r="L137" s="5" t="n"/>
       <c r="P137" s="5" t="n"/>
       <c r="BK137" s="5" t="n"/>
@@ -4332,7 +4338,7 @@
       <c r="CT137" s="5" t="n"/>
       <c r="DI137" s="5" t="n"/>
     </row>
-    <row r="138" ht="4.96" customHeight="1">
+    <row r="138" ht="4.65" customHeight="1">
       <c r="K138" s="2" t="n"/>
       <c r="L138" s="1" t="n"/>
       <c r="M138" s="2" t="n"/>
@@ -4437,7 +4443,7 @@
       <c r="DH138" s="2" t="n"/>
       <c r="DI138" s="1" t="n"/>
     </row>
-    <row r="139" ht="4.96" customHeight="1">
+    <row r="139" ht="4.65" customHeight="1">
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="22" t="inlineStr">
         <is>
@@ -4451,7 +4457,7 @@
       <c r="CT139" s="5" t="n"/>
       <c r="DI139" s="5" t="n"/>
     </row>
-    <row r="140" ht="4.96" customHeight="1">
+    <row r="140" ht="4.65" customHeight="1">
       <c r="L140" s="5" t="n"/>
       <c r="P140" s="5" t="n"/>
       <c r="BK140" s="5" t="n"/>
@@ -4460,7 +4466,7 @@
       <c r="CT140" s="5" t="n"/>
       <c r="DI140" s="5" t="n"/>
     </row>
-    <row r="141" ht="4.96" customHeight="1">
+    <row r="141" ht="4.65" customHeight="1">
       <c r="L141" s="1" t="n"/>
       <c r="M141" s="2" t="n"/>
       <c r="N141" s="2" t="n"/>
@@ -4564,7 +4570,7 @@
       <c r="DH141" s="2" t="n"/>
       <c r="DI141" s="1" t="n"/>
     </row>
-    <row r="142" ht="4.96" customHeight="1">
+    <row r="142" ht="4.65" customHeight="1">
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="22" t="inlineStr">
         <is>
@@ -4578,7 +4584,7 @@
       <c r="CT142" s="5" t="n"/>
       <c r="DI142" s="5" t="n"/>
     </row>
-    <row r="143" ht="4.96" customHeight="1">
+    <row r="143" ht="4.65" customHeight="1">
       <c r="L143" s="5" t="n"/>
       <c r="P143" s="5" t="n"/>
       <c r="BK143" s="5" t="n"/>
@@ -4587,7 +4593,7 @@
       <c r="CT143" s="5" t="n"/>
       <c r="DI143" s="5" t="n"/>
     </row>
-    <row r="144" ht="4.96" customHeight="1">
+    <row r="144" ht="4.65" customHeight="1">
       <c r="L144" s="5" t="n"/>
       <c r="P144" s="5" t="n"/>
       <c r="BK144" s="5" t="n"/>
@@ -4596,7 +4602,7 @@
       <c r="CT144" s="5" t="n"/>
       <c r="DI144" s="5" t="n"/>
     </row>
-    <row r="145" ht="4.96" customHeight="1">
+    <row r="145" ht="4.65" customHeight="1">
       <c r="L145" s="1" t="n"/>
       <c r="M145" s="24" t="inlineStr">
         <is>
@@ -4704,7 +4710,7 @@
       <c r="DH145" s="2" t="n"/>
       <c r="DI145" s="1" t="n"/>
     </row>
-    <row r="146" ht="4.96" customHeight="1">
+    <row r="146" ht="4.65" customHeight="1">
       <c r="L146" s="5" t="n"/>
       <c r="P146" s="5" t="n"/>
       <c r="BK146" s="5" t="n"/>
@@ -4713,7 +4719,7 @@
       <c r="CT146" s="5" t="n"/>
       <c r="DI146" s="5" t="n"/>
     </row>
-    <row r="147" ht="4.96" customHeight="1">
+    <row r="147" ht="4.65" customHeight="1">
       <c r="L147" s="5" t="n"/>
       <c r="P147" s="5" t="n"/>
       <c r="BK147" s="5" t="n"/>
@@ -4722,7 +4728,7 @@
       <c r="CT147" s="5" t="n"/>
       <c r="DI147" s="5" t="n"/>
     </row>
-    <row r="148" ht="4.96" customHeight="1">
+    <row r="148" ht="4.65" customHeight="1">
       <c r="L148" s="27" t="n"/>
       <c r="M148" s="19" t="n"/>
       <c r="N148" s="19" t="n"/>
@@ -4834,15 +4840,15 @@
       <c r="DH148" s="19" t="n"/>
       <c r="DI148" s="27" t="n"/>
     </row>
-    <row r="149" ht="4.96" customHeight="1">
+    <row r="149" ht="4.65" customHeight="1">
       <c r="L149" s="5" t="n"/>
       <c r="DI149" s="5" t="n"/>
     </row>
-    <row r="150" ht="4.96" customHeight="1">
+    <row r="150" ht="4.65" customHeight="1">
       <c r="L150" s="5" t="n"/>
       <c r="DI150" s="5" t="n"/>
     </row>
-    <row r="151" ht="4.96" customHeight="1">
+    <row r="151" ht="4.65" customHeight="1">
       <c r="L151" s="1" t="n"/>
       <c r="M151" s="2" t="n"/>
       <c r="N151" s="2" t="n"/>
@@ -4946,7 +4952,7 @@
       <c r="DH151" s="2" t="n"/>
       <c r="DI151" s="1" t="n"/>
     </row>
-    <row r="152" ht="4.96" customHeight="1">
+    <row r="152" ht="4.65" customHeight="1">
       <c r="L152" s="1" t="n"/>
       <c r="M152" s="30" t="inlineStr">
         <is>
@@ -5054,15 +5060,15 @@
       <c r="DH152" s="2" t="n"/>
       <c r="DI152" s="1" t="n"/>
     </row>
-    <row r="153" ht="4.96" customHeight="1">
+    <row r="153" ht="4.65" customHeight="1">
       <c r="L153" s="5" t="n"/>
       <c r="DI153" s="5" t="n"/>
     </row>
-    <row r="154" ht="4.96" customHeight="1">
+    <row r="154" ht="4.65" customHeight="1">
       <c r="L154" s="5" t="n"/>
       <c r="DI154" s="5" t="n"/>
     </row>
-    <row r="155" ht="4.96" customHeight="1">
+    <row r="155" ht="4.65" customHeight="1">
       <c r="L155" s="31" t="inlineStr">
         <is>
           <t>・消費税は別途計上させていただきます。</t>
@@ -5170,15 +5176,15 @@
       <c r="DH155" s="2" t="n"/>
       <c r="DI155" s="1" t="n"/>
     </row>
-    <row r="156" ht="4.96" customHeight="1">
+    <row r="156" ht="4.65" customHeight="1">
       <c r="L156" s="5" t="n"/>
       <c r="DI156" s="5" t="n"/>
     </row>
-    <row r="157" ht="4.96" customHeight="1">
+    <row r="157" ht="4.65" customHeight="1">
       <c r="L157" s="5" t="n"/>
       <c r="DI157" s="5" t="n"/>
     </row>
-    <row r="158" ht="4.96" customHeight="1">
+    <row r="158" ht="4.65" customHeight="1">
       <c r="L158" s="32" t="inlineStr">
         <is>
           <t>・製品の瑕疵、無償保証期間は御購入後3ヶ月間です。</t>
@@ -5186,31 +5192,31 @@
       </c>
       <c r="DI158" s="5" t="n"/>
     </row>
-    <row r="159" ht="4.96" customHeight="1">
+    <row r="159" ht="4.65" customHeight="1">
       <c r="L159" s="5" t="n"/>
       <c r="DI159" s="5" t="n"/>
     </row>
-    <row r="160" ht="4.96" customHeight="1">
+    <row r="160" ht="4.65" customHeight="1">
       <c r="L160" s="5" t="n"/>
       <c r="DI160" s="5" t="n"/>
     </row>
-    <row r="161" ht="4.96" customHeight="1">
+    <row r="161" ht="4.65" customHeight="1">
       <c r="L161" s="5" t="n"/>
       <c r="DI161" s="5" t="n"/>
     </row>
-    <row r="162" ht="4.96" customHeight="1">
+    <row r="162" ht="4.65" customHeight="1">
       <c r="L162" s="5" t="n"/>
       <c r="DI162" s="5" t="n"/>
     </row>
-    <row r="163" ht="4.96" customHeight="1">
+    <row r="163" ht="4.65" customHeight="1">
       <c r="L163" s="5" t="n"/>
       <c r="DI163" s="5" t="n"/>
     </row>
-    <row r="164" ht="4.96" customHeight="1">
+    <row r="164" ht="4.65" customHeight="1">
       <c r="L164" s="5" t="n"/>
       <c r="DI164" s="5" t="n"/>
     </row>
-    <row r="165" ht="4.96" customHeight="1">
+    <row r="165" ht="4.65" customHeight="1">
       <c r="L165" s="1" t="n"/>
       <c r="M165" s="2" t="n"/>
       <c r="N165" s="2" t="n"/>
@@ -5314,19 +5320,25 @@
       <c r="DH165" s="2" t="n"/>
       <c r="DI165" s="1" t="n"/>
     </row>
-    <row r="166" ht="4.96" customHeight="1"/>
-    <row r="167" ht="4.96" customHeight="1"/>
-    <row r="168" ht="4.96" customHeight="1"/>
-    <row r="169" ht="4.96" customHeight="1"/>
-    <row r="170" ht="4.96" customHeight="1"/>
-    <row r="171" ht="4.96" customHeight="1"/>
-    <row r="172" ht="4.96" customHeight="1"/>
-    <row r="173" ht="4.96" customHeight="1"/>
-    <row r="174" ht="4.96" customHeight="1"/>
-    <row r="175" ht="4.96" customHeight="1"/>
-    <row r="176" ht="4.96" customHeight="1"/>
+    <row r="166" ht="4.65" customHeight="1"/>
+    <row r="167" ht="4.65" customHeight="1"/>
+    <row r="168" ht="4.65" customHeight="1"/>
+    <row r="169" ht="4.65" customHeight="1"/>
+    <row r="170" ht="4.65" customHeight="1"/>
+    <row r="171" ht="4.65" customHeight="1"/>
+    <row r="172" ht="4.65" customHeight="1"/>
+    <row r="173" ht="4.65" customHeight="1"/>
+    <row r="174" ht="4.65" customHeight="1"/>
+    <row r="175" ht="4.65" customHeight="1"/>
+    <row r="176" ht="4.65" customHeight="1"/>
+    <row r="177" ht="4.65" customHeight="1"/>
+    <row r="178" ht="4.65" customHeight="1"/>
+    <row r="179" ht="4.65" customHeight="1"/>
+    <row r="180" ht="4.65" customHeight="1"/>
+    <row r="181" ht="4.65" customHeight="1"/>
+    <row r="182" ht="4.65" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.2" right="0.2" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -5518,7 +5530,7 @@
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>AAAAAA+MS-PGothic</t>
+          <t>MS-PGothic</t>
         </is>
       </c>
       <c r="C15" s="35" t="n">
@@ -5531,7 +5543,7 @@
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>AAAAAA+MS-PGothic</t>
+          <t>MS-PGothic</t>
         </is>
       </c>
       <c r="C16" s="35" t="n">
